--- a/inp_Excel/mov_clienti_alloggi.xlsx
+++ b/inp_Excel/mov_clienti_alloggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="16">
   <si>
     <t>MOV_CLIENTI_ALLOGGIO_PK</t>
   </si>
@@ -156,8 +156,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:N392" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:N392"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:N391" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:N391"/>
   <tableColumns count="14">
     <tableColumn id="1" name="MOV_CLIENTI_ALLOGGIO_PK"/>
     <tableColumn id="2" name="VIAGGIO_ID_FK"/>
@@ -3501,23 +3501,21 @@
     </row>
     <row r="100" customHeight="1" ht="20">
       <c r="A100" s="5" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>141</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="F100" s="5"/>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
@@ -3535,23 +3533,29 @@
     </row>
     <row r="101" customHeight="1" ht="20">
       <c r="A101" s="5" t="n">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>732</v>
-      </c>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
+        <v>527</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>766</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>765</v>
+      </c>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="6" t="s">
@@ -3567,29 +3571,23 @@
     </row>
     <row r="102" customHeight="1" ht="20">
       <c r="A102" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>527</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>766</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>528</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>765</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
       <c r="K102" s="6" t="s">
@@ -3605,19 +3603,19 @@
     </row>
     <row r="103" customHeight="1" ht="20">
       <c r="A103" s="5" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>81</v>
+        <v>783</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
@@ -3637,19 +3635,19 @@
     </row>
     <row r="104" customHeight="1" ht="20">
       <c r="A104" s="5" t="n">
-        <v>201</v>
+        <v>1621</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>322</v>
+        <v>922</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>783</v>
+        <v>1467</v>
       </c>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
@@ -3669,21 +3667,23 @@
     </row>
     <row r="105" customHeight="1" ht="20">
       <c r="A105" s="5" t="n">
-        <v>1621</v>
+        <v>262</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>922</v>
+        <v>363</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F105" s="5"/>
+        <v>807</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>808</v>
+      </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
@@ -3701,22 +3701,22 @@
     </row>
     <row r="106" customHeight="1" ht="20">
       <c r="A106" s="5" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>808</v>
+        <v>85</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="107" customHeight="1" ht="20">
       <c r="A107" s="5" t="n">
-        <v>281</v>
+        <v>441</v>
       </c>
       <c r="B107" s="5" t="n">
         <v>23</v>
@@ -3747,10 +3747,10 @@
         <v>1</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>843</v>
+        <v>963</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>85</v>
+        <v>964</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -3769,22 +3769,22 @@
     </row>
     <row r="108" customHeight="1" ht="20">
       <c r="A108" s="5" t="n">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>963</v>
+        <v>1164</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>964</v>
+        <v>1163</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="109" customHeight="1" ht="20">
       <c r="A109" s="5" t="n">
-        <v>501</v>
+        <v>562</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>262</v>
+        <v>402</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1164</v>
+        <v>1203</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>1163</v>
+        <v>90</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="110" customHeight="1" ht="20">
       <c r="A110" s="5" t="n">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="B110" s="5" t="n">
         <v>81</v>
@@ -3849,10 +3849,10 @@
         <v>1</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1203</v>
+        <v>1223</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>90</v>
+        <v>1224</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
@@ -3871,23 +3871,21 @@
     </row>
     <row r="111" customHeight="1" ht="20">
       <c r="A111" s="5" t="n">
-        <v>581</v>
+        <v>761</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>402</v>
+        <v>522</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1223</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>1224</v>
-      </c>
+        <v>1423</v>
+      </c>
+      <c r="F111" s="5"/>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
@@ -3905,19 +3903,19 @@
     </row>
     <row r="112" customHeight="1" ht="20">
       <c r="A112" s="5" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="D112" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1423</v>
+        <v>1404</v>
       </c>
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
@@ -3937,21 +3935,23 @@
     </row>
     <row r="113" customHeight="1" ht="20">
       <c r="A113" s="5" t="n">
-        <v>763</v>
+        <v>981</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>502</v>
+        <v>582</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1404</v>
-      </c>
-      <c r="F113" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>83</v>
+      </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
@@ -3969,22 +3969,22 @@
     </row>
     <row r="114" customHeight="1" ht="20">
       <c r="A114" s="5" t="n">
-        <v>981</v>
+        <v>1282</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>582</v>
+        <v>642</v>
       </c>
       <c r="D114" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>463</v>
+        <v>727</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>83</v>
+        <v>728</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="115" customHeight="1" ht="20">
       <c r="A115" s="5" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B115" s="5" t="n">
         <v>121</v>
@@ -4015,10 +4015,10 @@
         <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>727</v>
+        <v>1134</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>728</v>
+        <v>1133</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -4037,7 +4037,7 @@
     </row>
     <row r="116" customHeight="1" ht="20">
       <c r="A116" s="5" t="n">
-        <v>1283</v>
+        <v>1361</v>
       </c>
       <c r="B116" s="5" t="n">
         <v>121</v>
@@ -4049,10 +4049,10 @@
         <v>1</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1134</v>
+        <v>1804</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>1133</v>
+        <v>1803</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -4071,22 +4071,22 @@
     </row>
     <row r="117" customHeight="1" ht="20">
       <c r="A117" s="5" t="n">
-        <v>1361</v>
+        <v>1401</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>642</v>
+        <v>822</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1804</v>
+        <v>627</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>1803</v>
+        <v>626</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -4105,22 +4105,22 @@
     </row>
     <row r="118" customHeight="1" ht="20">
       <c r="A118" s="5" t="n">
-        <v>1401</v>
+        <v>1682</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>281</v>
+        <v>321</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>822</v>
+        <v>862</v>
       </c>
       <c r="D118" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>627</v>
+        <v>2003</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>626</v>
+        <v>2004</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="119" customHeight="1" ht="20">
       <c r="A119" s="5" t="n">
-        <v>1682</v>
+        <v>1582</v>
       </c>
       <c r="B119" s="5" t="n">
         <v>321</v>
@@ -4151,10 +4151,10 @@
         <v>1</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2003</v>
+        <v>1904</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>2004</v>
+        <v>1903</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -4173,23 +4173,21 @@
     </row>
     <row r="120" customHeight="1" ht="20">
       <c r="A120" s="5" t="n">
-        <v>1582</v>
+        <v>1641</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>862</v>
+        <v>942</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1904</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>1903</v>
-      </c>
+        <v>1948</v>
+      </c>
+      <c r="F120" s="5"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
@@ -4207,7 +4205,7 @@
     </row>
     <row r="121" customHeight="1" ht="20">
       <c r="A121" s="5" t="n">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>26</v>
@@ -4219,7 +4217,7 @@
         <v>2</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
@@ -4239,7 +4237,7 @@
     </row>
     <row r="122" customHeight="1" ht="20">
       <c r="A122" s="5" t="n">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="B122" s="5" t="n">
         <v>26</v>
@@ -4251,7 +4249,7 @@
         <v>2</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
@@ -4271,7 +4269,7 @@
     </row>
     <row r="123" customHeight="1" ht="20">
       <c r="A123" s="5" t="n">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B123" s="5" t="n">
         <v>26</v>
@@ -4280,12 +4278,14 @@
         <v>942</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1945</v>
-      </c>
-      <c r="F123" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>22</v>
+      </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -4303,23 +4303,21 @@
     </row>
     <row r="124" customHeight="1" ht="20">
       <c r="A124" s="5" t="n">
-        <v>1647</v>
+        <v>1681</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>26</v>
+        <v>321</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>942</v>
+        <v>862</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>22</v>
-      </c>
+        <v>1147</v>
+      </c>
+      <c r="F124" s="5"/>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -4337,19 +4335,19 @@
     </row>
     <row r="125" customHeight="1" ht="20">
       <c r="A125" s="5" t="n">
-        <v>1681</v>
+        <v>1701</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>862</v>
+        <v>822</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1147</v>
+        <v>341</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
@@ -4369,19 +4367,19 @@
     </row>
     <row r="126" customHeight="1" ht="20">
       <c r="A126" s="5" t="n">
-        <v>1701</v>
+        <v>1722</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>822</v>
+        <v>1002</v>
       </c>
       <c r="D126" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>341</v>
+        <v>26</v>
       </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
@@ -4401,21 +4399,23 @@
     </row>
     <row r="127" customHeight="1" ht="20">
       <c r="A127" s="5" t="n">
-        <v>1722</v>
+        <v>1921</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>48</v>
+        <v>281</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>1002</v>
+        <v>822</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F127" s="5"/>
+        <v>2164</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>2163</v>
+      </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
@@ -4433,22 +4433,22 @@
     </row>
     <row r="128" customHeight="1" ht="20">
       <c r="A128" s="5" t="n">
-        <v>1921</v>
+        <v>2141</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>822</v>
+        <v>1202</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2164</v>
+        <v>2304</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>2163</v>
+        <v>2303</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
@@ -4467,23 +4467,21 @@
     </row>
     <row r="129" customHeight="1" ht="20">
       <c r="A129" s="5" t="n">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>261</v>
+        <v>441</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>1202</v>
+        <v>1182</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2304</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>2303</v>
-      </c>
+        <v>2064</v>
+      </c>
+      <c r="F129" s="5"/>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
@@ -4501,21 +4499,23 @@
     </row>
     <row r="130" customHeight="1" ht="20">
       <c r="A130" s="5" t="n">
-        <v>2144</v>
+        <v>1883</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>441</v>
+        <v>281</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>1182</v>
+        <v>822</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F130" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>24</v>
+      </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
@@ -4533,22 +4533,22 @@
     </row>
     <row r="131" customHeight="1" ht="20">
       <c r="A131" s="5" t="n">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>281</v>
+        <v>50</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>822</v>
+        <v>1042</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E131" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F131" s="5" t="n">
         <v>22</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -4567,22 +4567,22 @@
     </row>
     <row r="132" customHeight="1" ht="20">
       <c r="A132" s="5" t="n">
-        <v>1884</v>
+        <v>1942</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>50</v>
+        <v>421</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>1042</v>
+        <v>1102</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>24</v>
+        <v>2184</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>22</v>
+        <v>2183</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="133" customHeight="1" ht="20">
       <c r="A133" s="5" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B133" s="5" t="n">
         <v>421</v>
@@ -4610,14 +4610,12 @@
         <v>1102</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2184</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>2183</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F133" s="5"/>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -4635,19 +4633,19 @@
     </row>
     <row r="134" customHeight="1" ht="20">
       <c r="A134" s="5" t="n">
-        <v>1943</v>
+        <v>2322</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>1102</v>
+        <v>1222</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>81</v>
+        <v>1583</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
@@ -4667,19 +4665,19 @@
     </row>
     <row r="135" customHeight="1" ht="20">
       <c r="A135" s="5" t="n">
-        <v>2322</v>
+        <v>2501</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D135" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1583</v>
+        <v>26</v>
       </c>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
@@ -4699,21 +4697,23 @@
     </row>
     <row r="136" customHeight="1" ht="20">
       <c r="A136" s="5" t="n">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F136" s="5"/>
+        <v>2443</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>1190</v>
+      </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -4731,22 +4731,22 @@
     </row>
     <row r="137" customHeight="1" ht="20">
       <c r="A137" s="5" t="n">
-        <v>2401</v>
+        <v>2461</v>
       </c>
       <c r="B137" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1222</v>
+        <v>1302</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2443</v>
+        <v>33</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>1190</v>
+        <v>2191</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="138" customHeight="1" ht="20">
       <c r="A138" s="5" t="n">
-        <v>2461</v>
+        <v>2841</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>461</v>
+        <v>41</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1302</v>
+        <v>1403</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>33</v>
+        <v>585</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>2191</v>
+        <v>584</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -4799,22 +4799,22 @@
     </row>
     <row r="139" customHeight="1" ht="20">
       <c r="A139" s="5" t="n">
-        <v>2841</v>
+        <v>2466</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>41</v>
+        <v>481</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1403</v>
+        <v>1282</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>585</v>
+        <v>728</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>584</v>
+        <v>727</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -4833,23 +4833,21 @@
     </row>
     <row r="140" customHeight="1" ht="20">
       <c r="A140" s="5" t="n">
-        <v>2466</v>
+        <v>2481</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1282</v>
+        <v>1302</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>728</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>727</v>
-      </c>
+        <v>2503</v>
+      </c>
+      <c r="F140" s="5"/>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
@@ -4867,19 +4865,19 @@
     </row>
     <row r="141" customHeight="1" ht="20">
       <c r="A141" s="5" t="n">
-        <v>2481</v>
+        <v>2621</v>
       </c>
       <c r="B141" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1302</v>
+        <v>1222</v>
       </c>
       <c r="D141" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2503</v>
+        <v>2623</v>
       </c>
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
@@ -4899,21 +4897,23 @@
     </row>
     <row r="142" customHeight="1" ht="20">
       <c r="A142" s="5" t="n">
-        <v>2621</v>
+        <v>2641</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>1222</v>
+        <v>1282</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2623</v>
-      </c>
-      <c r="F142" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>83</v>
+      </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -4931,23 +4931,21 @@
     </row>
     <row r="143" customHeight="1" ht="20">
       <c r="A143" s="5" t="n">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>481</v>
+        <v>47</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1282</v>
+        <v>1362</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>463</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>83</v>
-      </c>
+        <v>2643</v>
+      </c>
+      <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
@@ -4965,21 +4963,23 @@
     </row>
     <row r="144" customHeight="1" ht="20">
       <c r="A144" s="5" t="n">
-        <v>2642</v>
+        <v>2764</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>1362</v>
+        <v>1342</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2643</v>
-      </c>
-      <c r="F144" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>22</v>
+      </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
@@ -4997,22 +4997,22 @@
     </row>
     <row r="145" customHeight="1" ht="20">
       <c r="A145" s="5" t="n">
-        <v>2764</v>
+        <v>3081</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>27</v>
+        <v>481</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1342</v>
+        <v>1282</v>
       </c>
       <c r="D145" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>24</v>
+        <v>585</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -5031,53 +5031,49 @@
     </row>
     <row r="146" customHeight="1" ht="20">
       <c r="A146" s="5" t="n">
-        <v>3081</v>
+        <v>3842</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>481</v>
+        <v>681</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>1282</v>
+        <v>1647</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>584</v>
-      </c>
+        <v>3464</v>
+      </c>
+      <c r="F146" s="5"/>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L146" s="7"/>
-      <c r="M146" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N146" s="7" t="n">
-        <v>45831.8349884259</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L146" s="7" t="n">
+        <v>45895.6354861111</v>
+      </c>
+      <c r="M146" s="6"/>
+      <c r="N146" s="7"/>
     </row>
     <row r="147" customHeight="1" ht="20">
       <c r="A147" s="5" t="n">
-        <v>3842</v>
+        <v>2881</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>681</v>
+        <v>501</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>1647</v>
+        <v>1322</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>3464</v>
+        <v>1943</v>
       </c>
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
@@ -5085,31 +5081,35 @@
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L147" s="7" t="n">
-        <v>45895.6354861111</v>
-      </c>
-      <c r="M147" s="6"/>
-      <c r="N147" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L147" s="7"/>
+      <c r="M147" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N147" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="148" customHeight="1" ht="20">
       <c r="A148" s="5" t="n">
-        <v>2881</v>
+        <v>2901</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>501</v>
+        <v>25</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>1322</v>
+        <v>1383</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1943</v>
-      </c>
-      <c r="F148" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
@@ -5127,56 +5127,56 @@
     </row>
     <row r="149" customHeight="1" ht="20">
       <c r="A149" s="5" t="n">
-        <v>2901</v>
+        <v>3423</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>25</v>
+        <v>541</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1383</v>
+        <v>1503</v>
       </c>
       <c r="D149" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>585</v>
+        <v>3066</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>584</v>
+        <v>3067</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L149" s="7"/>
       <c r="M149" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N149" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="150" customHeight="1" ht="20">
       <c r="A150" s="5" t="n">
-        <v>3423</v>
+        <v>3861</v>
       </c>
       <c r="B150" s="5" t="n">
         <v>541</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>1503</v>
+        <v>1664</v>
       </c>
       <c r="D150" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3066</v>
+        <v>3484</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>3067</v>
+        <v>3483</v>
       </c>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
@@ -5185,33 +5185,29 @@
       <c r="K150" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L150" s="7"/>
-      <c r="M150" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N150" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L150" s="7" t="n">
+        <v>45903.5766435185</v>
+      </c>
+      <c r="M150" s="6"/>
+      <c r="N150" s="7"/>
     </row>
     <row r="151" customHeight="1" ht="20">
       <c r="A151" s="5" t="n">
-        <v>3861</v>
+        <v>3981</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>541</v>
+        <v>722</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1664</v>
+        <v>1684</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>3484</v>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>3483</v>
-      </c>
+        <v>3603</v>
+      </c>
+      <c r="F151" s="5"/>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
@@ -5220,28 +5216,30 @@
         <v>15</v>
       </c>
       <c r="L151" s="7" t="n">
-        <v>45903.5766435185</v>
+        <v>45938.6115740741</v>
       </c>
       <c r="M151" s="6"/>
       <c r="N151" s="7"/>
     </row>
     <row r="152" customHeight="1" ht="20">
       <c r="A152" s="5" t="n">
-        <v>3981</v>
+        <v>4181</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>722</v>
+        <v>762</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>1684</v>
+        <v>1724</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>3603</v>
-      </c>
-      <c r="F152" s="5"/>
+        <v>3767</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>3768</v>
+      </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
@@ -5250,61 +5248,63 @@
         <v>15</v>
       </c>
       <c r="L152" s="7" t="n">
-        <v>45938.6115740741</v>
+        <v>45994.6961805556</v>
       </c>
       <c r="M152" s="6"/>
       <c r="N152" s="7"/>
     </row>
     <row r="153" customHeight="1" ht="20">
       <c r="A153" s="5" t="n">
-        <v>4181</v>
+        <v>42</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>762</v>
+        <v>1</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1724</v>
+        <v>182</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>3767</v>
+        <v>503</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>3768</v>
+        <v>504</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L153" s="7" t="n">
-        <v>45994.6961805556</v>
-      </c>
-      <c r="M153" s="6"/>
-      <c r="N153" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L153" s="7"/>
+      <c r="M153" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N153" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="154" customHeight="1" ht="20">
       <c r="A154" s="5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>503</v>
+        <v>583</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>504</v>
+        <v>27</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
@@ -5323,7 +5323,7 @@
     </row>
     <row r="155" customHeight="1" ht="20">
       <c r="A155" s="5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B155" s="5" t="n">
         <v>48</v>
@@ -5332,13 +5332,13 @@
         <v>202</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>583</v>
+        <v>543</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>27</v>
+        <v>544</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="156" customHeight="1" ht="20">
       <c r="A156" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>543</v>
+        <v>585</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>544</v>
+        <v>584</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
@@ -5391,23 +5391,21 @@
     </row>
     <row r="157" customHeight="1" ht="20">
       <c r="A157" s="5" t="n">
-        <v>52</v>
+        <v>421</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>584</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="F157" s="5"/>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
@@ -5425,21 +5423,23 @@
     </row>
     <row r="158" customHeight="1" ht="20">
       <c r="A158" s="5" t="n">
-        <v>421</v>
+        <v>146</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>401</v>
-      </c>
-      <c r="F158" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>463</v>
+      </c>
       <c r="G158" s="5"/>
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
@@ -5457,22 +5457,22 @@
     </row>
     <row r="159" customHeight="1" ht="20">
       <c r="A159" s="5" t="n">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="D159" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>83</v>
+        <v>714</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>463</v>
+        <v>715</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
@@ -5491,22 +5491,22 @@
     </row>
     <row r="160" customHeight="1" ht="20">
       <c r="A160" s="5" t="n">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="D160" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>714</v>
+        <v>626</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>715</v>
+        <v>627</v>
       </c>
       <c r="G160" s="5"/>
       <c r="H160" s="5"/>
@@ -5525,7 +5525,7 @@
     </row>
     <row r="161" customHeight="1" ht="20">
       <c r="A161" s="5" t="n">
-        <v>263</v>
+        <v>347</v>
       </c>
       <c r="B161" s="5" t="n">
         <v>27</v>
@@ -5537,10 +5537,10 @@
         <v>1</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>626</v>
+        <v>24</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>627</v>
+        <v>22</v>
       </c>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
@@ -5559,23 +5559,21 @@
     </row>
     <row r="162" customHeight="1" ht="20">
       <c r="A162" s="5" t="n">
-        <v>347</v>
+        <v>194</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>22</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="F162" s="5"/>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
@@ -5593,7 +5591,7 @@
     </row>
     <row r="163" customHeight="1" ht="20">
       <c r="A163" s="5" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B163" s="5" t="n">
         <v>44</v>
@@ -5602,12 +5600,14 @@
         <v>322</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>773</v>
-      </c>
-      <c r="F163" s="5"/>
+        <v>774</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>784</v>
+      </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
@@ -5625,23 +5625,21 @@
     </row>
     <row r="164" customHeight="1" ht="20">
       <c r="A164" s="5" t="n">
-        <v>202</v>
+        <v>401</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>774</v>
-      </c>
-      <c r="F164" s="5" t="n">
-        <v>784</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="F164" s="5"/>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
@@ -5659,21 +5657,23 @@
     </row>
     <row r="165" customHeight="1" ht="20">
       <c r="A165" s="5" t="n">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>363</v>
+        <v>262</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>381</v>
-      </c>
-      <c r="F165" s="5"/>
+        <v>996</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>995</v>
+      </c>
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
       <c r="I165" s="5"/>
@@ -5691,22 +5691,22 @@
     </row>
     <row r="166" customHeight="1" ht="20">
       <c r="A166" s="5" t="n">
-        <v>482</v>
+        <v>604</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>262</v>
+        <v>502</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>996</v>
+        <v>142</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>995</v>
+        <v>141</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="167" customHeight="1" ht="20">
       <c r="A167" s="5" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>142</v>
+        <v>844</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="168" customHeight="1" ht="20">
       <c r="A168" s="5" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B168" s="5" t="n">
         <v>141</v>
@@ -5768,14 +5768,12 @@
         <v>462</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>844</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>91</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="F168" s="5"/>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
@@ -5793,19 +5791,19 @@
     </row>
     <row r="169" customHeight="1" ht="20">
       <c r="A169" s="5" t="n">
-        <v>608</v>
+        <v>722</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="D169" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>85</v>
+        <v>743</v>
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5"/>
@@ -5825,7 +5823,7 @@
     </row>
     <row r="170" customHeight="1" ht="20">
       <c r="A170" s="5" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B170" s="5" t="n">
         <v>181</v>
@@ -5837,7 +5835,7 @@
         <v>2</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>743</v>
+        <v>664</v>
       </c>
       <c r="F170" s="5"/>
       <c r="G170" s="5"/>
@@ -5857,7 +5855,7 @@
     </row>
     <row r="171" customHeight="1" ht="20">
       <c r="A171" s="5" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B171" s="5" t="n">
         <v>181</v>
@@ -5869,7 +5867,7 @@
         <v>2</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>664</v>
+        <v>1403</v>
       </c>
       <c r="F171" s="5"/>
       <c r="G171" s="5"/>
@@ -5889,21 +5887,23 @@
     </row>
     <row r="172" customHeight="1" ht="20">
       <c r="A172" s="5" t="n">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1403</v>
-      </c>
-      <c r="F172" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>625</v>
+      </c>
       <c r="G172" s="5"/>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
@@ -5921,23 +5921,21 @@
     </row>
     <row r="173" customHeight="1" ht="20">
       <c r="A173" s="5" t="n">
-        <v>741</v>
+        <v>801</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>625</v>
-      </c>
+        <v>1463</v>
+      </c>
+      <c r="F173" s="5"/>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
@@ -5955,21 +5953,23 @@
     </row>
     <row r="174" customHeight="1" ht="20">
       <c r="A174" s="5" t="n">
-        <v>801</v>
+        <v>962</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>181</v>
+        <v>25</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>502</v>
+        <v>622</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>1463</v>
-      </c>
-      <c r="F174" s="5"/>
+        <v>261</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>623</v>
+      </c>
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
@@ -5987,22 +5987,22 @@
     </row>
     <row r="175" customHeight="1" ht="20">
       <c r="A175" s="5" t="n">
-        <v>962</v>
+        <v>1161</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="D175" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>261</v>
+        <v>963</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>623</v>
+        <v>964</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5"/>
@@ -6021,23 +6021,21 @@
     </row>
     <row r="176" customHeight="1" ht="20">
       <c r="A176" s="5" t="n">
-        <v>1161</v>
+        <v>1003</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>642</v>
+        <v>562</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>963</v>
-      </c>
-      <c r="F176" s="5" t="n">
-        <v>964</v>
-      </c>
+        <v>1463</v>
+      </c>
+      <c r="F176" s="5"/>
       <c r="G176" s="5"/>
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
@@ -6055,21 +6053,23 @@
     </row>
     <row r="177" customHeight="1" ht="20">
       <c r="A177" s="5" t="n">
-        <v>1003</v>
+        <v>1042</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1463</v>
-      </c>
-      <c r="F177" s="5"/>
+        <v>221</v>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>1131</v>
+      </c>
       <c r="G177" s="5"/>
       <c r="H177" s="5"/>
       <c r="I177" s="5"/>
@@ -6087,23 +6087,21 @@
     </row>
     <row r="178" customHeight="1" ht="20">
       <c r="A178" s="5" t="n">
-        <v>1042</v>
+        <v>1721</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>582</v>
+        <v>822</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="F178" s="5" t="n">
-        <v>1131</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F178" s="5"/>
       <c r="G178" s="5"/>
       <c r="H178" s="5"/>
       <c r="I178" s="5"/>
@@ -6121,13 +6119,13 @@
     </row>
     <row r="179" customHeight="1" ht="20">
       <c r="A179" s="5" t="n">
-        <v>1721</v>
+        <v>1181</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>822</v>
+        <v>722</v>
       </c>
       <c r="D179" s="5" t="n">
         <v>2</v>
@@ -6153,19 +6151,19 @@
     </row>
     <row r="180" customHeight="1" ht="20">
       <c r="A180" s="5" t="n">
-        <v>1181</v>
+        <v>1245</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="D180" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>26</v>
+        <v>1052</v>
       </c>
       <c r="F180" s="5"/>
       <c r="G180" s="5"/>
@@ -6185,7 +6183,7 @@
     </row>
     <row r="181" customHeight="1" ht="20">
       <c r="A181" s="5" t="n">
-        <v>1245</v>
+        <v>1261</v>
       </c>
       <c r="B181" s="5" t="n">
         <v>101</v>
@@ -6194,12 +6192,14 @@
         <v>742</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1052</v>
-      </c>
-      <c r="F181" s="5"/>
+        <v>1684</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>1683</v>
+      </c>
       <c r="G181" s="5"/>
       <c r="H181" s="5"/>
       <c r="I181" s="5"/>
@@ -6217,23 +6217,21 @@
     </row>
     <row r="182" customHeight="1" ht="20">
       <c r="A182" s="5" t="n">
-        <v>1261</v>
+        <v>1662</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>742</v>
+        <v>962</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1684</v>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>1683</v>
-      </c>
+        <v>1964</v>
+      </c>
+      <c r="F182" s="5"/>
       <c r="G182" s="5"/>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
@@ -6251,21 +6249,23 @@
     </row>
     <row r="183" customHeight="1" ht="20">
       <c r="A183" s="5" t="n">
-        <v>1662</v>
+        <v>1302</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>381</v>
+        <v>121</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>962</v>
+        <v>642</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1964</v>
-      </c>
-      <c r="F183" s="5"/>
+        <v>1704</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>1703</v>
+      </c>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
@@ -6283,22 +6283,22 @@
     </row>
     <row r="184" customHeight="1" ht="20">
       <c r="A184" s="5" t="n">
-        <v>1302</v>
+        <v>1663</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>121</v>
+        <v>381</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>642</v>
+        <v>962</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1704</v>
+        <v>1965</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>1703</v>
+        <v>1963</v>
       </c>
       <c r="G184" s="5"/>
       <c r="H184" s="5"/>
@@ -6317,23 +6317,21 @@
     </row>
     <row r="185" customHeight="1" ht="20">
       <c r="A185" s="5" t="n">
-        <v>1663</v>
+        <v>1341</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>381</v>
+        <v>50</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>962</v>
+        <v>802</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1965</v>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>1963</v>
-      </c>
+        <v>1783</v>
+      </c>
+      <c r="F185" s="5"/>
       <c r="G185" s="5"/>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
@@ -6351,7 +6349,7 @@
     </row>
     <row r="186" customHeight="1" ht="20">
       <c r="A186" s="5" t="n">
-        <v>1341</v>
+        <v>1381</v>
       </c>
       <c r="B186" s="5" t="n">
         <v>50</v>
@@ -6363,7 +6361,7 @@
         <v>2</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>1783</v>
+        <v>1823</v>
       </c>
       <c r="F186" s="5"/>
       <c r="G186" s="5"/>
@@ -6383,21 +6381,23 @@
     </row>
     <row r="187" customHeight="1" ht="20">
       <c r="A187" s="5" t="n">
-        <v>1381</v>
+        <v>1421</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>802</v>
+        <v>642</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1823</v>
-      </c>
-      <c r="F187" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G187" s="5"/>
       <c r="H187" s="5"/>
       <c r="I187" s="5"/>
@@ -6415,22 +6415,22 @@
     </row>
     <row r="188" customHeight="1" ht="20">
       <c r="A188" s="5" t="n">
-        <v>1421</v>
+        <v>1442</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>642</v>
+        <v>822</v>
       </c>
       <c r="D188" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>585</v>
+        <v>624</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="G188" s="5"/>
       <c r="H188" s="5"/>
@@ -6449,7 +6449,7 @@
     </row>
     <row r="189" customHeight="1" ht="20">
       <c r="A189" s="5" t="n">
-        <v>1442</v>
+        <v>2046</v>
       </c>
       <c r="B189" s="5" t="n">
         <v>281</v>
@@ -6458,14 +6458,12 @@
         <v>822</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="F189" s="5" t="n">
-        <v>625</v>
-      </c>
+        <v>1404</v>
+      </c>
+      <c r="F189" s="5"/>
       <c r="G189" s="5"/>
       <c r="H189" s="5"/>
       <c r="I189" s="5"/>
@@ -6483,23 +6481,29 @@
     </row>
     <row r="190" customHeight="1" ht="20">
       <c r="A190" s="5" t="n">
-        <v>2046</v>
+        <v>1521</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>822</v>
+        <v>662</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>1404</v>
-      </c>
-      <c r="F190" s="5"/>
-      <c r="G190" s="5"/>
-      <c r="H190" s="5"/>
+        <v>1883</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>1886</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>1884</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>1885</v>
+      </c>
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
       <c r="K190" s="6" t="s">
@@ -6515,7 +6519,7 @@
     </row>
     <row r="191" customHeight="1" ht="20">
       <c r="A191" s="5" t="n">
-        <v>1521</v>
+        <v>1541</v>
       </c>
       <c r="B191" s="5" t="n">
         <v>241</v>
@@ -6524,20 +6528,16 @@
         <v>662</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1883</v>
+        <v>1763</v>
       </c>
       <c r="F191" s="5" t="n">
-        <v>1886</v>
-      </c>
-      <c r="G191" s="5" t="n">
-        <v>1884</v>
-      </c>
-      <c r="H191" s="5" t="n">
-        <v>1885</v>
-      </c>
+        <v>1764</v>
+      </c>
+      <c r="G191" s="5"/>
+      <c r="H191" s="5"/>
       <c r="I191" s="5"/>
       <c r="J191" s="5"/>
       <c r="K191" s="6" t="s">
@@ -6553,22 +6553,22 @@
     </row>
     <row r="192" customHeight="1" ht="20">
       <c r="A192" s="5" t="n">
-        <v>1541</v>
+        <v>1761</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>662</v>
+        <v>822</v>
       </c>
       <c r="D192" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1763</v>
+        <v>585</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>1764</v>
+        <v>584</v>
       </c>
       <c r="G192" s="5"/>
       <c r="H192" s="5"/>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="193" customHeight="1" ht="20">
       <c r="A193" s="5" t="n">
-        <v>1761</v>
+        <v>1801</v>
       </c>
       <c r="B193" s="5" t="n">
-        <v>281</v>
+        <v>101</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>822</v>
+        <v>1022</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>585</v>
+        <v>121</v>
       </c>
       <c r="F193" s="5" t="n">
-        <v>584</v>
+        <v>2043</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="194" customHeight="1" ht="20">
       <c r="A194" s="5" t="n">
-        <v>1801</v>
+        <v>1842</v>
       </c>
       <c r="B194" s="5" t="n">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>1022</v>
+        <v>1042</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>121</v>
+        <v>1164</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>2043</v>
+        <v>1163</v>
       </c>
       <c r="G194" s="5"/>
       <c r="H194" s="5"/>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="195" customHeight="1" ht="20">
       <c r="A195" s="5" t="n">
-        <v>1842</v>
+        <v>1881</v>
       </c>
       <c r="B195" s="5" t="n">
         <v>50</v>
@@ -6667,10 +6667,10 @@
         <v>1</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>1164</v>
+        <v>1523</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>1163</v>
+        <v>1524</v>
       </c>
       <c r="G195" s="5"/>
       <c r="H195" s="5"/>
@@ -6689,23 +6689,21 @@
     </row>
     <row r="196" customHeight="1" ht="20">
       <c r="A196" s="5" t="n">
-        <v>1881</v>
+        <v>2001</v>
       </c>
       <c r="B196" s="5" t="n">
-        <v>50</v>
+        <v>281</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>1042</v>
+        <v>822</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1523</v>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>1524</v>
-      </c>
+        <v>1143</v>
+      </c>
+      <c r="F196" s="5"/>
       <c r="G196" s="5"/>
       <c r="H196" s="5"/>
       <c r="I196" s="5"/>
@@ -6723,7 +6721,7 @@
     </row>
     <row r="197" customHeight="1" ht="20">
       <c r="A197" s="5" t="n">
-        <v>2001</v>
+        <v>1885</v>
       </c>
       <c r="B197" s="5" t="n">
         <v>281</v>
@@ -6732,12 +6730,14 @@
         <v>822</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>1143</v>
-      </c>
-      <c r="F197" s="5"/>
+        <v>2103</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>91</v>
+      </c>
       <c r="G197" s="5"/>
       <c r="H197" s="5"/>
       <c r="I197" s="5"/>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="198" customHeight="1" ht="20">
       <c r="A198" s="5" t="n">
-        <v>1885</v>
+        <v>2045</v>
       </c>
       <c r="B198" s="5" t="n">
         <v>281</v>
@@ -6764,14 +6764,12 @@
         <v>822</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>2103</v>
-      </c>
-      <c r="F198" s="5" t="n">
-        <v>91</v>
-      </c>
+        <v>1424</v>
+      </c>
+      <c r="F198" s="5"/>
       <c r="G198" s="5"/>
       <c r="H198" s="5"/>
       <c r="I198" s="5"/>
@@ -6789,21 +6787,23 @@
     </row>
     <row r="199" customHeight="1" ht="20">
       <c r="A199" s="5" t="n">
-        <v>2045</v>
+        <v>2061</v>
       </c>
       <c r="B199" s="5" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>822</v>
+        <v>1122</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="F199" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>625</v>
+      </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5"/>
       <c r="I199" s="5"/>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="200" customHeight="1" ht="20">
       <c r="A200" s="5" t="n">
-        <v>2061</v>
+        <v>1944</v>
       </c>
       <c r="B200" s="5" t="n">
-        <v>301</v>
+        <v>421</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>1122</v>
+        <v>1102</v>
       </c>
       <c r="D200" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>624</v>
+        <v>2186</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>625</v>
+        <v>2185</v>
       </c>
       <c r="G200" s="5"/>
       <c r="H200" s="5"/>
@@ -6855,7 +6855,7 @@
     </row>
     <row r="201" customHeight="1" ht="20">
       <c r="A201" s="5" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B201" s="5" t="n">
         <v>421</v>
@@ -6867,10 +6867,10 @@
         <v>1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F201" s="5" t="n">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5"/>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="202" customHeight="1" ht="20">
       <c r="A202" s="5" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B202" s="5" t="n">
         <v>421</v>
@@ -6901,10 +6901,10 @@
         <v>1</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="203" customHeight="1" ht="20">
       <c r="A203" s="5" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B203" s="5" t="n">
         <v>421</v>
@@ -6935,10 +6935,10 @@
         <v>1</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>2189</v>
+        <v>33</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
@@ -6957,22 +6957,22 @@
     </row>
     <row r="204" customHeight="1" ht="20">
       <c r="A204" s="5" t="n">
-        <v>1947</v>
+        <v>2463</v>
       </c>
       <c r="B204" s="5" t="n">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>1102</v>
+        <v>1302</v>
       </c>
       <c r="D204" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>33</v>
+        <v>2185</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="G204" s="5"/>
       <c r="H204" s="5"/>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="205" customHeight="1" ht="20">
       <c r="A205" s="5" t="n">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="B205" s="5" t="n">
         <v>461</v>
@@ -7000,13 +7000,13 @@
         <v>1302</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="G205" s="5"/>
       <c r="H205" s="5"/>
@@ -7025,22 +7025,22 @@
     </row>
     <row r="206" customHeight="1" ht="20">
       <c r="A206" s="5" t="n">
-        <v>2465</v>
+        <v>2521</v>
       </c>
       <c r="B206" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>1302</v>
+        <v>1322</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>2184</v>
+        <v>2543</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>2183</v>
+        <v>2544</v>
       </c>
       <c r="G206" s="5"/>
       <c r="H206" s="5"/>
@@ -7059,23 +7059,21 @@
     </row>
     <row r="207" customHeight="1" ht="20">
       <c r="A207" s="5" t="n">
-        <v>2521</v>
+        <v>2324</v>
       </c>
       <c r="B207" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>2543</v>
-      </c>
-      <c r="F207" s="5" t="n">
-        <v>2544</v>
-      </c>
+        <v>2363</v>
+      </c>
+      <c r="F207" s="5"/>
       <c r="G207" s="5"/>
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
@@ -7093,21 +7091,23 @@
     </row>
     <row r="208" customHeight="1" ht="20">
       <c r="A208" s="5" t="n">
-        <v>2324</v>
+        <v>2341</v>
       </c>
       <c r="B208" s="5" t="n">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>1222</v>
+        <v>1162</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>2363</v>
-      </c>
-      <c r="F208" s="5"/>
+        <v>2384</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>2383</v>
+      </c>
       <c r="G208" s="5"/>
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
@@ -7125,23 +7125,21 @@
     </row>
     <row r="209" customHeight="1" ht="20">
       <c r="A209" s="5" t="n">
-        <v>2341</v>
+        <v>2362</v>
       </c>
       <c r="B209" s="5" t="n">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>2384</v>
-      </c>
-      <c r="F209" s="5" t="n">
-        <v>2383</v>
-      </c>
+        <v>2064</v>
+      </c>
+      <c r="F209" s="5"/>
       <c r="G209" s="5"/>
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
@@ -7159,7 +7157,7 @@
     </row>
     <row r="210" customHeight="1" ht="20">
       <c r="A210" s="5" t="n">
-        <v>2362</v>
+        <v>2441</v>
       </c>
       <c r="B210" s="5" t="n">
         <v>461</v>
@@ -7171,7 +7169,7 @@
         <v>2</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>2064</v>
+        <v>2483</v>
       </c>
       <c r="F210" s="5"/>
       <c r="G210" s="5"/>
@@ -7191,21 +7189,23 @@
     </row>
     <row r="211" customHeight="1" ht="20">
       <c r="A211" s="5" t="n">
-        <v>2441</v>
+        <v>2541</v>
       </c>
       <c r="B211" s="5" t="n">
-        <v>461</v>
+        <v>27</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>1222</v>
+        <v>1342</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>2483</v>
-      </c>
-      <c r="F211" s="5"/>
+        <v>2563</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>2564</v>
+      </c>
       <c r="G211" s="5"/>
       <c r="H211" s="5"/>
       <c r="I211" s="5"/>
@@ -7223,23 +7223,21 @@
     </row>
     <row r="212" customHeight="1" ht="20">
       <c r="A212" s="5" t="n">
-        <v>2541</v>
+        <v>2582</v>
       </c>
       <c r="B212" s="5" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>1342</v>
+        <v>1162</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>2563</v>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>2564</v>
-      </c>
+        <v>1563</v>
+      </c>
+      <c r="F212" s="5"/>
       <c r="G212" s="5"/>
       <c r="H212" s="5"/>
       <c r="I212" s="5"/>
@@ -7257,21 +7255,23 @@
     </row>
     <row r="213" customHeight="1" ht="20">
       <c r="A213" s="5" t="n">
-        <v>2582</v>
+        <v>2661</v>
       </c>
       <c r="B213" s="5" t="n">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>1162</v>
+        <v>1202</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F213" s="5"/>
+        <v>2664</v>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>2663</v>
+      </c>
       <c r="G213" s="5"/>
       <c r="H213" s="5"/>
       <c r="I213" s="5"/>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="214" customHeight="1" ht="20">
       <c r="A214" s="5" t="n">
-        <v>2661</v>
+        <v>2702</v>
       </c>
       <c r="B214" s="5" t="n">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>1202</v>
+        <v>1342</v>
       </c>
       <c r="D214" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>2664</v>
+        <v>587</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>2663</v>
+        <v>586</v>
       </c>
       <c r="G214" s="5"/>
       <c r="H214" s="5"/>
@@ -7323,22 +7323,22 @@
     </row>
     <row r="215" customHeight="1" ht="20">
       <c r="A215" s="5" t="n">
-        <v>2702</v>
+        <v>2741</v>
       </c>
       <c r="B215" s="5" t="n">
-        <v>27</v>
+        <v>421</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>1342</v>
+        <v>1363</v>
       </c>
       <c r="D215" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="F215" s="5" t="n">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="G215" s="5"/>
       <c r="H215" s="5"/>
@@ -7357,22 +7357,22 @@
     </row>
     <row r="216" customHeight="1" ht="20">
       <c r="A216" s="5" t="n">
-        <v>2741</v>
+        <v>3101</v>
       </c>
       <c r="B216" s="5" t="n">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>1363</v>
+        <v>1282</v>
       </c>
       <c r="D216" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>624</v>
+        <v>2884</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>625</v>
+        <v>2883</v>
       </c>
       <c r="G216" s="5"/>
       <c r="H216" s="5"/>
@@ -7391,23 +7391,21 @@
     </row>
     <row r="217" customHeight="1" ht="20">
       <c r="A217" s="5" t="n">
-        <v>3101</v>
+        <v>2801</v>
       </c>
       <c r="B217" s="5" t="n">
-        <v>481</v>
+        <v>25</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>1282</v>
+        <v>1383</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>2884</v>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>2883</v>
-      </c>
+        <v>2743</v>
+      </c>
+      <c r="F217" s="5"/>
       <c r="G217" s="5"/>
       <c r="H217" s="5"/>
       <c r="I217" s="5"/>
@@ -7425,19 +7423,19 @@
     </row>
     <row r="218" customHeight="1" ht="20">
       <c r="A218" s="5" t="n">
-        <v>2801</v>
+        <v>2822</v>
       </c>
       <c r="B218" s="5" t="n">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>1383</v>
+        <v>1202</v>
       </c>
       <c r="D218" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>2743</v>
+        <v>2523</v>
       </c>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
@@ -7457,7 +7455,7 @@
     </row>
     <row r="219" customHeight="1" ht="20">
       <c r="A219" s="5" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="B219" s="5" t="n">
         <v>261</v>
@@ -7469,7 +7467,7 @@
         <v>2</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>2523</v>
+        <v>2323</v>
       </c>
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
@@ -7489,21 +7487,23 @@
     </row>
     <row r="220" customHeight="1" ht="20">
       <c r="A220" s="5" t="n">
-        <v>2823</v>
+        <v>2842</v>
       </c>
       <c r="B220" s="5" t="n">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>1202</v>
+        <v>1342</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>2323</v>
-      </c>
-      <c r="F220" s="5"/>
+        <v>2764</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>2783</v>
+      </c>
       <c r="G220" s="5"/>
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
@@ -7521,22 +7521,22 @@
     </row>
     <row r="221" customHeight="1" ht="20">
       <c r="A221" s="5" t="n">
-        <v>2842</v>
+        <v>3021</v>
       </c>
       <c r="B221" s="5" t="n">
-        <v>27</v>
+        <v>501</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>1342</v>
+        <v>1322</v>
       </c>
       <c r="D221" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>2764</v>
+        <v>1023</v>
       </c>
       <c r="F221" s="5" t="n">
-        <v>2783</v>
+        <v>1024</v>
       </c>
       <c r="G221" s="5"/>
       <c r="H221" s="5"/>
@@ -7555,22 +7555,22 @@
     </row>
     <row r="222" customHeight="1" ht="20">
       <c r="A222" s="5" t="n">
-        <v>3021</v>
+        <v>3381</v>
       </c>
       <c r="B222" s="5" t="n">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>1322</v>
+        <v>1423</v>
       </c>
       <c r="D222" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>1023</v>
+        <v>2963</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>1024</v>
+        <v>2964</v>
       </c>
       <c r="G222" s="5"/>
       <c r="H222" s="5"/>
@@ -7589,7 +7589,7 @@
     </row>
     <row r="223" customHeight="1" ht="20">
       <c r="A223" s="5" t="n">
-        <v>3381</v>
+        <v>3321</v>
       </c>
       <c r="B223" s="5" t="n">
         <v>521</v>
@@ -7598,14 +7598,12 @@
         <v>1423</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>2963</v>
-      </c>
-      <c r="F223" s="5" t="n">
-        <v>2964</v>
-      </c>
+        <v>1583</v>
+      </c>
+      <c r="F223" s="5"/>
       <c r="G223" s="5"/>
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
@@ -7623,55 +7621,55 @@
     </row>
     <row r="224" customHeight="1" ht="20">
       <c r="A224" s="5" t="n">
-        <v>3321</v>
+        <v>3401</v>
       </c>
       <c r="B224" s="5" t="n">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="C224" s="5" t="n">
-        <v>1423</v>
+        <v>1503</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>1583</v>
-      </c>
-      <c r="F224" s="5"/>
+        <v>3003</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>3023</v>
+      </c>
       <c r="G224" s="5"/>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
       <c r="K224" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L224" s="7"/>
       <c r="M224" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N224" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="225" customHeight="1" ht="20">
       <c r="A225" s="5" t="n">
-        <v>3401</v>
+        <v>3843</v>
       </c>
       <c r="B225" s="5" t="n">
         <v>541</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>1503</v>
+        <v>1664</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>3003</v>
-      </c>
-      <c r="F225" s="5" t="n">
-        <v>3023</v>
-      </c>
+        <v>3465</v>
+      </c>
+      <c r="F225" s="5"/>
       <c r="G225" s="5"/>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
@@ -7679,31 +7677,31 @@
       <c r="K225" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L225" s="7"/>
-      <c r="M225" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N225" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L225" s="7" t="n">
+        <v>45896.2966550926</v>
+      </c>
+      <c r="M225" s="6"/>
+      <c r="N225" s="7"/>
     </row>
     <row r="226" customHeight="1" ht="20">
       <c r="A226" s="5" t="n">
-        <v>3843</v>
+        <v>3406</v>
       </c>
       <c r="B226" s="5" t="n">
         <v>541</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>1664</v>
+        <v>1503</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>3465</v>
-      </c>
-      <c r="F226" s="5"/>
+        <v>3028</v>
+      </c>
+      <c r="F226" s="5" t="n">
+        <v>3029</v>
+      </c>
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
@@ -7711,31 +7709,31 @@
       <c r="K226" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L226" s="7" t="n">
-        <v>45896.2966550926</v>
-      </c>
-      <c r="M226" s="6"/>
-      <c r="N226" s="7"/>
+      <c r="L226" s="7"/>
+      <c r="M226" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N226" s="7" t="n">
+        <v>45831.8393287037</v>
+      </c>
     </row>
     <row r="227" customHeight="1" ht="20">
       <c r="A227" s="5" t="n">
-        <v>3406</v>
+        <v>3961</v>
       </c>
       <c r="B227" s="5" t="n">
-        <v>541</v>
+        <v>722</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>1503</v>
+        <v>1684</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>3028</v>
-      </c>
-      <c r="F227" s="5" t="n">
-        <v>3029</v>
-      </c>
+        <v>3589</v>
+      </c>
+      <c r="F227" s="5"/>
       <c r="G227" s="5"/>
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
@@ -7743,31 +7741,31 @@
       <c r="K227" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L227" s="7"/>
-      <c r="M227" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N227" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L227" s="7" t="n">
+        <v>45935.4751157407</v>
+      </c>
+      <c r="M227" s="6"/>
+      <c r="N227" s="7"/>
     </row>
     <row r="228" customHeight="1" ht="20">
       <c r="A228" s="5" t="n">
-        <v>3961</v>
+        <v>4061</v>
       </c>
       <c r="B228" s="5" t="n">
-        <v>722</v>
+        <v>762</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>1684</v>
+        <v>1724</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>3589</v>
-      </c>
-      <c r="F228" s="5"/>
+        <v>3663</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>3664</v>
+      </c>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
@@ -7776,14 +7774,14 @@
         <v>15</v>
       </c>
       <c r="L228" s="7" t="n">
-        <v>45935.4751157407</v>
+        <v>45964.6311342593</v>
       </c>
       <c r="M228" s="6"/>
       <c r="N228" s="7"/>
     </row>
     <row r="229" customHeight="1" ht="20">
       <c r="A229" s="5" t="n">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B229" s="5" t="n">
         <v>762</v>
@@ -7795,10 +7793,10 @@
         <v>1</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>3663</v>
+        <v>584</v>
       </c>
       <c r="F229" s="5" t="n">
-        <v>3664</v>
+        <v>585</v>
       </c>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
@@ -7808,29 +7806,29 @@
         <v>15</v>
       </c>
       <c r="L229" s="7" t="n">
-        <v>45964.6311342593</v>
+        <v>45965.4697453704</v>
       </c>
       <c r="M229" s="6"/>
       <c r="N229" s="7"/>
     </row>
     <row r="230" customHeight="1" ht="20">
       <c r="A230" s="5" t="n">
-        <v>4062</v>
+        <v>4064</v>
       </c>
       <c r="B230" s="5" t="n">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>1724</v>
+        <v>1743</v>
       </c>
       <c r="D230" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>584</v>
+        <v>3669</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>585</v>
+        <v>3666</v>
       </c>
       <c r="G230" s="5"/>
       <c r="H230" s="5"/>
@@ -7840,14 +7838,14 @@
         <v>15</v>
       </c>
       <c r="L230" s="7" t="n">
-        <v>45965.4697453704</v>
+        <v>45966.4389236111</v>
       </c>
       <c r="M230" s="6"/>
       <c r="N230" s="7"/>
     </row>
     <row r="231" customHeight="1" ht="20">
       <c r="A231" s="5" t="n">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B231" s="5" t="n">
         <v>781</v>
@@ -7856,14 +7854,12 @@
         <v>1743</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>3669</v>
-      </c>
-      <c r="F231" s="5" t="n">
-        <v>3666</v>
-      </c>
+        <v>3670</v>
+      </c>
+      <c r="F231" s="5"/>
       <c r="G231" s="5"/>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
@@ -7872,14 +7868,14 @@
         <v>15</v>
       </c>
       <c r="L231" s="7" t="n">
-        <v>45966.4389236111</v>
+        <v>45966.5908101852</v>
       </c>
       <c r="M231" s="6"/>
       <c r="N231" s="7"/>
     </row>
     <row r="232" customHeight="1" ht="20">
       <c r="A232" s="5" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B232" s="5" t="n">
         <v>781</v>
@@ -7888,10 +7884,10 @@
         <v>1743</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>3670</v>
+        <v>81</v>
       </c>
       <c r="F232" s="5"/>
       <c r="G232" s="5"/>
@@ -7902,14 +7898,14 @@
         <v>15</v>
       </c>
       <c r="L232" s="7" t="n">
-        <v>45966.5908101852</v>
+        <v>45966.7075231481</v>
       </c>
       <c r="M232" s="6"/>
       <c r="N232" s="7"/>
     </row>
     <row r="233" customHeight="1" ht="20">
       <c r="A233" s="5" t="n">
-        <v>4066</v>
+        <v>4068</v>
       </c>
       <c r="B233" s="5" t="n">
         <v>781</v>
@@ -7918,12 +7914,14 @@
         <v>1743</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="F233" s="5"/>
+        <v>3676</v>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>3675</v>
+      </c>
       <c r="G233" s="5"/>
       <c r="H233" s="5"/>
       <c r="I233" s="5"/>
@@ -7932,14 +7930,14 @@
         <v>15</v>
       </c>
       <c r="L233" s="7" t="n">
-        <v>45966.7075231481</v>
+        <v>45967.3274768519</v>
       </c>
       <c r="M233" s="6"/>
       <c r="N233" s="7"/>
     </row>
     <row r="234" customHeight="1" ht="20">
       <c r="A234" s="5" t="n">
-        <v>4068</v>
+        <v>4069</v>
       </c>
       <c r="B234" s="5" t="n">
         <v>781</v>
@@ -7951,10 +7949,10 @@
         <v>1</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>3676</v>
+        <v>3678</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>3675</v>
+        <v>3677</v>
       </c>
       <c r="G234" s="5"/>
       <c r="H234" s="5"/>
@@ -7964,14 +7962,14 @@
         <v>15</v>
       </c>
       <c r="L234" s="7" t="n">
-        <v>45967.3274768519</v>
+        <v>45967.4627314815</v>
       </c>
       <c r="M234" s="6"/>
       <c r="N234" s="7"/>
     </row>
     <row r="235" customHeight="1" ht="20">
       <c r="A235" s="5" t="n">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="B235" s="5" t="n">
         <v>781</v>
@@ -7983,10 +7981,10 @@
         <v>1</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>3678</v>
+        <v>2203</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>3677</v>
+        <v>3679</v>
       </c>
       <c r="G235" s="5"/>
       <c r="H235" s="5"/>
@@ -7996,29 +7994,29 @@
         <v>15</v>
       </c>
       <c r="L235" s="7" t="n">
-        <v>45967.4627314815</v>
+        <v>45967.5829398148</v>
       </c>
       <c r="M235" s="6"/>
       <c r="N235" s="7"/>
     </row>
     <row r="236" customHeight="1" ht="20">
       <c r="A236" s="5" t="n">
-        <v>4070</v>
+        <v>4303</v>
       </c>
       <c r="B236" s="5" t="n">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>1743</v>
+        <v>1724</v>
       </c>
       <c r="D236" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>2203</v>
+        <v>3868</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>3679</v>
+        <v>3869</v>
       </c>
       <c r="G236" s="5"/>
       <c r="H236" s="5"/>
@@ -8028,29 +8026,29 @@
         <v>15</v>
       </c>
       <c r="L236" s="7" t="n">
-        <v>45967.5829398148</v>
+        <v>46014.8150231481</v>
       </c>
       <c r="M236" s="6"/>
       <c r="N236" s="7"/>
     </row>
     <row r="237" customHeight="1" ht="20">
       <c r="A237" s="5" t="n">
-        <v>4303</v>
+        <v>4321</v>
       </c>
       <c r="B237" s="5" t="n">
-        <v>762</v>
+        <v>801</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>1724</v>
+        <v>1763</v>
       </c>
       <c r="D237" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>3868</v>
+        <v>3888</v>
       </c>
       <c r="F237" s="5" t="n">
-        <v>3869</v>
+        <v>3884</v>
       </c>
       <c r="G237" s="5"/>
       <c r="H237" s="5"/>
@@ -8060,7 +8058,7 @@
         <v>15</v>
       </c>
       <c r="L237" s="7" t="n">
-        <v>46014.8150231481</v>
+        <v>46030.6246180556</v>
       </c>
       <c r="M237" s="6"/>
       <c r="N237" s="7"/>
@@ -8439,22 +8437,26 @@
     </row>
     <row r="249" customHeight="1" ht="20">
       <c r="A249" s="5" t="n">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="B249" s="5" t="n">
         <v>22</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>664</v>
-      </c>
-      <c r="F249" s="5"/>
-      <c r="G249" s="5"/>
+        <v>769</v>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>767</v>
+      </c>
+      <c r="G249" s="5" t="n">
+        <v>768</v>
+      </c>
       <c r="H249" s="5"/>
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
@@ -8471,7 +8473,7 @@
     </row>
     <row r="250" customHeight="1" ht="20">
       <c r="A250" s="5" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B250" s="5" t="n">
         <v>22</v>
@@ -8480,17 +8482,15 @@
         <v>382</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>769</v>
+        <v>624</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="G250" s="5" t="n">
-        <v>768</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="G250" s="5"/>
       <c r="H250" s="5"/>
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="251" customHeight="1" ht="20">
       <c r="A251" s="5" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="B251" s="5" t="n">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="D251" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>624</v>
+        <v>31</v>
       </c>
       <c r="F251" s="5" t="n">
-        <v>625</v>
+        <v>772</v>
       </c>
       <c r="G251" s="5"/>
       <c r="H251" s="5"/>
@@ -8541,7 +8541,7 @@
     </row>
     <row r="252" customHeight="1" ht="20">
       <c r="A252" s="5" t="n">
-        <v>223</v>
+        <v>461</v>
       </c>
       <c r="B252" s="5" t="n">
         <v>121</v>
@@ -8553,10 +8553,10 @@
         <v>1</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>31</v>
+        <v>1023</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>772</v>
+        <v>1024</v>
       </c>
       <c r="G252" s="5"/>
       <c r="H252" s="5"/>
@@ -8575,22 +8575,22 @@
     </row>
     <row r="253" customHeight="1" ht="20">
       <c r="A253" s="5" t="n">
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="B253" s="5" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="D253" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>1023</v>
+        <v>725</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>1024</v>
+        <v>282</v>
       </c>
       <c r="G253" s="5"/>
       <c r="H253" s="5"/>
@@ -8609,7 +8609,7 @@
     </row>
     <row r="254" customHeight="1" ht="20">
       <c r="A254" s="5" t="n">
-        <v>521</v>
+        <v>721</v>
       </c>
       <c r="B254" s="5" t="n">
         <v>141</v>
@@ -8621,10 +8621,10 @@
         <v>1</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>725</v>
+        <v>990</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>282</v>
+        <v>989</v>
       </c>
       <c r="G254" s="5"/>
       <c r="H254" s="5"/>
@@ -8643,22 +8643,22 @@
     </row>
     <row r="255" customHeight="1" ht="20">
       <c r="A255" s="5" t="n">
-        <v>721</v>
+        <v>242</v>
       </c>
       <c r="B255" s="5" t="n">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>462</v>
+        <v>322</v>
       </c>
       <c r="D255" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>990</v>
+        <v>524</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>989</v>
+        <v>523</v>
       </c>
       <c r="G255" s="5"/>
       <c r="H255" s="5"/>
@@ -8677,7 +8677,7 @@
     </row>
     <row r="256" customHeight="1" ht="20">
       <c r="A256" s="5" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B256" s="5" t="n">
         <v>44</v>
@@ -8686,14 +8686,12 @@
         <v>322</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>524</v>
-      </c>
-      <c r="F256" s="5" t="n">
-        <v>523</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="F256" s="5"/>
       <c r="G256" s="5"/>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
@@ -8711,21 +8709,23 @@
     </row>
     <row r="257" customHeight="1" ht="20">
       <c r="A257" s="5" t="n">
-        <v>243</v>
+        <v>605</v>
       </c>
       <c r="B257" s="5" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>764</v>
-      </c>
-      <c r="F257" s="5"/>
+        <v>844</v>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>91</v>
+      </c>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
@@ -8743,23 +8743,21 @@
     </row>
     <row r="258" customHeight="1" ht="20">
       <c r="A258" s="5" t="n">
-        <v>605</v>
+        <v>762</v>
       </c>
       <c r="B258" s="5" t="n">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>262</v>
+        <v>502</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>844</v>
-      </c>
-      <c r="F258" s="5" t="n">
-        <v>91</v>
-      </c>
+        <v>1424</v>
+      </c>
+      <c r="F258" s="5"/>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
@@ -8777,21 +8775,23 @@
     </row>
     <row r="259" customHeight="1" ht="20">
       <c r="A259" s="5" t="n">
-        <v>762</v>
+        <v>1163</v>
       </c>
       <c r="B259" s="5" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>502</v>
+        <v>702</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="F259" s="5"/>
+        <v>1023</v>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>1024</v>
+      </c>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
@@ -8809,22 +8809,22 @@
     </row>
     <row r="260" customHeight="1" ht="20">
       <c r="A260" s="5" t="n">
-        <v>1163</v>
+        <v>1021</v>
       </c>
       <c r="B260" s="5" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>702</v>
+        <v>562</v>
       </c>
       <c r="D260" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>1023</v>
+        <v>1383</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>1024</v>
+        <v>1384</v>
       </c>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
@@ -8843,23 +8843,21 @@
     </row>
     <row r="261" customHeight="1" ht="20">
       <c r="A261" s="5" t="n">
-        <v>1021</v>
+        <v>1324</v>
       </c>
       <c r="B261" s="5" t="n">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>562</v>
+        <v>642</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>1383</v>
-      </c>
-      <c r="F261" s="5" t="n">
-        <v>1384</v>
-      </c>
+        <v>1743</v>
+      </c>
+      <c r="F261" s="5"/>
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
       <c r="I261" s="5"/>
@@ -8877,21 +8875,23 @@
     </row>
     <row r="262" customHeight="1" ht="20">
       <c r="A262" s="5" t="n">
-        <v>1324</v>
+        <v>1246</v>
       </c>
       <c r="B262" s="5" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>642</v>
+        <v>742</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>1743</v>
-      </c>
-      <c r="F262" s="5"/>
+        <v>1664</v>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>1663</v>
+      </c>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
@@ -8909,23 +8909,21 @@
     </row>
     <row r="263" customHeight="1" ht="20">
       <c r="A263" s="5" t="n">
-        <v>1246</v>
+        <v>1323</v>
       </c>
       <c r="B263" s="5" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>742</v>
+        <v>642</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>1664</v>
-      </c>
-      <c r="F263" s="5" t="n">
-        <v>1663</v>
-      </c>
+        <v>1723</v>
+      </c>
+      <c r="F263" s="5"/>
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
       <c r="I263" s="5"/>
@@ -8943,19 +8941,19 @@
     </row>
     <row r="264" customHeight="1" ht="20">
       <c r="A264" s="5" t="n">
-        <v>1323</v>
+        <v>1622</v>
       </c>
       <c r="B264" s="5" t="n">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="D264" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>1723</v>
+        <v>1923</v>
       </c>
       <c r="F264" s="5"/>
       <c r="G264" s="5"/>
@@ -8975,21 +8973,23 @@
     </row>
     <row r="265" customHeight="1" ht="20">
       <c r="A265" s="5" t="n">
-        <v>1622</v>
+        <v>1328</v>
       </c>
       <c r="B265" s="5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>922</v>
+        <v>802</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>1923</v>
-      </c>
-      <c r="F265" s="5"/>
+        <v>1764</v>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>1763</v>
+      </c>
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
       <c r="I265" s="5"/>
@@ -9007,22 +9007,22 @@
     </row>
     <row r="266" customHeight="1" ht="20">
       <c r="A266" s="5" t="n">
-        <v>1328</v>
+        <v>1624</v>
       </c>
       <c r="B266" s="5" t="n">
-        <v>50</v>
+        <v>321</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>802</v>
+        <v>862</v>
       </c>
       <c r="D266" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>1764</v>
+        <v>963</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>1763</v>
+        <v>964</v>
       </c>
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="267" customHeight="1" ht="20">
       <c r="A267" s="5" t="n">
-        <v>1624</v>
+        <v>1461</v>
       </c>
       <c r="B267" s="5" t="n">
-        <v>321</v>
+        <v>241</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>862</v>
+        <v>662</v>
       </c>
       <c r="D267" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>963</v>
+        <v>624</v>
       </c>
       <c r="F267" s="5" t="n">
-        <v>964</v>
+        <v>625</v>
       </c>
       <c r="G267" s="5"/>
       <c r="H267" s="5"/>
@@ -9075,23 +9075,21 @@
     </row>
     <row r="268" customHeight="1" ht="20">
       <c r="A268" s="5" t="n">
-        <v>1461</v>
+        <v>1821</v>
       </c>
       <c r="B268" s="5" t="n">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>662</v>
+        <v>1022</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="F268" s="5" t="n">
-        <v>625</v>
-      </c>
+        <v>1563</v>
+      </c>
+      <c r="F268" s="5"/>
       <c r="G268" s="5"/>
       <c r="H268" s="5"/>
       <c r="I268" s="5"/>
@@ -9109,21 +9107,23 @@
     </row>
     <row r="269" customHeight="1" ht="20">
       <c r="A269" s="5" t="n">
-        <v>1821</v>
+        <v>1581</v>
       </c>
       <c r="B269" s="5" t="n">
-        <v>101</v>
+        <v>321</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>1022</v>
+        <v>862</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F269" s="5"/>
+        <v>261</v>
+      </c>
+      <c r="F269" s="5" t="n">
+        <v>623</v>
+      </c>
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
@@ -9141,23 +9141,21 @@
     </row>
     <row r="270" customHeight="1" ht="20">
       <c r="A270" s="5" t="n">
-        <v>1581</v>
+        <v>1643</v>
       </c>
       <c r="B270" s="5" t="n">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>862</v>
+        <v>942</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="F270" s="5" t="n">
-        <v>623</v>
-      </c>
+        <v>1946</v>
+      </c>
+      <c r="F270" s="5"/>
       <c r="G270" s="5"/>
       <c r="H270" s="5"/>
       <c r="I270" s="5"/>
@@ -9175,7 +9173,7 @@
     </row>
     <row r="271" customHeight="1" ht="20">
       <c r="A271" s="5" t="n">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B271" s="5" t="n">
         <v>26</v>
@@ -9187,7 +9185,7 @@
         <v>2</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="F271" s="5"/>
       <c r="G271" s="5"/>
@@ -9207,19 +9205,19 @@
     </row>
     <row r="272" customHeight="1" ht="20">
       <c r="A272" s="5" t="n">
-        <v>1645</v>
+        <v>1685</v>
       </c>
       <c r="B272" s="5" t="n">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>942</v>
+        <v>982</v>
       </c>
       <c r="D272" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>1943</v>
+        <v>763</v>
       </c>
       <c r="F272" s="5"/>
       <c r="G272" s="5"/>
@@ -9239,19 +9237,19 @@
     </row>
     <row r="273" customHeight="1" ht="20">
       <c r="A273" s="5" t="n">
-        <v>1685</v>
+        <v>1844</v>
       </c>
       <c r="B273" s="5" t="n">
-        <v>401</v>
+        <v>281</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>982</v>
+        <v>822</v>
       </c>
       <c r="D273" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>763</v>
+        <v>2085</v>
       </c>
       <c r="F273" s="5"/>
       <c r="G273" s="5"/>
@@ -9271,21 +9269,23 @@
     </row>
     <row r="274" customHeight="1" ht="20">
       <c r="A274" s="5" t="n">
-        <v>1844</v>
+        <v>1902</v>
       </c>
       <c r="B274" s="5" t="n">
-        <v>281</v>
+        <v>50</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>822</v>
+        <v>1042</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>2085</v>
-      </c>
-      <c r="F274" s="5"/>
+        <v>1864</v>
+      </c>
+      <c r="F274" s="5" t="n">
+        <v>1863</v>
+      </c>
       <c r="G274" s="5"/>
       <c r="H274" s="5"/>
       <c r="I274" s="5"/>
@@ -9303,23 +9303,21 @@
     </row>
     <row r="275" customHeight="1" ht="20">
       <c r="A275" s="5" t="n">
-        <v>1902</v>
+        <v>2044</v>
       </c>
       <c r="B275" s="5" t="n">
-        <v>50</v>
+        <v>301</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>1042</v>
+        <v>1122</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>1864</v>
-      </c>
-      <c r="F275" s="5" t="n">
-        <v>1863</v>
-      </c>
+        <v>2267</v>
+      </c>
+      <c r="F275" s="5"/>
       <c r="G275" s="5"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5"/>
@@ -9337,21 +9335,23 @@
     </row>
     <row r="276" customHeight="1" ht="20">
       <c r="A276" s="5" t="n">
-        <v>2044</v>
+        <v>2121</v>
       </c>
       <c r="B276" s="5" t="n">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>1122</v>
+        <v>1162</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>2267</v>
-      </c>
-      <c r="F276" s="5"/>
+        <v>2283</v>
+      </c>
+      <c r="F276" s="5" t="n">
+        <v>2284</v>
+      </c>
       <c r="G276" s="5"/>
       <c r="H276" s="5"/>
       <c r="I276" s="5"/>
@@ -9369,23 +9369,21 @@
     </row>
     <row r="277" customHeight="1" ht="20">
       <c r="A277" s="5" t="n">
-        <v>2121</v>
+        <v>2142</v>
       </c>
       <c r="B277" s="5" t="n">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>1162</v>
+        <v>1182</v>
       </c>
       <c r="D277" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>2283</v>
-      </c>
-      <c r="F277" s="5" t="n">
-        <v>2284</v>
-      </c>
+        <v>1150</v>
+      </c>
+      <c r="F277" s="5"/>
       <c r="G277" s="5"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
@@ -9403,7 +9401,7 @@
     </row>
     <row r="278" customHeight="1" ht="20">
       <c r="A278" s="5" t="n">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B278" s="5" t="n">
         <v>441</v>
@@ -9412,12 +9410,14 @@
         <v>1182</v>
       </c>
       <c r="D278" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>1150</v>
-      </c>
-      <c r="F278" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G278" s="5"/>
       <c r="H278" s="5"/>
       <c r="I278" s="5"/>
@@ -9435,22 +9435,22 @@
     </row>
     <row r="279" customHeight="1" ht="20">
       <c r="A279" s="5" t="n">
-        <v>2143</v>
+        <v>3041</v>
       </c>
       <c r="B279" s="5" t="n">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>1182</v>
+        <v>1322</v>
       </c>
       <c r="D279" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>585</v>
+        <v>2863</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>584</v>
+        <v>2823</v>
       </c>
       <c r="G279" s="5"/>
       <c r="H279" s="5"/>
@@ -9469,7 +9469,7 @@
     </row>
     <row r="280" customHeight="1" ht="20">
       <c r="A280" s="5" t="n">
-        <v>3041</v>
+        <v>3061</v>
       </c>
       <c r="B280" s="5" t="n">
         <v>501</v>
@@ -9481,10 +9481,10 @@
         <v>1</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>2863</v>
+        <v>24</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>2823</v>
+        <v>22</v>
       </c>
       <c r="G280" s="5"/>
       <c r="H280" s="5"/>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="281" customHeight="1" ht="20">
       <c r="A281" s="5" t="n">
-        <v>3061</v>
+        <v>2301</v>
       </c>
       <c r="B281" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D281" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="F281" s="5" t="n">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="G281" s="5"/>
       <c r="H281" s="5"/>
@@ -9537,7 +9537,7 @@
     </row>
     <row r="282" customHeight="1" ht="20">
       <c r="A282" s="5" t="n">
-        <v>2301</v>
+        <v>2321</v>
       </c>
       <c r="B282" s="5" t="n">
         <v>461</v>
@@ -9549,10 +9549,10 @@
         <v>1</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>142</v>
+        <v>585</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>141</v>
+        <v>584</v>
       </c>
       <c r="G282" s="5"/>
       <c r="H282" s="5"/>
@@ -9571,7 +9571,7 @@
     </row>
     <row r="283" customHeight="1" ht="20">
       <c r="A283" s="5" t="n">
-        <v>2321</v>
+        <v>2363</v>
       </c>
       <c r="B283" s="5" t="n">
         <v>461</v>
@@ -9580,14 +9580,12 @@
         <v>1222</v>
       </c>
       <c r="D283" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F283" s="5" t="n">
-        <v>584</v>
-      </c>
+        <v>963</v>
+      </c>
+      <c r="F283" s="5"/>
       <c r="G283" s="5"/>
       <c r="H283" s="5"/>
       <c r="I283" s="5"/>
@@ -9605,21 +9603,23 @@
     </row>
     <row r="284" customHeight="1" ht="20">
       <c r="A284" s="5" t="n">
-        <v>2363</v>
+        <v>3141</v>
       </c>
       <c r="B284" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D284" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>963</v>
-      </c>
-      <c r="F284" s="5"/>
+        <v>687</v>
+      </c>
+      <c r="F284" s="5" t="n">
+        <v>688</v>
+      </c>
       <c r="G284" s="5"/>
       <c r="H284" s="5"/>
       <c r="I284" s="5"/>
@@ -9637,22 +9637,22 @@
     </row>
     <row r="285" customHeight="1" ht="20">
       <c r="A285" s="5" t="n">
-        <v>3141</v>
+        <v>2442</v>
       </c>
       <c r="B285" s="5" t="n">
-        <v>501</v>
+        <v>261</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>1322</v>
+        <v>1202</v>
       </c>
       <c r="D285" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E285" s="5" t="n">
-        <v>687</v>
+        <v>2484</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>688</v>
+        <v>2485</v>
       </c>
       <c r="G285" s="5"/>
       <c r="H285" s="5"/>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="286" customHeight="1" ht="20">
       <c r="A286" s="5" t="n">
-        <v>2442</v>
+        <v>2503</v>
       </c>
       <c r="B286" s="5" t="n">
         <v>261</v>
@@ -9680,13 +9680,13 @@
         <v>1202</v>
       </c>
       <c r="D286" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>2484</v>
+        <v>2525</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>2485</v>
+        <v>2524</v>
       </c>
       <c r="G286" s="5"/>
       <c r="H286" s="5"/>
@@ -9705,22 +9705,22 @@
     </row>
     <row r="287" customHeight="1" ht="20">
       <c r="A287" s="5" t="n">
-        <v>2503</v>
+        <v>2581</v>
       </c>
       <c r="B287" s="5" t="n">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>1202</v>
+        <v>1342</v>
       </c>
       <c r="D287" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>2525</v>
+        <v>2584</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>2524</v>
+        <v>2583</v>
       </c>
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
@@ -9739,22 +9739,22 @@
     </row>
     <row r="288" customHeight="1" ht="20">
       <c r="A288" s="5" t="n">
-        <v>2581</v>
+        <v>2701</v>
       </c>
       <c r="B288" s="5" t="n">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>1342</v>
+        <v>1262</v>
       </c>
       <c r="D288" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>2584</v>
+        <v>221</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>2583</v>
+        <v>1131</v>
       </c>
       <c r="G288" s="5"/>
       <c r="H288" s="5"/>
@@ -9773,22 +9773,22 @@
     </row>
     <row r="289" customHeight="1" ht="20">
       <c r="A289" s="5" t="n">
-        <v>2701</v>
+        <v>2761</v>
       </c>
       <c r="B289" s="5" t="n">
-        <v>181</v>
+        <v>461</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>1262</v>
+        <v>1302</v>
       </c>
       <c r="D289" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E289" s="5" t="n">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="F289" s="5" t="n">
-        <v>1131</v>
+        <v>2683</v>
       </c>
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
@@ -9807,22 +9807,22 @@
     </row>
     <row r="290" customHeight="1" ht="20">
       <c r="A290" s="5" t="n">
-        <v>2761</v>
+        <v>2921</v>
       </c>
       <c r="B290" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>1302</v>
+        <v>1322</v>
       </c>
       <c r="D290" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>81</v>
+        <v>2803</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>2683</v>
+        <v>2804</v>
       </c>
       <c r="G290" s="5"/>
       <c r="H290" s="5"/>
@@ -9841,22 +9841,22 @@
     </row>
     <row r="291" customHeight="1" ht="20">
       <c r="A291" s="5" t="n">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="B291" s="5" t="n">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>1322</v>
+        <v>1423</v>
       </c>
       <c r="D291" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>2803</v>
+        <v>1303</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>2804</v>
+        <v>1147</v>
       </c>
       <c r="G291" s="5"/>
       <c r="H291" s="5"/>
@@ -9875,7 +9875,7 @@
     </row>
     <row r="292" customHeight="1" ht="20">
       <c r="A292" s="5" t="n">
-        <v>2922</v>
+        <v>2924</v>
       </c>
       <c r="B292" s="5" t="n">
         <v>521</v>
@@ -9887,10 +9887,10 @@
         <v>1</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>1303</v>
+        <v>24</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>1147</v>
+        <v>22</v>
       </c>
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
@@ -9909,7 +9909,7 @@
     </row>
     <row r="293" customHeight="1" ht="20">
       <c r="A293" s="5" t="n">
-        <v>2924</v>
+        <v>2983</v>
       </c>
       <c r="B293" s="5" t="n">
         <v>521</v>
@@ -9921,10 +9921,10 @@
         <v>1</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>24</v>
+        <v>2846</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>22</v>
+        <v>2845</v>
       </c>
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
@@ -9943,22 +9943,22 @@
     </row>
     <row r="294" customHeight="1" ht="20">
       <c r="A294" s="5" t="n">
-        <v>2983</v>
+        <v>3181</v>
       </c>
       <c r="B294" s="5" t="n">
-        <v>521</v>
+        <v>481</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>1423</v>
+        <v>1282</v>
       </c>
       <c r="D294" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>2846</v>
+        <v>2164</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>2845</v>
+        <v>2163</v>
       </c>
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
@@ -9977,22 +9977,22 @@
     </row>
     <row r="295" customHeight="1" ht="20">
       <c r="A295" s="5" t="n">
-        <v>3181</v>
+        <v>3221</v>
       </c>
       <c r="B295" s="5" t="n">
-        <v>481</v>
+        <v>41</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>1282</v>
+        <v>1403</v>
       </c>
       <c r="D295" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>2164</v>
+        <v>2003</v>
       </c>
       <c r="F295" s="5" t="n">
-        <v>2163</v>
+        <v>2004</v>
       </c>
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
@@ -10011,22 +10011,22 @@
     </row>
     <row r="296" customHeight="1" ht="20">
       <c r="A296" s="5" t="n">
-        <v>3221</v>
+        <v>3261</v>
       </c>
       <c r="B296" s="5" t="n">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>1403</v>
+        <v>1444</v>
       </c>
       <c r="D296" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>2003</v>
+        <v>2944</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>2004</v>
+        <v>2943</v>
       </c>
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
@@ -10045,23 +10045,21 @@
     </row>
     <row r="297" customHeight="1" ht="20">
       <c r="A297" s="5" t="n">
-        <v>3261</v>
+        <v>3301</v>
       </c>
       <c r="B297" s="5" t="n">
-        <v>321</v>
+        <v>461</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>1444</v>
+        <v>1483</v>
       </c>
       <c r="D297" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>2944</v>
-      </c>
-      <c r="F297" s="5" t="n">
-        <v>2943</v>
-      </c>
+        <v>2643</v>
+      </c>
+      <c r="F297" s="5"/>
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5"/>
@@ -10079,39 +10077,41 @@
     </row>
     <row r="298" customHeight="1" ht="20">
       <c r="A298" s="5" t="n">
-        <v>3301</v>
+        <v>3403</v>
       </c>
       <c r="B298" s="5" t="n">
-        <v>461</v>
+        <v>541</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>1483</v>
+        <v>1503</v>
       </c>
       <c r="D298" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>2643</v>
-      </c>
-      <c r="F298" s="5"/>
+        <v>3024</v>
+      </c>
+      <c r="F298" s="5" t="n">
+        <v>3025</v>
+      </c>
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
       <c r="I298" s="5"/>
       <c r="J298" s="5"/>
       <c r="K298" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L298" s="7"/>
       <c r="M298" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N298" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="299" customHeight="1" ht="20">
       <c r="A299" s="5" t="n">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="B299" s="5" t="n">
         <v>541</v>
@@ -10123,10 +10123,10 @@
         <v>1</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>3024</v>
+        <v>3026</v>
       </c>
       <c r="F299" s="5" t="n">
-        <v>3025</v>
+        <v>3027</v>
       </c>
       <c r="G299" s="5"/>
       <c r="H299" s="5"/>
@@ -10145,7 +10145,7 @@
     </row>
     <row r="300" customHeight="1" ht="20">
       <c r="A300" s="5" t="n">
-        <v>3404</v>
+        <v>3422</v>
       </c>
       <c r="B300" s="5" t="n">
         <v>541</v>
@@ -10154,14 +10154,12 @@
         <v>1503</v>
       </c>
       <c r="D300" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>3026</v>
-      </c>
-      <c r="F300" s="5" t="n">
-        <v>3027</v>
-      </c>
+        <v>3065</v>
+      </c>
+      <c r="F300" s="5"/>
       <c r="G300" s="5"/>
       <c r="H300" s="5"/>
       <c r="I300" s="5"/>
@@ -10179,7 +10177,7 @@
     </row>
     <row r="301" customHeight="1" ht="20">
       <c r="A301" s="5" t="n">
-        <v>3422</v>
+        <v>3424</v>
       </c>
       <c r="B301" s="5" t="n">
         <v>541</v>
@@ -10188,12 +10186,14 @@
         <v>1503</v>
       </c>
       <c r="D301" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>3065</v>
-      </c>
-      <c r="F301" s="5"/>
+        <v>3068</v>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>3069</v>
+      </c>
       <c r="G301" s="5"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5"/>
@@ -10211,7 +10211,7 @@
     </row>
     <row r="302" customHeight="1" ht="20">
       <c r="A302" s="5" t="n">
-        <v>3424</v>
+        <v>3427</v>
       </c>
       <c r="B302" s="5" t="n">
         <v>541</v>
@@ -10223,10 +10223,10 @@
         <v>1</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>3068</v>
+        <v>2583</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>3069</v>
+        <v>2584</v>
       </c>
       <c r="G302" s="5"/>
       <c r="H302" s="5"/>
@@ -10245,7 +10245,7 @@
     </row>
     <row r="303" customHeight="1" ht="20">
       <c r="A303" s="5" t="n">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="B303" s="5" t="n">
         <v>541</v>
@@ -10254,14 +10254,12 @@
         <v>1503</v>
       </c>
       <c r="D303" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>2583</v>
-      </c>
-      <c r="F303" s="5" t="n">
-        <v>2584</v>
-      </c>
+        <v>3071</v>
+      </c>
+      <c r="F303" s="5"/>
       <c r="G303" s="5"/>
       <c r="H303" s="5"/>
       <c r="I303" s="5"/>
@@ -10279,19 +10277,19 @@
     </row>
     <row r="304" customHeight="1" ht="20">
       <c r="A304" s="5" t="n">
-        <v>3428</v>
+        <v>3761</v>
       </c>
       <c r="B304" s="5" t="n">
-        <v>541</v>
+        <v>681</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>1503</v>
+        <v>1647</v>
       </c>
       <c r="D304" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>3071</v>
+        <v>3403</v>
       </c>
       <c r="F304" s="5"/>
       <c r="G304" s="5"/>
@@ -10301,17 +10299,15 @@
       <c r="K304" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L304" s="7"/>
-      <c r="M304" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N304" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L304" s="7" t="n">
+        <v>45859.6980671296</v>
+      </c>
+      <c r="M304" s="6"/>
+      <c r="N304" s="7"/>
     </row>
     <row r="305" customHeight="1" ht="20">
       <c r="A305" s="5" t="n">
-        <v>3761</v>
+        <v>3841</v>
       </c>
       <c r="B305" s="5" t="n">
         <v>681</v>
@@ -10320,10 +10316,10 @@
         <v>1647</v>
       </c>
       <c r="D305" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>3403</v>
+        <v>3463</v>
       </c>
       <c r="F305" s="5"/>
       <c r="G305" s="5"/>
@@ -10334,28 +10330,30 @@
         <v>15</v>
       </c>
       <c r="L305" s="7" t="n">
-        <v>45859.6980671296</v>
+        <v>45895.3855324074</v>
       </c>
       <c r="M305" s="6"/>
       <c r="N305" s="7"/>
     </row>
     <row r="306" customHeight="1" ht="20">
       <c r="A306" s="5" t="n">
-        <v>3841</v>
+        <v>3901</v>
       </c>
       <c r="B306" s="5" t="n">
-        <v>681</v>
+        <v>722</v>
       </c>
       <c r="C306" s="5" t="n">
-        <v>1647</v>
+        <v>1684</v>
       </c>
       <c r="D306" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>3463</v>
-      </c>
-      <c r="F306" s="5"/>
+        <v>3523</v>
+      </c>
+      <c r="F306" s="5" t="n">
+        <v>3524</v>
+      </c>
       <c r="G306" s="5"/>
       <c r="H306" s="5"/>
       <c r="I306" s="5"/>
@@ -10364,29 +10362,29 @@
         <v>15</v>
       </c>
       <c r="L306" s="7" t="n">
-        <v>45895.3855324074</v>
+        <v>45911.2688078704</v>
       </c>
       <c r="M306" s="6"/>
       <c r="N306" s="7"/>
     </row>
     <row r="307" customHeight="1" ht="20">
       <c r="A307" s="5" t="n">
-        <v>3901</v>
+        <v>3902</v>
       </c>
       <c r="B307" s="5" t="n">
-        <v>722</v>
+        <v>621</v>
       </c>
       <c r="C307" s="5" t="n">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D307" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>3523</v>
+        <v>3526</v>
       </c>
       <c r="F307" s="5" t="n">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="G307" s="5"/>
       <c r="H307" s="5"/>
@@ -10396,14 +10394,14 @@
         <v>15</v>
       </c>
       <c r="L307" s="7" t="n">
-        <v>45911.2688078704</v>
+        <v>45911.4241203704</v>
       </c>
       <c r="M307" s="6"/>
       <c r="N307" s="7"/>
     </row>
     <row r="308" customHeight="1" ht="20">
       <c r="A308" s="5" t="n">
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="B308" s="5" t="n">
         <v>621</v>
@@ -10415,10 +10413,10 @@
         <v>1</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>3526</v>
+        <v>3531</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>3525</v>
+        <v>3530</v>
       </c>
       <c r="G308" s="5"/>
       <c r="H308" s="5"/>
@@ -10428,30 +10426,28 @@
         <v>15</v>
       </c>
       <c r="L308" s="7" t="n">
-        <v>45911.4241203704</v>
+        <v>45911.6326967593</v>
       </c>
       <c r="M308" s="6"/>
       <c r="N308" s="7"/>
     </row>
     <row r="309" customHeight="1" ht="20">
       <c r="A309" s="5" t="n">
-        <v>3903</v>
+        <v>4284</v>
       </c>
       <c r="B309" s="5" t="n">
-        <v>621</v>
+        <v>801</v>
       </c>
       <c r="C309" s="5" t="n">
-        <v>1683</v>
+        <v>1763</v>
       </c>
       <c r="D309" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>3531</v>
-      </c>
-      <c r="F309" s="5" t="n">
-        <v>3530</v>
-      </c>
+        <v>3810</v>
+      </c>
+      <c r="F309" s="5"/>
       <c r="G309" s="5"/>
       <c r="H309" s="5"/>
       <c r="I309" s="5"/>
@@ -10460,76 +10456,78 @@
         <v>15</v>
       </c>
       <c r="L309" s="7" t="n">
-        <v>45911.6326967593</v>
+        <v>46012.2927083333</v>
       </c>
       <c r="M309" s="6"/>
       <c r="N309" s="7"/>
     </row>
     <row r="310" customHeight="1" ht="20">
       <c r="A310" s="5" t="n">
-        <v>4284</v>
+        <v>4022</v>
       </c>
       <c r="B310" s="5" t="n">
-        <v>801</v>
+        <v>621</v>
       </c>
       <c r="C310" s="5" t="n">
-        <v>1763</v>
+        <v>1683</v>
       </c>
       <c r="D310" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>3810</v>
-      </c>
-      <c r="F310" s="5"/>
+        <v>3543</v>
+      </c>
+      <c r="F310" s="5" t="n">
+        <v>3563</v>
+      </c>
       <c r="G310" s="5"/>
       <c r="H310" s="5"/>
       <c r="I310" s="5"/>
       <c r="J310" s="5"/>
       <c r="K310" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L310" s="7" t="n">
-        <v>46012.2927083333</v>
+        <v>45947.2722222222</v>
       </c>
       <c r="M310" s="6"/>
       <c r="N310" s="7"/>
     </row>
     <row r="311" customHeight="1" ht="20">
       <c r="A311" s="5" t="n">
-        <v>4022</v>
+        <v>4067</v>
       </c>
       <c r="B311" s="5" t="n">
-        <v>621</v>
+        <v>781</v>
       </c>
       <c r="C311" s="5" t="n">
-        <v>1683</v>
+        <v>1743</v>
       </c>
       <c r="D311" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>3543</v>
+        <v>3673</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>3563</v>
+        <v>3674</v>
       </c>
       <c r="G311" s="5"/>
       <c r="H311" s="5"/>
       <c r="I311" s="5"/>
       <c r="J311" s="5"/>
       <c r="K311" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L311" s="7" t="n">
-        <v>45947.2722222222</v>
+        <v>45966.7240046296</v>
       </c>
       <c r="M311" s="6"/>
       <c r="N311" s="7"/>
     </row>
     <row r="312" customHeight="1" ht="20">
       <c r="A312" s="5" t="n">
-        <v>4067</v>
+        <v>4071</v>
       </c>
       <c r="B312" s="5" t="n">
         <v>781</v>
@@ -10541,10 +10539,10 @@
         <v>1</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>3673</v>
+        <v>33</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>3674</v>
+        <v>3680</v>
       </c>
       <c r="G312" s="5"/>
       <c r="H312" s="5"/>
@@ -10554,29 +10552,29 @@
         <v>15</v>
       </c>
       <c r="L312" s="7" t="n">
-        <v>45966.7240046296</v>
+        <v>45967.679375</v>
       </c>
       <c r="M312" s="6"/>
       <c r="N312" s="7"/>
     </row>
     <row r="313" customHeight="1" ht="20">
       <c r="A313" s="5" t="n">
-        <v>4071</v>
+        <v>4141</v>
       </c>
       <c r="B313" s="5" t="n">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="C313" s="5" t="n">
-        <v>1743</v>
+        <v>1763</v>
       </c>
       <c r="D313" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>33</v>
+        <v>3732</v>
       </c>
       <c r="F313" s="5" t="n">
-        <v>3680</v>
+        <v>3731</v>
       </c>
       <c r="G313" s="5"/>
       <c r="H313" s="5"/>
@@ -10586,29 +10584,29 @@
         <v>15</v>
       </c>
       <c r="L313" s="7" t="n">
-        <v>45967.679375</v>
+        <v>45985.7560185185</v>
       </c>
       <c r="M313" s="6"/>
       <c r="N313" s="7"/>
     </row>
     <row r="314" customHeight="1" ht="20">
       <c r="A314" s="5" t="n">
-        <v>4141</v>
+        <v>4142</v>
       </c>
       <c r="B314" s="5" t="n">
-        <v>801</v>
+        <v>722</v>
       </c>
       <c r="C314" s="5" t="n">
-        <v>1763</v>
+        <v>1684</v>
       </c>
       <c r="D314" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>3732</v>
+        <v>3736</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>3731</v>
+        <v>3733</v>
       </c>
       <c r="G314" s="5"/>
       <c r="H314" s="5"/>
@@ -10618,30 +10616,28 @@
         <v>15</v>
       </c>
       <c r="L314" s="7" t="n">
-        <v>45985.7560185185</v>
+        <v>45986.6275578704</v>
       </c>
       <c r="M314" s="6"/>
       <c r="N314" s="7"/>
     </row>
     <row r="315" customHeight="1" ht="20">
       <c r="A315" s="5" t="n">
-        <v>4142</v>
+        <v>4281</v>
       </c>
       <c r="B315" s="5" t="n">
-        <v>722</v>
+        <v>822</v>
       </c>
       <c r="C315" s="5" t="n">
-        <v>1684</v>
+        <v>1784</v>
       </c>
       <c r="D315" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>3736</v>
-      </c>
-      <c r="F315" s="5" t="n">
-        <v>3733</v>
-      </c>
+        <v>3843</v>
+      </c>
+      <c r="F315" s="5"/>
       <c r="G315" s="5"/>
       <c r="H315" s="5"/>
       <c r="I315" s="5"/>
@@ -10650,28 +10646,30 @@
         <v>15</v>
       </c>
       <c r="L315" s="7" t="n">
-        <v>45986.6275578704</v>
+        <v>46011.5137962963</v>
       </c>
       <c r="M315" s="6"/>
       <c r="N315" s="7"/>
     </row>
     <row r="316" customHeight="1" ht="20">
       <c r="A316" s="5" t="n">
-        <v>4281</v>
+        <v>4301</v>
       </c>
       <c r="B316" s="5" t="n">
-        <v>822</v>
+        <v>762</v>
       </c>
       <c r="C316" s="5" t="n">
-        <v>1784</v>
+        <v>1724</v>
       </c>
       <c r="D316" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>3843</v>
-      </c>
-      <c r="F316" s="5"/>
+        <v>3864</v>
+      </c>
+      <c r="F316" s="5" t="n">
+        <v>3865</v>
+      </c>
       <c r="G316" s="5"/>
       <c r="H316" s="5"/>
       <c r="I316" s="5"/>
@@ -10680,14 +10678,14 @@
         <v>15</v>
       </c>
       <c r="L316" s="7" t="n">
-        <v>46011.5137962963</v>
+        <v>46014.5824189815</v>
       </c>
       <c r="M316" s="6"/>
       <c r="N316" s="7"/>
     </row>
     <row r="317" customHeight="1" ht="20">
       <c r="A317" s="5" t="n">
-        <v>4301</v>
+        <v>4302</v>
       </c>
       <c r="B317" s="5" t="n">
         <v>762</v>
@@ -10696,13 +10694,13 @@
         <v>1724</v>
       </c>
       <c r="D317" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>3864</v>
+        <v>3866</v>
       </c>
       <c r="F317" s="5" t="n">
-        <v>3865</v>
+        <v>3867</v>
       </c>
       <c r="G317" s="5"/>
       <c r="H317" s="5"/>
@@ -10712,61 +10710,63 @@
         <v>15</v>
       </c>
       <c r="L317" s="7" t="n">
-        <v>46014.5824189815</v>
+        <v>46014.7677199074</v>
       </c>
       <c r="M317" s="6"/>
       <c r="N317" s="7"/>
     </row>
     <row r="318" customHeight="1" ht="20">
       <c r="A318" s="5" t="n">
-        <v>4302</v>
+        <v>43</v>
       </c>
       <c r="B318" s="5" t="n">
-        <v>762</v>
+        <v>1</v>
       </c>
       <c r="C318" s="5" t="n">
-        <v>1724</v>
+        <v>182</v>
       </c>
       <c r="D318" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>3866</v>
+        <v>525</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>3867</v>
+        <v>526</v>
       </c>
       <c r="G318" s="5"/>
       <c r="H318" s="5"/>
       <c r="I318" s="5"/>
       <c r="J318" s="5"/>
       <c r="K318" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L318" s="7" t="n">
-        <v>46014.7677199074</v>
-      </c>
-      <c r="M318" s="6"/>
-      <c r="N318" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L318" s="7"/>
+      <c r="M318" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N318" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="319" customHeight="1" ht="20">
       <c r="A319" s="5" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B319" s="5" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C319" s="5" t="n">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="D319" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>525</v>
+        <v>627</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>526</v>
+        <v>626</v>
       </c>
       <c r="G319" s="5"/>
       <c r="H319" s="5"/>
@@ -10785,22 +10785,22 @@
     </row>
     <row r="320" customHeight="1" ht="20">
       <c r="A320" s="5" t="n">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="B320" s="5" t="n">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="C320" s="5" t="n">
-        <v>262</v>
+        <v>342</v>
       </c>
       <c r="D320" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>627</v>
+        <v>713</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>626</v>
+        <v>712</v>
       </c>
       <c r="G320" s="5"/>
       <c r="H320" s="5"/>
@@ -10819,22 +10819,22 @@
     </row>
     <row r="321" customHeight="1" ht="20">
       <c r="A321" s="5" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B321" s="5" t="n">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="C321" s="5" t="n">
-        <v>342</v>
+        <v>262</v>
       </c>
       <c r="D321" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>713</v>
+        <v>726</v>
       </c>
       <c r="F321" s="5" t="n">
-        <v>712</v>
+        <v>381</v>
       </c>
       <c r="G321" s="5"/>
       <c r="H321" s="5"/>
@@ -10853,22 +10853,22 @@
     </row>
     <row r="322" customHeight="1" ht="20">
       <c r="A322" s="5" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B322" s="5" t="n">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="C322" s="5" t="n">
-        <v>262</v>
+        <v>342</v>
       </c>
       <c r="D322" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>381</v>
+        <v>729</v>
       </c>
       <c r="G322" s="5"/>
       <c r="H322" s="5"/>
@@ -10887,22 +10887,22 @@
     </row>
     <row r="323" customHeight="1" ht="20">
       <c r="A323" s="5" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B323" s="5" t="n">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="C323" s="5" t="n">
-        <v>342</v>
+        <v>262</v>
       </c>
       <c r="D323" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="F323" s="5" t="n">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="G323" s="5"/>
       <c r="H323" s="5"/>
@@ -10921,23 +10921,21 @@
     </row>
     <row r="324" customHeight="1" ht="20">
       <c r="A324" s="5" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B324" s="5" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="C324" s="5" t="n">
+        <v>322</v>
+      </c>
+      <c r="D324" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E324" s="5" t="n">
         <v>262</v>
       </c>
-      <c r="D324" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E324" s="5" t="n">
-        <v>723</v>
-      </c>
-      <c r="F324" s="5" t="n">
-        <v>724</v>
-      </c>
+      <c r="F324" s="5"/>
       <c r="G324" s="5"/>
       <c r="H324" s="5"/>
       <c r="I324" s="5"/>
@@ -10955,21 +10953,23 @@
     </row>
     <row r="325" customHeight="1" ht="20">
       <c r="A325" s="5" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B325" s="5" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C325" s="5" t="n">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="D325" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E325" s="5" t="n">
-        <v>262</v>
-      </c>
-      <c r="F325" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="F325" s="5" t="n">
+        <v>24</v>
+      </c>
       <c r="G325" s="5"/>
       <c r="H325" s="5"/>
       <c r="I325" s="5"/>
@@ -10987,7 +10987,7 @@
     </row>
     <row r="326" customHeight="1" ht="20">
       <c r="A326" s="5" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B326" s="5" t="n">
         <v>22</v>
@@ -10996,14 +10996,12 @@
         <v>382</v>
       </c>
       <c r="D326" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F326" s="5" t="n">
-        <v>24</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="F326" s="5"/>
       <c r="G326" s="5"/>
       <c r="H326" s="5"/>
       <c r="I326" s="5"/>
@@ -11021,21 +11019,23 @@
     </row>
     <row r="327" customHeight="1" ht="20">
       <c r="A327" s="5" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B327" s="5" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C327" s="5" t="n">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="D327" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>743</v>
-      </c>
-      <c r="F327" s="5"/>
+        <v>771</v>
+      </c>
+      <c r="F327" s="5" t="n">
+        <v>770</v>
+      </c>
       <c r="G327" s="5"/>
       <c r="H327" s="5"/>
       <c r="I327" s="5"/>
@@ -11053,22 +11053,22 @@
     </row>
     <row r="328" customHeight="1" ht="20">
       <c r="A328" s="5" t="n">
-        <v>193</v>
+        <v>823</v>
       </c>
       <c r="B328" s="5" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="C328" s="5" t="n">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="D328" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>771</v>
+        <v>1353</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>770</v>
+        <v>1354</v>
       </c>
       <c r="G328" s="5"/>
       <c r="H328" s="5"/>
@@ -11087,22 +11087,22 @@
     </row>
     <row r="329" customHeight="1" ht="20">
       <c r="A329" s="5" t="n">
-        <v>823</v>
+        <v>561</v>
       </c>
       <c r="B329" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C329" s="5" t="n">
-        <v>262</v>
+        <v>402</v>
       </c>
       <c r="D329" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>1353</v>
+        <v>1000</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>1354</v>
+        <v>999</v>
       </c>
       <c r="G329" s="5"/>
       <c r="H329" s="5"/>
@@ -11121,22 +11121,22 @@
     </row>
     <row r="330" customHeight="1" ht="20">
       <c r="A330" s="5" t="n">
-        <v>561</v>
+        <v>227</v>
       </c>
       <c r="B330" s="5" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C330" s="5" t="n">
-        <v>402</v>
+        <v>363</v>
       </c>
       <c r="D330" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>1000</v>
+        <v>624</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>999</v>
+        <v>625</v>
       </c>
       <c r="G330" s="5"/>
       <c r="H330" s="5"/>
@@ -11155,22 +11155,22 @@
     </row>
     <row r="331" customHeight="1" ht="20">
       <c r="A331" s="5" t="n">
-        <v>227</v>
+        <v>601</v>
       </c>
       <c r="B331" s="5" t="n">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="C331" s="5" t="n">
-        <v>363</v>
+        <v>262</v>
       </c>
       <c r="D331" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>624</v>
+        <v>1264</v>
       </c>
       <c r="F331" s="5" t="n">
-        <v>625</v>
+        <v>1063</v>
       </c>
       <c r="G331" s="5"/>
       <c r="H331" s="5"/>
@@ -11189,22 +11189,22 @@
     </row>
     <row r="332" customHeight="1" ht="20">
       <c r="A332" s="5" t="n">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="B332" s="5" t="n">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="C332" s="5" t="n">
-        <v>262</v>
+        <v>502</v>
       </c>
       <c r="D332" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>1264</v>
+        <v>585</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>1063</v>
+        <v>584</v>
       </c>
       <c r="G332" s="5"/>
       <c r="H332" s="5"/>
@@ -11223,7 +11223,7 @@
     </row>
     <row r="333" customHeight="1" ht="20">
       <c r="A333" s="5" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B333" s="5" t="n">
         <v>181</v>
@@ -11235,10 +11235,10 @@
         <v>1</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>585</v>
+        <v>726</v>
       </c>
       <c r="F333" s="5" t="n">
-        <v>584</v>
+        <v>381</v>
       </c>
       <c r="G333" s="5"/>
       <c r="H333" s="5"/>
@@ -11257,22 +11257,22 @@
     </row>
     <row r="334" customHeight="1" ht="20">
       <c r="A334" s="5" t="n">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="B334" s="5" t="n">
-        <v>181</v>
+        <v>48</v>
       </c>
       <c r="C334" s="5" t="n">
-        <v>502</v>
+        <v>422</v>
       </c>
       <c r="D334" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>726</v>
+        <v>24</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>381</v>
+        <v>22</v>
       </c>
       <c r="G334" s="5"/>
       <c r="H334" s="5"/>
@@ -11291,22 +11291,22 @@
     </row>
     <row r="335" customHeight="1" ht="20">
       <c r="A335" s="5" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B335" s="5" t="n">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="C335" s="5" t="n">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="D335" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>24</v>
+        <v>1303</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>22</v>
+        <v>1147</v>
       </c>
       <c r="G335" s="5"/>
       <c r="H335" s="5"/>
@@ -11325,22 +11325,22 @@
     </row>
     <row r="336" customHeight="1" ht="20">
       <c r="A336" s="5" t="n">
-        <v>643</v>
+        <v>701</v>
       </c>
       <c r="B336" s="5" t="n">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C336" s="5" t="n">
-        <v>462</v>
+        <v>402</v>
       </c>
       <c r="D336" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>1303</v>
+        <v>990</v>
       </c>
       <c r="F336" s="5" t="n">
-        <v>1147</v>
+        <v>989</v>
       </c>
       <c r="G336" s="5"/>
       <c r="H336" s="5"/>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="337" customHeight="1" ht="20">
       <c r="A337" s="5" t="n">
-        <v>701</v>
+        <v>742</v>
       </c>
       <c r="B337" s="5" t="n">
         <v>81</v>
@@ -11368,14 +11368,12 @@
         <v>402</v>
       </c>
       <c r="D337" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>990</v>
-      </c>
-      <c r="F337" s="5" t="n">
-        <v>989</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="F337" s="5"/>
       <c r="G337" s="5"/>
       <c r="H337" s="5"/>
       <c r="I337" s="5"/>
@@ -11393,19 +11391,19 @@
     </row>
     <row r="338" customHeight="1" ht="20">
       <c r="A338" s="5" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B338" s="5" t="n">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="C338" s="5" t="n">
-        <v>402</v>
+        <v>502</v>
       </c>
       <c r="D338" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E338" s="5" t="n">
-        <v>523</v>
+        <v>342</v>
       </c>
       <c r="F338" s="5"/>
       <c r="G338" s="5"/>
@@ -11425,7 +11423,7 @@
     </row>
     <row r="339" customHeight="1" ht="20">
       <c r="A339" s="5" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B339" s="5" t="n">
         <v>181</v>
@@ -11434,12 +11432,14 @@
         <v>502</v>
       </c>
       <c r="D339" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E339" s="5" t="n">
-        <v>342</v>
-      </c>
-      <c r="F339" s="5"/>
+        <v>341</v>
+      </c>
+      <c r="F339" s="5" t="n">
+        <v>1405</v>
+      </c>
       <c r="G339" s="5"/>
       <c r="H339" s="5"/>
       <c r="I339" s="5"/>
@@ -11457,24 +11457,26 @@
     </row>
     <row r="340" customHeight="1" ht="20">
       <c r="A340" s="5" t="n">
-        <v>744</v>
+        <v>821</v>
       </c>
       <c r="B340" s="5" t="n">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="C340" s="5" t="n">
-        <v>502</v>
+        <v>262</v>
       </c>
       <c r="D340" s="5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E340" s="5" t="n">
-        <v>341</v>
+        <v>1059</v>
       </c>
       <c r="F340" s="5" t="n">
-        <v>1405</v>
-      </c>
-      <c r="G340" s="5"/>
+        <v>1060</v>
+      </c>
+      <c r="G340" s="5" t="n">
+        <v>1061</v>
+      </c>
       <c r="H340" s="5"/>
       <c r="I340" s="5"/>
       <c r="J340" s="5"/>
@@ -11491,7 +11493,7 @@
     </row>
     <row r="341" customHeight="1" ht="20">
       <c r="A341" s="5" t="n">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B341" s="5" t="n">
         <v>121</v>
@@ -11500,17 +11502,15 @@
         <v>262</v>
       </c>
       <c r="D341" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>1059</v>
+        <v>22</v>
       </c>
       <c r="F341" s="5" t="n">
-        <v>1060</v>
-      </c>
-      <c r="G341" s="5" t="n">
-        <v>1061</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G341" s="5"/>
       <c r="H341" s="5"/>
       <c r="I341" s="5"/>
       <c r="J341" s="5"/>
@@ -11527,23 +11527,21 @@
     </row>
     <row r="342" customHeight="1" ht="20">
       <c r="A342" s="5" t="n">
-        <v>824</v>
+        <v>961</v>
       </c>
       <c r="B342" s="5" t="n">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="C342" s="5" t="n">
-        <v>262</v>
+        <v>602</v>
       </c>
       <c r="D342" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E342" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F342" s="5" t="n">
-        <v>24</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F342" s="5"/>
       <c r="G342" s="5"/>
       <c r="H342" s="5"/>
       <c r="I342" s="5"/>
@@ -11561,19 +11559,19 @@
     </row>
     <row r="343" customHeight="1" ht="20">
       <c r="A343" s="5" t="n">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B343" s="5" t="n">
-        <v>181</v>
+        <v>25</v>
       </c>
       <c r="C343" s="5" t="n">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="D343" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E343" s="5" t="n">
-        <v>26</v>
+        <v>262</v>
       </c>
       <c r="F343" s="5"/>
       <c r="G343" s="5"/>
@@ -11593,19 +11591,19 @@
     </row>
     <row r="344" customHeight="1" ht="20">
       <c r="A344" s="5" t="n">
-        <v>963</v>
+        <v>1061</v>
       </c>
       <c r="B344" s="5" t="n">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="C344" s="5" t="n">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="D344" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E344" s="5" t="n">
-        <v>262</v>
+        <v>26</v>
       </c>
       <c r="F344" s="5"/>
       <c r="G344" s="5"/>
@@ -11625,19 +11623,19 @@
     </row>
     <row r="345" customHeight="1" ht="20">
       <c r="A345" s="5" t="n">
-        <v>1061</v>
+        <v>1082</v>
       </c>
       <c r="B345" s="5" t="n">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="C345" s="5" t="n">
-        <v>642</v>
+        <v>682</v>
       </c>
       <c r="D345" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E345" s="5" t="n">
-        <v>26</v>
+        <v>282</v>
       </c>
       <c r="F345" s="5"/>
       <c r="G345" s="5"/>
@@ -11657,19 +11655,19 @@
     </row>
     <row r="346" customHeight="1" ht="20">
       <c r="A346" s="5" t="n">
-        <v>1082</v>
+        <v>1141</v>
       </c>
       <c r="B346" s="5" t="n">
-        <v>48</v>
+        <v>181</v>
       </c>
       <c r="C346" s="5" t="n">
-        <v>682</v>
+        <v>602</v>
       </c>
       <c r="D346" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>282</v>
+        <v>1563</v>
       </c>
       <c r="F346" s="5"/>
       <c r="G346" s="5"/>
@@ -11689,21 +11687,23 @@
     </row>
     <row r="347" customHeight="1" ht="20">
       <c r="A347" s="5" t="n">
-        <v>1141</v>
+        <v>1264</v>
       </c>
       <c r="B347" s="5" t="n">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="C347" s="5" t="n">
-        <v>602</v>
+        <v>642</v>
       </c>
       <c r="D347" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F347" s="5"/>
+        <v>1383</v>
+      </c>
+      <c r="F347" s="5" t="n">
+        <v>1384</v>
+      </c>
       <c r="G347" s="5"/>
       <c r="H347" s="5"/>
       <c r="I347" s="5"/>
@@ -11721,22 +11721,22 @@
     </row>
     <row r="348" customHeight="1" ht="20">
       <c r="A348" s="5" t="n">
-        <v>1264</v>
+        <v>1201</v>
       </c>
       <c r="B348" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C348" s="5" t="n">
-        <v>642</v>
+        <v>702</v>
       </c>
       <c r="D348" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>1383</v>
+        <v>1643</v>
       </c>
       <c r="F348" s="5" t="n">
-        <v>1384</v>
+        <v>1644</v>
       </c>
       <c r="G348" s="5"/>
       <c r="H348" s="5"/>
@@ -11755,23 +11755,21 @@
     </row>
     <row r="349" customHeight="1" ht="20">
       <c r="A349" s="5" t="n">
-        <v>1201</v>
+        <v>1322</v>
       </c>
       <c r="B349" s="5" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C349" s="5" t="n">
-        <v>702</v>
+        <v>642</v>
       </c>
       <c r="D349" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E349" s="5" t="n">
-        <v>1643</v>
-      </c>
-      <c r="F349" s="5" t="n">
-        <v>1644</v>
-      </c>
+        <v>1103</v>
+      </c>
+      <c r="F349" s="5"/>
       <c r="G349" s="5"/>
       <c r="H349" s="5"/>
       <c r="I349" s="5"/>
@@ -11789,21 +11787,23 @@
     </row>
     <row r="350" customHeight="1" ht="20">
       <c r="A350" s="5" t="n">
-        <v>1322</v>
+        <v>1684</v>
       </c>
       <c r="B350" s="5" t="n">
-        <v>121</v>
+        <v>401</v>
       </c>
       <c r="C350" s="5" t="n">
-        <v>642</v>
+        <v>982</v>
       </c>
       <c r="D350" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>1103</v>
-      </c>
-      <c r="F350" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F350" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G350" s="5"/>
       <c r="H350" s="5"/>
       <c r="I350" s="5"/>
@@ -11821,22 +11821,22 @@
     </row>
     <row r="351" customHeight="1" ht="20">
       <c r="A351" s="5" t="n">
-        <v>1684</v>
+        <v>1422</v>
       </c>
       <c r="B351" s="5" t="n">
-        <v>401</v>
+        <v>121</v>
       </c>
       <c r="C351" s="5" t="n">
-        <v>982</v>
+        <v>642</v>
       </c>
       <c r="D351" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>585</v>
+        <v>1563</v>
       </c>
       <c r="F351" s="5" t="n">
-        <v>584</v>
+        <v>1564</v>
       </c>
       <c r="G351" s="5"/>
       <c r="H351" s="5"/>
@@ -11855,23 +11855,21 @@
     </row>
     <row r="352" customHeight="1" ht="20">
       <c r="A352" s="5" t="n">
-        <v>1422</v>
+        <v>1644</v>
       </c>
       <c r="B352" s="5" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="C352" s="5" t="n">
-        <v>642</v>
+        <v>942</v>
       </c>
       <c r="D352" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F352" s="5" t="n">
-        <v>1564</v>
-      </c>
+        <v>1947</v>
+      </c>
+      <c r="F352" s="5"/>
       <c r="G352" s="5"/>
       <c r="H352" s="5"/>
       <c r="I352" s="5"/>
@@ -11889,21 +11887,23 @@
     </row>
     <row r="353" customHeight="1" ht="20">
       <c r="A353" s="5" t="n">
-        <v>1644</v>
+        <v>1683</v>
       </c>
       <c r="B353" s="5" t="n">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C353" s="5" t="n">
-        <v>942</v>
+        <v>982</v>
       </c>
       <c r="D353" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>1947</v>
-      </c>
-      <c r="F353" s="5"/>
+        <v>221</v>
+      </c>
+      <c r="F353" s="5" t="n">
+        <v>1131</v>
+      </c>
       <c r="G353" s="5"/>
       <c r="H353" s="5"/>
       <c r="I353" s="5"/>
@@ -11921,23 +11921,21 @@
     </row>
     <row r="354" customHeight="1" ht="20">
       <c r="A354" s="5" t="n">
-        <v>1683</v>
+        <v>2381</v>
       </c>
       <c r="B354" s="5" t="n">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="C354" s="5" t="n">
-        <v>982</v>
+        <v>1222</v>
       </c>
       <c r="D354" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="F354" s="5" t="n">
-        <v>1131</v>
-      </c>
+        <v>2423</v>
+      </c>
+      <c r="F354" s="5"/>
       <c r="G354" s="5"/>
       <c r="H354" s="5"/>
       <c r="I354" s="5"/>
@@ -11955,19 +11953,19 @@
     </row>
     <row r="355" customHeight="1" ht="20">
       <c r="A355" s="5" t="n">
-        <v>2381</v>
+        <v>2101</v>
       </c>
       <c r="B355" s="5" t="n">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="C355" s="5" t="n">
-        <v>1222</v>
+        <v>1162</v>
       </c>
       <c r="D355" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>2423</v>
+        <v>1163</v>
       </c>
       <c r="F355" s="5"/>
       <c r="G355" s="5"/>
@@ -11987,7 +11985,7 @@
     </row>
     <row r="356" customHeight="1" ht="20">
       <c r="A356" s="5" t="n">
-        <v>2101</v>
+        <v>2261</v>
       </c>
       <c r="B356" s="5" t="n">
         <v>81</v>
@@ -11996,12 +11994,14 @@
         <v>1162</v>
       </c>
       <c r="D356" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>1163</v>
-      </c>
-      <c r="F356" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="F356" s="5" t="n">
+        <v>83</v>
+      </c>
       <c r="G356" s="5"/>
       <c r="H356" s="5"/>
       <c r="I356" s="5"/>
@@ -12019,22 +12019,22 @@
     </row>
     <row r="357" customHeight="1" ht="20">
       <c r="A357" s="5" t="n">
-        <v>2261</v>
+        <v>2464</v>
       </c>
       <c r="B357" s="5" t="n">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="C357" s="5" t="n">
-        <v>1162</v>
+        <v>1302</v>
       </c>
       <c r="D357" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>463</v>
+        <v>2203</v>
       </c>
       <c r="F357" s="5" t="n">
-        <v>83</v>
+        <v>2204</v>
       </c>
       <c r="G357" s="5"/>
       <c r="H357" s="5"/>
@@ -12053,23 +12053,21 @@
     </row>
     <row r="358" customHeight="1" ht="20">
       <c r="A358" s="5" t="n">
-        <v>2464</v>
+        <v>2323</v>
       </c>
       <c r="B358" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C358" s="5" t="n">
-        <v>1302</v>
+        <v>1222</v>
       </c>
       <c r="D358" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>2203</v>
-      </c>
-      <c r="F358" s="5" t="n">
-        <v>2204</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="F358" s="5"/>
       <c r="G358" s="5"/>
       <c r="H358" s="5"/>
       <c r="I358" s="5"/>
@@ -12087,21 +12085,23 @@
     </row>
     <row r="359" customHeight="1" ht="20">
       <c r="A359" s="5" t="n">
-        <v>2323</v>
+        <v>1861</v>
       </c>
       <c r="B359" s="5" t="n">
-        <v>461</v>
+        <v>41</v>
       </c>
       <c r="C359" s="5" t="n">
-        <v>1222</v>
+        <v>1062</v>
       </c>
       <c r="D359" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E359" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="F359" s="5"/>
+        <v>1427</v>
+      </c>
+      <c r="F359" s="5" t="n">
+        <v>1428</v>
+      </c>
       <c r="G359" s="5"/>
       <c r="H359" s="5"/>
       <c r="I359" s="5"/>
@@ -12119,22 +12119,22 @@
     </row>
     <row r="360" customHeight="1" ht="20">
       <c r="A360" s="5" t="n">
-        <v>1861</v>
+        <v>1886</v>
       </c>
       <c r="B360" s="5" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C360" s="5" t="n">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="D360" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E360" s="5" t="n">
-        <v>1427</v>
+        <v>2105</v>
       </c>
       <c r="F360" s="5" t="n">
-        <v>1428</v>
+        <v>2104</v>
       </c>
       <c r="G360" s="5"/>
       <c r="H360" s="5"/>
@@ -12153,24 +12153,26 @@
     </row>
     <row r="361" customHeight="1" ht="20">
       <c r="A361" s="5" t="n">
-        <v>1886</v>
+        <v>1904</v>
       </c>
       <c r="B361" s="5" t="n">
-        <v>50</v>
+        <v>281</v>
       </c>
       <c r="C361" s="5" t="n">
-        <v>1042</v>
+        <v>822</v>
       </c>
       <c r="D361" s="5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E361" s="5" t="n">
-        <v>2105</v>
+        <v>1059</v>
       </c>
       <c r="F361" s="5" t="n">
-        <v>2104</v>
-      </c>
-      <c r="G361" s="5"/>
+        <v>1061</v>
+      </c>
+      <c r="G361" s="5" t="n">
+        <v>1060</v>
+      </c>
       <c r="H361" s="5"/>
       <c r="I361" s="5"/>
       <c r="J361" s="5"/>
@@ -12187,7 +12189,7 @@
     </row>
     <row r="362" customHeight="1" ht="20">
       <c r="A362" s="5" t="n">
-        <v>1904</v>
+        <v>1922</v>
       </c>
       <c r="B362" s="5" t="n">
         <v>281</v>
@@ -12196,17 +12198,13 @@
         <v>822</v>
       </c>
       <c r="D362" s="5" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E362" s="5" t="n">
-        <v>1059</v>
-      </c>
-      <c r="F362" s="5" t="n">
-        <v>1061</v>
-      </c>
-      <c r="G362" s="5" t="n">
-        <v>1060</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="F362" s="5"/>
+      <c r="G362" s="5"/>
       <c r="H362" s="5"/>
       <c r="I362" s="5"/>
       <c r="J362" s="5"/>
@@ -12223,21 +12221,23 @@
     </row>
     <row r="363" customHeight="1" ht="20">
       <c r="A363" s="5" t="n">
-        <v>1922</v>
+        <v>1948</v>
       </c>
       <c r="B363" s="5" t="n">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="C363" s="5" t="n">
-        <v>822</v>
+        <v>1102</v>
       </c>
       <c r="D363" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="F363" s="5"/>
+        <v>301</v>
+      </c>
+      <c r="F363" s="5" t="n">
+        <v>2193</v>
+      </c>
       <c r="G363" s="5"/>
       <c r="H363" s="5"/>
       <c r="I363" s="5"/>
@@ -12255,7 +12255,7 @@
     </row>
     <row r="364" customHeight="1" ht="20">
       <c r="A364" s="5" t="n">
-        <v>1948</v>
+        <v>1961</v>
       </c>
       <c r="B364" s="5" t="n">
         <v>421</v>
@@ -12267,10 +12267,10 @@
         <v>1</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>301</v>
+        <v>2203</v>
       </c>
       <c r="F364" s="5" t="n">
-        <v>2193</v>
+        <v>2204</v>
       </c>
       <c r="G364" s="5"/>
       <c r="H364" s="5"/>
@@ -12289,22 +12289,22 @@
     </row>
     <row r="365" customHeight="1" ht="20">
       <c r="A365" s="5" t="n">
-        <v>1961</v>
+        <v>2424</v>
       </c>
       <c r="B365" s="5" t="n">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="C365" s="5" t="n">
-        <v>1102</v>
+        <v>1282</v>
       </c>
       <c r="D365" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E365" s="5" t="n">
-        <v>2203</v>
+        <v>725</v>
       </c>
       <c r="F365" s="5" t="n">
-        <v>2204</v>
+        <v>282</v>
       </c>
       <c r="G365" s="5"/>
       <c r="H365" s="5"/>
@@ -12323,22 +12323,22 @@
     </row>
     <row r="366" customHeight="1" ht="20">
       <c r="A366" s="5" t="n">
-        <v>2424</v>
+        <v>2602</v>
       </c>
       <c r="B366" s="5" t="n">
-        <v>481</v>
+        <v>81</v>
       </c>
       <c r="C366" s="5" t="n">
-        <v>1282</v>
+        <v>1162</v>
       </c>
       <c r="D366" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E366" s="5" t="n">
-        <v>725</v>
+        <v>2606</v>
       </c>
       <c r="F366" s="5" t="n">
-        <v>282</v>
+        <v>2605</v>
       </c>
       <c r="G366" s="5"/>
       <c r="H366" s="5"/>
@@ -12357,22 +12357,22 @@
     </row>
     <row r="367" customHeight="1" ht="20">
       <c r="A367" s="5" t="n">
-        <v>2602</v>
+        <v>2681</v>
       </c>
       <c r="B367" s="5" t="n">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="C367" s="5" t="n">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="D367" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E367" s="5" t="n">
-        <v>2606</v>
+        <v>2265</v>
       </c>
       <c r="F367" s="5" t="n">
-        <v>2605</v>
+        <v>2263</v>
       </c>
       <c r="G367" s="5"/>
       <c r="H367" s="5"/>
@@ -12391,22 +12391,22 @@
     </row>
     <row r="368" customHeight="1" ht="20">
       <c r="A368" s="5" t="n">
-        <v>2681</v>
+        <v>2721</v>
       </c>
       <c r="B368" s="5" t="n">
-        <v>461</v>
+        <v>261</v>
       </c>
       <c r="C368" s="5" t="n">
-        <v>1222</v>
+        <v>1202</v>
       </c>
       <c r="D368" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E368" s="5" t="n">
-        <v>2265</v>
+        <v>2344</v>
       </c>
       <c r="F368" s="5" t="n">
-        <v>2263</v>
+        <v>2343</v>
       </c>
       <c r="G368" s="5"/>
       <c r="H368" s="5"/>
@@ -12425,25 +12425,29 @@
     </row>
     <row r="369" customHeight="1" ht="20">
       <c r="A369" s="5" t="n">
-        <v>2721</v>
+        <v>2742</v>
       </c>
       <c r="B369" s="5" t="n">
-        <v>261</v>
+        <v>501</v>
       </c>
       <c r="C369" s="5" t="n">
-        <v>1202</v>
+        <v>1322</v>
       </c>
       <c r="D369" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E369" s="5" t="n">
-        <v>2344</v>
+        <v>2703</v>
       </c>
       <c r="F369" s="5" t="n">
-        <v>2343</v>
-      </c>
-      <c r="G369" s="5"/>
-      <c r="H369" s="5"/>
+        <v>2707</v>
+      </c>
+      <c r="G369" s="5" t="n">
+        <v>2706</v>
+      </c>
+      <c r="H369" s="5" t="n">
+        <v>2704</v>
+      </c>
       <c r="I369" s="5"/>
       <c r="J369" s="5"/>
       <c r="K369" s="6" t="s">
@@ -12459,29 +12463,23 @@
     </row>
     <row r="370" customHeight="1" ht="20">
       <c r="A370" s="5" t="n">
-        <v>2742</v>
+        <v>2783</v>
       </c>
       <c r="B370" s="5" t="n">
-        <v>501</v>
+        <v>181</v>
       </c>
       <c r="C370" s="5" t="n">
-        <v>1322</v>
+        <v>1262</v>
       </c>
       <c r="D370" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E370" s="5" t="n">
-        <v>2703</v>
-      </c>
-      <c r="F370" s="5" t="n">
-        <v>2707</v>
-      </c>
-      <c r="G370" s="5" t="n">
-        <v>2706</v>
-      </c>
-      <c r="H370" s="5" t="n">
-        <v>2704</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="F370" s="5"/>
+      <c r="G370" s="5"/>
+      <c r="H370" s="5"/>
       <c r="I370" s="5"/>
       <c r="J370" s="5"/>
       <c r="K370" s="6" t="s">
@@ -12497,7 +12495,7 @@
     </row>
     <row r="371" customHeight="1" ht="20">
       <c r="A371" s="5" t="n">
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="B371" s="5" t="n">
         <v>181</v>
@@ -12506,12 +12504,14 @@
         <v>1262</v>
       </c>
       <c r="D371" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="F371" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="F371" s="5" t="n">
+        <v>22</v>
+      </c>
       <c r="G371" s="5"/>
       <c r="H371" s="5"/>
       <c r="I371" s="5"/>
@@ -12529,22 +12529,22 @@
     </row>
     <row r="372" customHeight="1" ht="20">
       <c r="A372" s="5" t="n">
-        <v>2784</v>
+        <v>2803</v>
       </c>
       <c r="B372" s="5" t="n">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="C372" s="5" t="n">
-        <v>1262</v>
+        <v>1342</v>
       </c>
       <c r="D372" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E372" s="5" t="n">
-        <v>24</v>
+        <v>2744</v>
       </c>
       <c r="F372" s="5" t="n">
-        <v>22</v>
+        <v>2745</v>
       </c>
       <c r="G372" s="5"/>
       <c r="H372" s="5"/>
@@ -12563,23 +12563,21 @@
     </row>
     <row r="373" customHeight="1" ht="20">
       <c r="A373" s="5" t="n">
-        <v>2803</v>
+        <v>2843</v>
       </c>
       <c r="B373" s="5" t="n">
-        <v>27</v>
+        <v>501</v>
       </c>
       <c r="C373" s="5" t="n">
-        <v>1342</v>
+        <v>1322</v>
       </c>
       <c r="D373" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E373" s="5" t="n">
-        <v>2744</v>
-      </c>
-      <c r="F373" s="5" t="n">
-        <v>2745</v>
-      </c>
+        <v>1946</v>
+      </c>
+      <c r="F373" s="5"/>
       <c r="G373" s="5"/>
       <c r="H373" s="5"/>
       <c r="I373" s="5"/>
@@ -12597,21 +12595,23 @@
     </row>
     <row r="374" customHeight="1" ht="20">
       <c r="A374" s="5" t="n">
-        <v>2843</v>
+        <v>3281</v>
       </c>
       <c r="B374" s="5" t="n">
-        <v>501</v>
+        <v>261</v>
       </c>
       <c r="C374" s="5" t="n">
-        <v>1322</v>
+        <v>1463</v>
       </c>
       <c r="D374" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>1946</v>
-      </c>
-      <c r="F374" s="5"/>
+        <v>527</v>
+      </c>
+      <c r="F374" s="5" t="n">
+        <v>766</v>
+      </c>
       <c r="G374" s="5"/>
       <c r="H374" s="5"/>
       <c r="I374" s="5"/>
@@ -12629,22 +12629,22 @@
     </row>
     <row r="375" customHeight="1" ht="20">
       <c r="A375" s="5" t="n">
-        <v>3281</v>
+        <v>2982</v>
       </c>
       <c r="B375" s="5" t="n">
         <v>261</v>
       </c>
       <c r="C375" s="5" t="n">
-        <v>1463</v>
+        <v>1202</v>
       </c>
       <c r="D375" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E375" s="5" t="n">
-        <v>527</v>
+        <v>2843</v>
       </c>
       <c r="F375" s="5" t="n">
-        <v>766</v>
+        <v>2844</v>
       </c>
       <c r="G375" s="5"/>
       <c r="H375" s="5"/>
@@ -12663,22 +12663,22 @@
     </row>
     <row r="376" customHeight="1" ht="20">
       <c r="A376" s="5" t="n">
-        <v>2982</v>
+        <v>3182</v>
       </c>
       <c r="B376" s="5" t="n">
-        <v>261</v>
+        <v>481</v>
       </c>
       <c r="C376" s="5" t="n">
-        <v>1202</v>
+        <v>1282</v>
       </c>
       <c r="D376" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E376" s="5" t="n">
-        <v>2843</v>
+        <v>24</v>
       </c>
       <c r="F376" s="5" t="n">
-        <v>2844</v>
+        <v>22</v>
       </c>
       <c r="G376" s="5"/>
       <c r="H376" s="5"/>
@@ -12697,23 +12697,21 @@
     </row>
     <row r="377" customHeight="1" ht="20">
       <c r="A377" s="5" t="n">
-        <v>3182</v>
+        <v>3322</v>
       </c>
       <c r="B377" s="5" t="n">
-        <v>481</v>
+        <v>521</v>
       </c>
       <c r="C377" s="5" t="n">
-        <v>1282</v>
+        <v>1423</v>
       </c>
       <c r="D377" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E377" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F377" s="5" t="n">
-        <v>22</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="F377" s="5"/>
       <c r="G377" s="5"/>
       <c r="H377" s="5"/>
       <c r="I377" s="5"/>
@@ -12731,19 +12729,19 @@
     </row>
     <row r="378" customHeight="1" ht="20">
       <c r="A378" s="5" t="n">
-        <v>3322</v>
+        <v>3426</v>
       </c>
       <c r="B378" s="5" t="n">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="C378" s="5" t="n">
-        <v>1423</v>
+        <v>1503</v>
       </c>
       <c r="D378" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E378" s="5" t="n">
-        <v>282</v>
+        <v>3070</v>
       </c>
       <c r="F378" s="5"/>
       <c r="G378" s="5"/>
@@ -12751,31 +12749,31 @@
       <c r="I378" s="5"/>
       <c r="J378" s="5"/>
       <c r="K378" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L378" s="7"/>
       <c r="M378" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N378" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="379" customHeight="1" ht="20">
       <c r="A379" s="5" t="n">
-        <v>3426</v>
+        <v>3821</v>
       </c>
       <c r="B379" s="5" t="n">
-        <v>541</v>
+        <v>681</v>
       </c>
       <c r="C379" s="5" t="n">
-        <v>1503</v>
+        <v>1647</v>
       </c>
       <c r="D379" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E379" s="5" t="n">
-        <v>3070</v>
+        <v>3443</v>
       </c>
       <c r="F379" s="5"/>
       <c r="G379" s="5"/>
@@ -12785,31 +12783,31 @@
       <c r="K379" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L379" s="7"/>
-      <c r="M379" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N379" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L379" s="7" t="n">
+        <v>45888.8230208333</v>
+      </c>
+      <c r="M379" s="6"/>
+      <c r="N379" s="7"/>
     </row>
     <row r="380" customHeight="1" ht="20">
       <c r="A380" s="5" t="n">
-        <v>3821</v>
+        <v>3881</v>
       </c>
       <c r="B380" s="5" t="n">
-        <v>681</v>
+        <v>621</v>
       </c>
       <c r="C380" s="5" t="n">
-        <v>1647</v>
+        <v>1683</v>
       </c>
       <c r="D380" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E380" s="5" t="n">
-        <v>3443</v>
-      </c>
-      <c r="F380" s="5"/>
+        <v>3503</v>
+      </c>
+      <c r="F380" s="5" t="n">
+        <v>3504</v>
+      </c>
       <c r="G380" s="5"/>
       <c r="H380" s="5"/>
       <c r="I380" s="5"/>
@@ -12818,14 +12816,14 @@
         <v>15</v>
       </c>
       <c r="L380" s="7" t="n">
-        <v>45888.8230208333</v>
+        <v>45908.7021990741</v>
       </c>
       <c r="M380" s="6"/>
       <c r="N380" s="7"/>
     </row>
     <row r="381" customHeight="1" ht="20">
       <c r="A381" s="5" t="n">
-        <v>3881</v>
+        <v>4001</v>
       </c>
       <c r="B381" s="5" t="n">
         <v>621</v>
@@ -12834,14 +12832,12 @@
         <v>1683</v>
       </c>
       <c r="D381" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E381" s="5" t="n">
-        <v>3503</v>
-      </c>
-      <c r="F381" s="5" t="n">
-        <v>3504</v>
-      </c>
+        <v>2743</v>
+      </c>
+      <c r="F381" s="5"/>
       <c r="G381" s="5"/>
       <c r="H381" s="5"/>
       <c r="I381" s="5"/>
@@ -12850,26 +12846,26 @@
         <v>15</v>
       </c>
       <c r="L381" s="7" t="n">
-        <v>45908.7021990741</v>
+        <v>45943.8618981481</v>
       </c>
       <c r="M381" s="6"/>
       <c r="N381" s="7"/>
     </row>
     <row r="382" customHeight="1" ht="20">
       <c r="A382" s="5" t="n">
-        <v>4001</v>
+        <v>4041</v>
       </c>
       <c r="B382" s="5" t="n">
-        <v>621</v>
+        <v>741</v>
       </c>
       <c r="C382" s="5" t="n">
-        <v>1683</v>
+        <v>1703</v>
       </c>
       <c r="D382" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E382" s="5" t="n">
-        <v>2743</v>
+        <v>527</v>
       </c>
       <c r="F382" s="5"/>
       <c r="G382" s="5"/>
@@ -12880,28 +12876,30 @@
         <v>15</v>
       </c>
       <c r="L382" s="7" t="n">
-        <v>45943.8618981481</v>
+        <v>45957.6777777778</v>
       </c>
       <c r="M382" s="6"/>
       <c r="N382" s="7"/>
     </row>
     <row r="383" customHeight="1" ht="20">
       <c r="A383" s="5" t="n">
-        <v>4041</v>
+        <v>4063</v>
       </c>
       <c r="B383" s="5" t="n">
-        <v>741</v>
+        <v>781</v>
       </c>
       <c r="C383" s="5" t="n">
-        <v>1703</v>
+        <v>1743</v>
       </c>
       <c r="D383" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E383" s="5" t="n">
-        <v>527</v>
-      </c>
-      <c r="F383" s="5"/>
+        <v>3665</v>
+      </c>
+      <c r="F383" s="5" t="n">
+        <v>2504</v>
+      </c>
       <c r="G383" s="5"/>
       <c r="H383" s="5"/>
       <c r="I383" s="5"/>
@@ -12910,14 +12908,14 @@
         <v>15</v>
       </c>
       <c r="L383" s="7" t="n">
-        <v>45957.6777777778</v>
+        <v>45966.4241203704</v>
       </c>
       <c r="M383" s="6"/>
       <c r="N383" s="7"/>
     </row>
     <row r="384" customHeight="1" ht="20">
       <c r="A384" s="5" t="n">
-        <v>4063</v>
+        <v>4101</v>
       </c>
       <c r="B384" s="5" t="n">
         <v>781</v>
@@ -12926,14 +12924,12 @@
         <v>1743</v>
       </c>
       <c r="D384" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E384" s="5" t="n">
-        <v>3665</v>
-      </c>
-      <c r="F384" s="5" t="n">
-        <v>2504</v>
-      </c>
+        <v>2503</v>
+      </c>
+      <c r="F384" s="5"/>
       <c r="G384" s="5"/>
       <c r="H384" s="5"/>
       <c r="I384" s="5"/>
@@ -12942,28 +12938,30 @@
         <v>15</v>
       </c>
       <c r="L384" s="7" t="n">
-        <v>45966.4241203704</v>
+        <v>45980.8233680556</v>
       </c>
       <c r="M384" s="6"/>
       <c r="N384" s="7"/>
     </row>
     <row r="385" customHeight="1" ht="20">
       <c r="A385" s="5" t="n">
-        <v>4101</v>
+        <v>4121</v>
       </c>
       <c r="B385" s="5" t="n">
-        <v>781</v>
+        <v>681</v>
       </c>
       <c r="C385" s="5" t="n">
-        <v>1743</v>
+        <v>1647</v>
       </c>
       <c r="D385" s="5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E385" s="5" t="n">
-        <v>2503</v>
-      </c>
-      <c r="F385" s="5"/>
+        <v>3706</v>
+      </c>
+      <c r="F385" s="5" t="n">
+        <v>3705</v>
+      </c>
       <c r="G385" s="5"/>
       <c r="H385" s="5"/>
       <c r="I385" s="5"/>
@@ -12972,29 +12970,29 @@
         <v>15</v>
       </c>
       <c r="L385" s="7" t="n">
-        <v>45980.8233680556</v>
+        <v>45982.3899537037</v>
       </c>
       <c r="M385" s="6"/>
       <c r="N385" s="7"/>
     </row>
     <row r="386" customHeight="1" ht="20">
       <c r="A386" s="5" t="n">
-        <v>4121</v>
+        <v>4202</v>
       </c>
       <c r="B386" s="5" t="n">
-        <v>681</v>
+        <v>762</v>
       </c>
       <c r="C386" s="5" t="n">
-        <v>1647</v>
+        <v>1724</v>
       </c>
       <c r="D386" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>3706</v>
+        <v>3784</v>
       </c>
       <c r="F386" s="5" t="n">
-        <v>3705</v>
+        <v>3786</v>
       </c>
       <c r="G386" s="5"/>
       <c r="H386" s="5"/>
@@ -13004,31 +13002,33 @@
         <v>15</v>
       </c>
       <c r="L386" s="7" t="n">
-        <v>45982.3899537037</v>
+        <v>46000.8910185185</v>
       </c>
       <c r="M386" s="6"/>
       <c r="N386" s="7"/>
     </row>
     <row r="387" customHeight="1" ht="20">
       <c r="A387" s="5" t="n">
-        <v>4202</v>
+        <v>4221</v>
       </c>
       <c r="B387" s="5" t="n">
-        <v>762</v>
+        <v>822</v>
       </c>
       <c r="C387" s="5" t="n">
-        <v>1724</v>
+        <v>1784</v>
       </c>
       <c r="D387" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>3784</v>
+        <v>3813</v>
       </c>
       <c r="F387" s="5" t="n">
-        <v>3786</v>
-      </c>
-      <c r="G387" s="5"/>
+        <v>3817</v>
+      </c>
+      <c r="G387" s="5" t="n">
+        <v>3818</v>
+      </c>
       <c r="H387" s="5"/>
       <c r="I387" s="5"/>
       <c r="J387" s="5"/>
@@ -13036,32 +13036,32 @@
         <v>15</v>
       </c>
       <c r="L387" s="7" t="n">
-        <v>46000.8910185185</v>
+        <v>46002.888275463</v>
       </c>
       <c r="M387" s="6"/>
       <c r="N387" s="7"/>
     </row>
     <row r="388" customHeight="1" ht="20">
       <c r="A388" s="5" t="n">
-        <v>4221</v>
+        <v>4261</v>
       </c>
       <c r="B388" s="5" t="n">
-        <v>822</v>
+        <v>781</v>
       </c>
       <c r="C388" s="5" t="n">
-        <v>1784</v>
+        <v>1743</v>
       </c>
       <c r="D388" s="5" t="n">
         <v>27</v>
       </c>
       <c r="E388" s="5" t="n">
-        <v>3813</v>
+        <v>3824</v>
       </c>
       <c r="F388" s="5" t="n">
-        <v>3817</v>
+        <v>34</v>
       </c>
       <c r="G388" s="5" t="n">
-        <v>3818</v>
+        <v>3823</v>
       </c>
       <c r="H388" s="5"/>
       <c r="I388" s="5"/>
@@ -13070,14 +13070,14 @@
         <v>15</v>
       </c>
       <c r="L388" s="7" t="n">
-        <v>46002.888275463</v>
+        <v>46008.9022800926</v>
       </c>
       <c r="M388" s="6"/>
       <c r="N388" s="7"/>
     </row>
     <row r="389" customHeight="1" ht="20">
       <c r="A389" s="5" t="n">
-        <v>4261</v>
+        <v>4262</v>
       </c>
       <c r="B389" s="5" t="n">
         <v>781</v>
@@ -13086,64 +13086,60 @@
         <v>1743</v>
       </c>
       <c r="D389" s="5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>3824</v>
+        <v>2183</v>
       </c>
       <c r="F389" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="G389" s="5" t="n">
-        <v>3823</v>
-      </c>
+        <v>3809</v>
+      </c>
+      <c r="G389" s="5"/>
       <c r="H389" s="5"/>
       <c r="I389" s="5"/>
       <c r="J389" s="5"/>
       <c r="K389" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L389" s="7" t="n">
-        <v>46008.9022800926</v>
+        <v>46009.3191435185</v>
       </c>
       <c r="M389" s="6"/>
       <c r="N389" s="7"/>
     </row>
     <row r="390" customHeight="1" ht="20">
       <c r="A390" s="5" t="n">
-        <v>4262</v>
+        <v>4282</v>
       </c>
       <c r="B390" s="5" t="n">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="C390" s="5" t="n">
-        <v>1743</v>
+        <v>1784</v>
       </c>
       <c r="D390" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E390" s="5" t="n">
-        <v>2183</v>
-      </c>
-      <c r="F390" s="5" t="n">
-        <v>3809</v>
-      </c>
+        <v>3852</v>
+      </c>
+      <c r="F390" s="5"/>
       <c r="G390" s="5"/>
       <c r="H390" s="5"/>
       <c r="I390" s="5"/>
       <c r="J390" s="5"/>
       <c r="K390" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L390" s="7" t="n">
-        <v>46009.3191435185</v>
+        <v>46011.5151736111</v>
       </c>
       <c r="M390" s="6"/>
       <c r="N390" s="7"/>
     </row>
     <row r="391" customHeight="1" ht="20">
       <c r="A391" s="5" t="n">
-        <v>4282</v>
+        <v>4283</v>
       </c>
       <c r="B391" s="5" t="n">
         <v>822</v>
@@ -13155,7 +13151,7 @@
         <v>21</v>
       </c>
       <c r="E391" s="5" t="n">
-        <v>3852</v>
+        <v>3853</v>
       </c>
       <c r="F391" s="5"/>
       <c r="G391" s="5"/>
@@ -13166,40 +13162,10 @@
         <v>15</v>
       </c>
       <c r="L391" s="7" t="n">
-        <v>46011.5151736111</v>
+        <v>46011.5212152778</v>
       </c>
       <c r="M391" s="6"/>
       <c r="N391" s="7"/>
-    </row>
-    <row r="392" customHeight="1" ht="20">
-      <c r="A392" s="5" t="n">
-        <v>4283</v>
-      </c>
-      <c r="B392" s="5" t="n">
-        <v>822</v>
-      </c>
-      <c r="C392" s="5" t="n">
-        <v>1784</v>
-      </c>
-      <c r="D392" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E392" s="5" t="n">
-        <v>3853</v>
-      </c>
-      <c r="F392" s="5"/>
-      <c r="G392" s="5"/>
-      <c r="H392" s="5"/>
-      <c r="I392" s="5"/>
-      <c r="J392" s="5"/>
-      <c r="K392" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L392" s="7" t="n">
-        <v>46011.5212152778</v>
-      </c>
-      <c r="M392" s="6"/>
-      <c r="N392" s="7"/>
     </row>
   </sheetData>
   <tableParts count="1">

--- a/inp_Excel/mov_clienti_alloggi.xlsx
+++ b/inp_Excel/mov_clienti_alloggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="16">
   <si>
     <t>MOV_CLIENTI_ALLOGGIO_PK</t>
   </si>
@@ -1499,9 +1499,7 @@
       <c r="E39" s="5" t="n">
         <v>627</v>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>626</v>
-      </c>
+      <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -3005,7 +3003,7 @@
     </row>
     <row r="85" customHeight="1" ht="20">
       <c r="A85" s="5" t="n">
-        <v>4122</v>
+        <v>4161</v>
       </c>
       <c r="B85" s="5" t="n">
         <v>801</v>
@@ -3014,12 +3012,14 @@
         <v>1763</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1163</v>
-      </c>
-      <c r="F85" s="5"/>
+        <v>3744</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>3743</v>
+      </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -3028,29 +3028,29 @@
         <v>15</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>45982.4876851852</v>
+        <v>45989.386724537</v>
       </c>
       <c r="M85" s="6"/>
       <c r="N85" s="7"/>
     </row>
     <row r="86" customHeight="1" ht="20">
       <c r="A86" s="5" t="n">
-        <v>4161</v>
+        <v>4205</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>801</v>
+        <v>762</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1763</v>
+        <v>1724</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3744</v>
+        <v>2143</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>3743</v>
+        <v>3787</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -3060,61 +3060,63 @@
         <v>15</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>45989.386724537</v>
+        <v>46001.3052314815</v>
       </c>
       <c r="M86" s="6"/>
       <c r="N86" s="7"/>
     </row>
     <row r="87" customHeight="1" ht="20">
       <c r="A87" s="5" t="n">
-        <v>4205</v>
+        <v>49</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>762</v>
+        <v>48</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1724</v>
+        <v>202</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2143</v>
+        <v>529</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>3787</v>
+        <v>530</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L87" s="7" t="n">
-        <v>46001.3052314815</v>
-      </c>
-      <c r="M87" s="6"/>
-      <c r="N87" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L87" s="7"/>
+      <c r="M87" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N87" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="88" customHeight="1" ht="20">
       <c r="A88" s="5" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>529</v>
+        <v>563</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>530</v>
+        <v>564</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -3133,22 +3135,22 @@
     </row>
     <row r="89" customHeight="1" ht="20">
       <c r="A89" s="5" t="n">
-        <v>53</v>
+        <v>822</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>563</v>
+        <v>488</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>564</v>
+        <v>487</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -3167,22 +3169,22 @@
     </row>
     <row r="90" customHeight="1" ht="20">
       <c r="A90" s="5" t="n">
-        <v>822</v>
+        <v>122</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -3201,7 +3203,7 @@
     </row>
     <row r="91" customHeight="1" ht="20">
       <c r="A91" s="5" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>44</v>
@@ -3210,14 +3212,12 @@
         <v>322</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>527</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>528</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="F91" s="5"/>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="92" customHeight="1" ht="20">
       <c r="A92" s="5" t="n">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="B92" s="5" t="n">
         <v>44</v>
@@ -3244,12 +3244,14 @@
         <v>322</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>763</v>
-      </c>
-      <c r="F92" s="5"/>
+        <v>261</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>623</v>
+      </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -3267,7 +3269,7 @@
     </row>
     <row r="93" customHeight="1" ht="20">
       <c r="A93" s="5" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B93" s="5" t="n">
         <v>44</v>
@@ -3276,15 +3278,17 @@
         <v>322</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>261</v>
+        <v>704</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>623</v>
-      </c>
-      <c r="G93" s="5"/>
+        <v>703</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>705</v>
+      </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
@@ -3301,26 +3305,24 @@
     </row>
     <row r="94" customHeight="1" ht="20">
       <c r="A94" s="5" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>704</v>
+        <v>22</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>703</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>705</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G94" s="5"/>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
@@ -3337,7 +3339,7 @@
     </row>
     <row r="95" customHeight="1" ht="20">
       <c r="A95" s="5" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>25</v>
@@ -3349,10 +3351,10 @@
         <v>1</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>22</v>
+        <v>381</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>24</v>
+        <v>726</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -3371,23 +3373,21 @@
     </row>
     <row r="96" customHeight="1" ht="20">
       <c r="A96" s="5" t="n">
-        <v>148</v>
+        <v>861</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>79</v>
+        <v>462</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>381</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>726</v>
-      </c>
+        <v>1483</v>
+      </c>
+      <c r="F96" s="5"/>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -3405,19 +3405,19 @@
     </row>
     <row r="97" customHeight="1" ht="20">
       <c r="A97" s="5" t="n">
-        <v>861</v>
+        <v>152</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>462</v>
+        <v>262</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1483</v>
+        <v>81</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
@@ -3437,19 +3437,19 @@
     </row>
     <row r="98" customHeight="1" ht="20">
       <c r="A98" s="5" t="n">
-        <v>152</v>
+        <v>1244</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>262</v>
+        <v>742</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>81</v>
+        <v>663</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
@@ -3469,19 +3469,19 @@
     </row>
     <row r="99" customHeight="1" ht="20">
       <c r="A99" s="5" t="n">
-        <v>1244</v>
+        <v>158</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>742</v>
+        <v>363</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>663</v>
+        <v>732</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
@@ -3501,23 +3501,29 @@
     </row>
     <row r="100" customHeight="1" ht="20">
       <c r="A100" s="5" t="n">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>732</v>
-      </c>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
+        <v>527</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>766</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>765</v>
+      </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="6" t="s">
@@ -3533,29 +3539,23 @@
     </row>
     <row r="101" customHeight="1" ht="20">
       <c r="A101" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>527</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>766</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>528</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>765</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="6" t="s">
@@ -3571,19 +3571,19 @@
     </row>
     <row r="102" customHeight="1" ht="20">
       <c r="A102" s="5" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>81</v>
+        <v>783</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
@@ -3603,19 +3603,19 @@
     </row>
     <row r="103" customHeight="1" ht="20">
       <c r="A103" s="5" t="n">
-        <v>201</v>
+        <v>1621</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>322</v>
+        <v>922</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>783</v>
+        <v>1467</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
@@ -3635,21 +3635,23 @@
     </row>
     <row r="104" customHeight="1" ht="20">
       <c r="A104" s="5" t="n">
-        <v>1621</v>
+        <v>262</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>922</v>
+        <v>363</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F104" s="5"/>
+        <v>807</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>808</v>
+      </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
@@ -3667,22 +3669,22 @@
     </row>
     <row r="105" customHeight="1" ht="20">
       <c r="A105" s="5" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>808</v>
+        <v>85</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -3701,7 +3703,7 @@
     </row>
     <row r="106" customHeight="1" ht="20">
       <c r="A106" s="5" t="n">
-        <v>281</v>
+        <v>441</v>
       </c>
       <c r="B106" s="5" t="n">
         <v>23</v>
@@ -3713,10 +3715,10 @@
         <v>1</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>843</v>
+        <v>963</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>85</v>
+        <v>964</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -3735,22 +3737,22 @@
     </row>
     <row r="107" customHeight="1" ht="20">
       <c r="A107" s="5" t="n">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>963</v>
+        <v>1164</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>964</v>
+        <v>1163</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -3769,22 +3771,22 @@
     </row>
     <row r="108" customHeight="1" ht="20">
       <c r="A108" s="5" t="n">
-        <v>501</v>
+        <v>562</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>262</v>
+        <v>402</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1164</v>
+        <v>1203</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>1163</v>
+        <v>90</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -3803,7 +3805,7 @@
     </row>
     <row r="109" customHeight="1" ht="20">
       <c r="A109" s="5" t="n">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="B109" s="5" t="n">
         <v>81</v>
@@ -3815,10 +3817,10 @@
         <v>1</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1203</v>
+        <v>1223</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>90</v>
+        <v>1224</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
@@ -3837,23 +3839,21 @@
     </row>
     <row r="110" customHeight="1" ht="20">
       <c r="A110" s="5" t="n">
-        <v>581</v>
+        <v>761</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>402</v>
+        <v>522</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1223</v>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>1224</v>
-      </c>
+        <v>1423</v>
+      </c>
+      <c r="F110" s="5"/>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -3871,19 +3871,19 @@
     </row>
     <row r="111" customHeight="1" ht="20">
       <c r="A111" s="5" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="D111" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1423</v>
+        <v>1404</v>
       </c>
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
@@ -3903,21 +3903,23 @@
     </row>
     <row r="112" customHeight="1" ht="20">
       <c r="A112" s="5" t="n">
-        <v>763</v>
+        <v>981</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>502</v>
+        <v>582</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1404</v>
-      </c>
-      <c r="F112" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>83</v>
+      </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
@@ -3935,22 +3937,22 @@
     </row>
     <row r="113" customHeight="1" ht="20">
       <c r="A113" s="5" t="n">
-        <v>981</v>
+        <v>1282</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>582</v>
+        <v>642</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>463</v>
+        <v>727</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>83</v>
+        <v>728</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -3969,7 +3971,7 @@
     </row>
     <row r="114" customHeight="1" ht="20">
       <c r="A114" s="5" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B114" s="5" t="n">
         <v>121</v>
@@ -3981,10 +3983,10 @@
         <v>1</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>727</v>
+        <v>1134</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>728</v>
+        <v>1133</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -4003,7 +4005,7 @@
     </row>
     <row r="115" customHeight="1" ht="20">
       <c r="A115" s="5" t="n">
-        <v>1283</v>
+        <v>1361</v>
       </c>
       <c r="B115" s="5" t="n">
         <v>121</v>
@@ -4015,10 +4017,10 @@
         <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1134</v>
+        <v>1804</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>1133</v>
+        <v>1803</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -4037,23 +4039,21 @@
     </row>
     <row r="116" customHeight="1" ht="20">
       <c r="A116" s="5" t="n">
-        <v>1361</v>
+        <v>1401</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>642</v>
+        <v>822</v>
       </c>
       <c r="D116" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1804</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>1803</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="F116" s="5"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
@@ -4071,22 +4071,22 @@
     </row>
     <row r="117" customHeight="1" ht="20">
       <c r="A117" s="5" t="n">
-        <v>1401</v>
+        <v>1682</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>281</v>
+        <v>321</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>822</v>
+        <v>862</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>627</v>
+        <v>2003</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>626</v>
+        <v>2004</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="118" customHeight="1" ht="20">
       <c r="A118" s="5" t="n">
-        <v>1682</v>
+        <v>1582</v>
       </c>
       <c r="B118" s="5" t="n">
         <v>321</v>
@@ -4117,10 +4117,10 @@
         <v>1</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2003</v>
+        <v>1904</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>2004</v>
+        <v>1903</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -4139,23 +4139,21 @@
     </row>
     <row r="119" customHeight="1" ht="20">
       <c r="A119" s="5" t="n">
-        <v>1582</v>
+        <v>1641</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>862</v>
+        <v>942</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1904</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>1903</v>
-      </c>
+        <v>1948</v>
+      </c>
+      <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
@@ -4173,7 +4171,7 @@
     </row>
     <row r="120" customHeight="1" ht="20">
       <c r="A120" s="5" t="n">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B120" s="5" t="n">
         <v>26</v>
@@ -4185,7 +4183,7 @@
         <v>2</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
@@ -4205,7 +4203,7 @@
     </row>
     <row r="121" customHeight="1" ht="20">
       <c r="A121" s="5" t="n">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>26</v>
@@ -4217,7 +4215,7 @@
         <v>2</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
@@ -4237,7 +4235,7 @@
     </row>
     <row r="122" customHeight="1" ht="20">
       <c r="A122" s="5" t="n">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B122" s="5" t="n">
         <v>26</v>
@@ -4246,12 +4244,14 @@
         <v>942</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1945</v>
-      </c>
-      <c r="F122" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>22</v>
+      </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
@@ -4269,23 +4269,21 @@
     </row>
     <row r="123" customHeight="1" ht="20">
       <c r="A123" s="5" t="n">
-        <v>1647</v>
+        <v>1681</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>26</v>
+        <v>321</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>942</v>
+        <v>862</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>22</v>
-      </c>
+        <v>1147</v>
+      </c>
+      <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -4303,19 +4301,19 @@
     </row>
     <row r="124" customHeight="1" ht="20">
       <c r="A124" s="5" t="n">
-        <v>1681</v>
+        <v>1701</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>862</v>
+        <v>822</v>
       </c>
       <c r="D124" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1147</v>
+        <v>341</v>
       </c>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
@@ -4335,19 +4333,19 @@
     </row>
     <row r="125" customHeight="1" ht="20">
       <c r="A125" s="5" t="n">
-        <v>1701</v>
+        <v>1722</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>822</v>
+        <v>1002</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>341</v>
+        <v>26</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
@@ -4367,21 +4365,23 @@
     </row>
     <row r="126" customHeight="1" ht="20">
       <c r="A126" s="5" t="n">
-        <v>1722</v>
+        <v>1921</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>48</v>
+        <v>281</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>1002</v>
+        <v>822</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F126" s="5"/>
+        <v>2164</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>2163</v>
+      </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -4399,22 +4399,22 @@
     </row>
     <row r="127" customHeight="1" ht="20">
       <c r="A127" s="5" t="n">
-        <v>1921</v>
+        <v>2141</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>822</v>
+        <v>1202</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2164</v>
+        <v>2304</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>2163</v>
+        <v>2303</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
@@ -4433,23 +4433,21 @@
     </row>
     <row r="128" customHeight="1" ht="20">
       <c r="A128" s="5" t="n">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>261</v>
+        <v>441</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>1202</v>
+        <v>1182</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2304</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>2303</v>
-      </c>
+        <v>2064</v>
+      </c>
+      <c r="F128" s="5"/>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -4467,21 +4465,23 @@
     </row>
     <row r="129" customHeight="1" ht="20">
       <c r="A129" s="5" t="n">
-        <v>2144</v>
+        <v>1883</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>441</v>
+        <v>281</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>1182</v>
+        <v>822</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F129" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>24</v>
+      </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="130" customHeight="1" ht="20">
       <c r="A130" s="5" t="n">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>281</v>
+        <v>50</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>822</v>
+        <v>1042</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E130" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F130" s="5" t="n">
         <v>22</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
@@ -4533,22 +4533,22 @@
     </row>
     <row r="131" customHeight="1" ht="20">
       <c r="A131" s="5" t="n">
-        <v>1884</v>
+        <v>1942</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>50</v>
+        <v>421</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1042</v>
+        <v>1102</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>24</v>
+        <v>2184</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>22</v>
+        <v>2183</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="132" customHeight="1" ht="20">
       <c r="A132" s="5" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B132" s="5" t="n">
         <v>421</v>
@@ -4576,14 +4576,12 @@
         <v>1102</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2184</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>2183</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F132" s="5"/>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -4601,19 +4599,19 @@
     </row>
     <row r="133" customHeight="1" ht="20">
       <c r="A133" s="5" t="n">
-        <v>1943</v>
+        <v>2322</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1102</v>
+        <v>1222</v>
       </c>
       <c r="D133" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>81</v>
+        <v>1583</v>
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
@@ -4633,19 +4631,19 @@
     </row>
     <row r="134" customHeight="1" ht="20">
       <c r="A134" s="5" t="n">
-        <v>2322</v>
+        <v>2501</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1583</v>
+        <v>26</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
@@ -4665,21 +4663,23 @@
     </row>
     <row r="135" customHeight="1" ht="20">
       <c r="A135" s="5" t="n">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F135" s="5"/>
+        <v>2443</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>1190</v>
+      </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
@@ -4697,22 +4697,22 @@
     </row>
     <row r="136" customHeight="1" ht="20">
       <c r="A136" s="5" t="n">
-        <v>2401</v>
+        <v>2461</v>
       </c>
       <c r="B136" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>1222</v>
+        <v>1302</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2443</v>
+        <v>33</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>1190</v>
+        <v>2191</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -4731,22 +4731,22 @@
     </row>
     <row r="137" customHeight="1" ht="20">
       <c r="A137" s="5" t="n">
-        <v>2461</v>
+        <v>2841</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>461</v>
+        <v>41</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1302</v>
+        <v>1403</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>33</v>
+        <v>585</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>2191</v>
+        <v>584</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="138" customHeight="1" ht="20">
       <c r="A138" s="5" t="n">
-        <v>2841</v>
+        <v>2466</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>41</v>
+        <v>481</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1403</v>
+        <v>1282</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>585</v>
+        <v>728</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>584</v>
+        <v>727</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -4799,23 +4799,21 @@
     </row>
     <row r="139" customHeight="1" ht="20">
       <c r="A139" s="5" t="n">
-        <v>2466</v>
+        <v>2481</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1282</v>
+        <v>1302</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>728</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>727</v>
-      </c>
+        <v>2503</v>
+      </c>
+      <c r="F139" s="5"/>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -4833,19 +4831,19 @@
     </row>
     <row r="140" customHeight="1" ht="20">
       <c r="A140" s="5" t="n">
-        <v>2481</v>
+        <v>2621</v>
       </c>
       <c r="B140" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1302</v>
+        <v>1222</v>
       </c>
       <c r="D140" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2503</v>
+        <v>2623</v>
       </c>
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
@@ -4865,21 +4863,23 @@
     </row>
     <row r="141" customHeight="1" ht="20">
       <c r="A141" s="5" t="n">
-        <v>2621</v>
+        <v>2641</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1222</v>
+        <v>1282</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2623</v>
-      </c>
-      <c r="F141" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>83</v>
+      </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -4897,23 +4897,21 @@
     </row>
     <row r="142" customHeight="1" ht="20">
       <c r="A142" s="5" t="n">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>481</v>
+        <v>47</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>1282</v>
+        <v>1362</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>463</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>83</v>
-      </c>
+        <v>2643</v>
+      </c>
+      <c r="F142" s="5"/>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -4931,21 +4929,23 @@
     </row>
     <row r="143" customHeight="1" ht="20">
       <c r="A143" s="5" t="n">
-        <v>2642</v>
+        <v>2764</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1362</v>
+        <v>1342</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2643</v>
-      </c>
-      <c r="F143" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>22</v>
+      </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="144" customHeight="1" ht="20">
       <c r="A144" s="5" t="n">
-        <v>2764</v>
+        <v>3081</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>27</v>
+        <v>481</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>1342</v>
+        <v>1282</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>24</v>
+        <v>585</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -4997,53 +4997,49 @@
     </row>
     <row r="145" customHeight="1" ht="20">
       <c r="A145" s="5" t="n">
-        <v>3081</v>
+        <v>3842</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>481</v>
+        <v>681</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1282</v>
+        <v>1647</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>584</v>
-      </c>
+        <v>3464</v>
+      </c>
+      <c r="F145" s="5"/>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L145" s="7"/>
-      <c r="M145" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N145" s="7" t="n">
-        <v>45831.8349884259</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L145" s="7" t="n">
+        <v>45895.6354861111</v>
+      </c>
+      <c r="M145" s="6"/>
+      <c r="N145" s="7"/>
     </row>
     <row r="146" customHeight="1" ht="20">
       <c r="A146" s="5" t="n">
-        <v>3842</v>
+        <v>2881</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>681</v>
+        <v>501</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>1647</v>
+        <v>1322</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>3464</v>
+        <v>1943</v>
       </c>
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
@@ -5051,31 +5047,35 @@
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L146" s="7" t="n">
-        <v>45895.6354861111</v>
-      </c>
-      <c r="M146" s="6"/>
-      <c r="N146" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L146" s="7"/>
+      <c r="M146" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N146" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="147" customHeight="1" ht="20">
       <c r="A147" s="5" t="n">
-        <v>2881</v>
+        <v>2901</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>501</v>
+        <v>25</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>1322</v>
+        <v>1383</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1943</v>
-      </c>
-      <c r="F147" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
@@ -5093,56 +5093,56 @@
     </row>
     <row r="148" customHeight="1" ht="20">
       <c r="A148" s="5" t="n">
-        <v>2901</v>
+        <v>3423</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>25</v>
+        <v>541</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>1383</v>
+        <v>1503</v>
       </c>
       <c r="D148" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>585</v>
+        <v>3066</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>584</v>
+        <v>3067</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L148" s="7"/>
       <c r="M148" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N148" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="149" customHeight="1" ht="20">
       <c r="A149" s="5" t="n">
-        <v>3423</v>
+        <v>3861</v>
       </c>
       <c r="B149" s="5" t="n">
         <v>541</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1503</v>
+        <v>1664</v>
       </c>
       <c r="D149" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3066</v>
+        <v>3484</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>3067</v>
+        <v>3483</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
@@ -5151,33 +5151,29 @@
       <c r="K149" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L149" s="7"/>
-      <c r="M149" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N149" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L149" s="7" t="n">
+        <v>45903.5766435185</v>
+      </c>
+      <c r="M149" s="6"/>
+      <c r="N149" s="7"/>
     </row>
     <row r="150" customHeight="1" ht="20">
       <c r="A150" s="5" t="n">
-        <v>3861</v>
+        <v>3981</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>541</v>
+        <v>722</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>1664</v>
+        <v>1684</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3484</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>3483</v>
-      </c>
+        <v>3603</v>
+      </c>
+      <c r="F150" s="5"/>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
@@ -5186,28 +5182,30 @@
         <v>15</v>
       </c>
       <c r="L150" s="7" t="n">
-        <v>45903.5766435185</v>
+        <v>45938.6115740741</v>
       </c>
       <c r="M150" s="6"/>
       <c r="N150" s="7"/>
     </row>
     <row r="151" customHeight="1" ht="20">
       <c r="A151" s="5" t="n">
-        <v>3981</v>
+        <v>4181</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>722</v>
+        <v>762</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1684</v>
+        <v>1724</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>3603</v>
-      </c>
-      <c r="F151" s="5"/>
+        <v>3767</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>3768</v>
+      </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
@@ -5216,61 +5214,63 @@
         <v>15</v>
       </c>
       <c r="L151" s="7" t="n">
-        <v>45938.6115740741</v>
+        <v>45994.6961805556</v>
       </c>
       <c r="M151" s="6"/>
       <c r="N151" s="7"/>
     </row>
     <row r="152" customHeight="1" ht="20">
       <c r="A152" s="5" t="n">
-        <v>4181</v>
+        <v>42</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>762</v>
+        <v>1</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>1724</v>
+        <v>182</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>3767</v>
+        <v>503</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>3768</v>
+        <v>504</v>
       </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L152" s="7" t="n">
-        <v>45994.6961805556</v>
-      </c>
-      <c r="M152" s="6"/>
-      <c r="N152" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L152" s="7"/>
+      <c r="M152" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N152" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="153" customHeight="1" ht="20">
       <c r="A153" s="5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>503</v>
+        <v>583</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>504</v>
+        <v>27</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
@@ -5289,7 +5289,7 @@
     </row>
     <row r="154" customHeight="1" ht="20">
       <c r="A154" s="5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B154" s="5" t="n">
         <v>48</v>
@@ -5298,13 +5298,13 @@
         <v>202</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>583</v>
+        <v>543</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>27</v>
+        <v>544</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
@@ -5323,22 +5323,22 @@
     </row>
     <row r="155" customHeight="1" ht="20">
       <c r="A155" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>543</v>
+        <v>585</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>544</v>
+        <v>584</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
@@ -5357,23 +5357,21 @@
     </row>
     <row r="156" customHeight="1" ht="20">
       <c r="A156" s="5" t="n">
-        <v>52</v>
+        <v>421</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F156" s="5" t="n">
-        <v>584</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="F156" s="5"/>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
@@ -5391,21 +5389,23 @@
     </row>
     <row r="157" customHeight="1" ht="20">
       <c r="A157" s="5" t="n">
-        <v>421</v>
+        <v>146</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>401</v>
-      </c>
-      <c r="F157" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>463</v>
+      </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
@@ -5423,22 +5423,22 @@
     </row>
     <row r="158" customHeight="1" ht="20">
       <c r="A158" s="5" t="n">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="D158" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>83</v>
+        <v>714</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>463</v>
+        <v>715</v>
       </c>
       <c r="G158" s="5"/>
       <c r="H158" s="5"/>
@@ -5457,22 +5457,22 @@
     </row>
     <row r="159" customHeight="1" ht="20">
       <c r="A159" s="5" t="n">
-        <v>182</v>
+        <v>347</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="D159" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>714</v>
+        <v>24</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>715</v>
+        <v>22</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
@@ -5491,23 +5491,21 @@
     </row>
     <row r="160" customHeight="1" ht="20">
       <c r="A160" s="5" t="n">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>626</v>
-      </c>
-      <c r="F160" s="5" t="n">
-        <v>627</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="F160" s="5"/>
       <c r="G160" s="5"/>
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
@@ -5525,22 +5523,22 @@
     </row>
     <row r="161" customHeight="1" ht="20">
       <c r="A161" s="5" t="n">
-        <v>347</v>
+        <v>202</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>24</v>
+        <v>774</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>22</v>
+        <v>784</v>
       </c>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
@@ -5559,19 +5557,19 @@
     </row>
     <row r="162" customHeight="1" ht="20">
       <c r="A162" s="5" t="n">
-        <v>194</v>
+        <v>401</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="D162" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>773</v>
+        <v>381</v>
       </c>
       <c r="F162" s="5"/>
       <c r="G162" s="5"/>
@@ -5591,22 +5589,22 @@
     </row>
     <row r="163" customHeight="1" ht="20">
       <c r="A163" s="5" t="n">
-        <v>202</v>
+        <v>482</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="D163" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>774</v>
+        <v>996</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>784</v>
+        <v>995</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
@@ -5625,21 +5623,23 @@
     </row>
     <row r="164" customHeight="1" ht="20">
       <c r="A164" s="5" t="n">
-        <v>401</v>
+        <v>604</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>363</v>
+        <v>502</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>381</v>
-      </c>
-      <c r="F164" s="5"/>
+        <v>142</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>141</v>
+      </c>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
@@ -5657,22 +5657,22 @@
     </row>
     <row r="165" customHeight="1" ht="20">
       <c r="A165" s="5" t="n">
-        <v>482</v>
+        <v>606</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="D165" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>996</v>
+        <v>844</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>995</v>
+        <v>91</v>
       </c>
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
@@ -5691,23 +5691,21 @@
     </row>
     <row r="166" customHeight="1" ht="20">
       <c r="A166" s="5" t="n">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>141</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="F166" s="5"/>
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
       <c r="I166" s="5"/>
@@ -5725,23 +5723,21 @@
     </row>
     <row r="167" customHeight="1" ht="20">
       <c r="A167" s="5" t="n">
-        <v>606</v>
+        <v>722</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>844</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>91</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="F167" s="5"/>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
@@ -5759,19 +5755,19 @@
     </row>
     <row r="168" customHeight="1" ht="20">
       <c r="A168" s="5" t="n">
-        <v>608</v>
+        <v>723</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="D168" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>85</v>
+        <v>664</v>
       </c>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
@@ -5791,7 +5787,7 @@
     </row>
     <row r="169" customHeight="1" ht="20">
       <c r="A169" s="5" t="n">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B169" s="5" t="n">
         <v>181</v>
@@ -5803,7 +5799,7 @@
         <v>2</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>743</v>
+        <v>1403</v>
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5"/>
@@ -5823,21 +5819,23 @@
     </row>
     <row r="170" customHeight="1" ht="20">
       <c r="A170" s="5" t="n">
-        <v>723</v>
+        <v>741</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>664</v>
-      </c>
-      <c r="F170" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>625</v>
+      </c>
       <c r="G170" s="5"/>
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
@@ -5855,7 +5853,7 @@
     </row>
     <row r="171" customHeight="1" ht="20">
       <c r="A171" s="5" t="n">
-        <v>724</v>
+        <v>801</v>
       </c>
       <c r="B171" s="5" t="n">
         <v>181</v>
@@ -5867,7 +5865,7 @@
         <v>2</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1403</v>
+        <v>1463</v>
       </c>
       <c r="F171" s="5"/>
       <c r="G171" s="5"/>
@@ -5887,22 +5885,22 @@
     </row>
     <row r="172" customHeight="1" ht="20">
       <c r="A172" s="5" t="n">
-        <v>741</v>
+        <v>962</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>201</v>
+        <v>25</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>522</v>
+        <v>622</v>
       </c>
       <c r="D172" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>624</v>
+        <v>261</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G172" s="5"/>
       <c r="H172" s="5"/>
@@ -5921,21 +5919,23 @@
     </row>
     <row r="173" customHeight="1" ht="20">
       <c r="A173" s="5" t="n">
-        <v>801</v>
+        <v>1161</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>502</v>
+        <v>642</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1463</v>
-      </c>
-      <c r="F173" s="5"/>
+        <v>963</v>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>964</v>
+      </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
@@ -5953,23 +5953,21 @@
     </row>
     <row r="174" customHeight="1" ht="20">
       <c r="A174" s="5" t="n">
-        <v>962</v>
+        <v>1003</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>622</v>
+        <v>562</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="F174" s="5" t="n">
-        <v>623</v>
-      </c>
+        <v>1463</v>
+      </c>
+      <c r="F174" s="5"/>
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
@@ -5987,22 +5985,22 @@
     </row>
     <row r="175" customHeight="1" ht="20">
       <c r="A175" s="5" t="n">
-        <v>1161</v>
+        <v>1042</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>642</v>
+        <v>582</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>963</v>
+        <v>221</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>964</v>
+        <v>1131</v>
       </c>
       <c r="G175" s="5"/>
       <c r="H175" s="5"/>
@@ -6021,19 +6019,19 @@
     </row>
     <row r="176" customHeight="1" ht="20">
       <c r="A176" s="5" t="n">
-        <v>1003</v>
+        <v>1721</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>51</v>
+        <v>281</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>562</v>
+        <v>822</v>
       </c>
       <c r="D176" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>1463</v>
+        <v>26</v>
       </c>
       <c r="F176" s="5"/>
       <c r="G176" s="5"/>
@@ -6053,23 +6051,21 @@
     </row>
     <row r="177" customHeight="1" ht="20">
       <c r="A177" s="5" t="n">
-        <v>1042</v>
+        <v>1181</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>582</v>
+        <v>722</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="F177" s="5" t="n">
-        <v>1131</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F177" s="5"/>
       <c r="G177" s="5"/>
       <c r="H177" s="5"/>
       <c r="I177" s="5"/>
@@ -6087,19 +6083,19 @@
     </row>
     <row r="178" customHeight="1" ht="20">
       <c r="A178" s="5" t="n">
-        <v>1721</v>
+        <v>1245</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>281</v>
+        <v>101</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>822</v>
+        <v>742</v>
       </c>
       <c r="D178" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>26</v>
+        <v>1052</v>
       </c>
       <c r="F178" s="5"/>
       <c r="G178" s="5"/>
@@ -6119,21 +6115,23 @@
     </row>
     <row r="179" customHeight="1" ht="20">
       <c r="A179" s="5" t="n">
-        <v>1181</v>
+        <v>1261</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F179" s="5"/>
+        <v>1684</v>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>1683</v>
+      </c>
       <c r="G179" s="5"/>
       <c r="H179" s="5"/>
       <c r="I179" s="5"/>
@@ -6151,19 +6149,19 @@
     </row>
     <row r="180" customHeight="1" ht="20">
       <c r="A180" s="5" t="n">
-        <v>1245</v>
+        <v>1662</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>742</v>
+        <v>962</v>
       </c>
       <c r="D180" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1052</v>
+        <v>1964</v>
       </c>
       <c r="F180" s="5"/>
       <c r="G180" s="5"/>
@@ -6183,22 +6181,22 @@
     </row>
     <row r="181" customHeight="1" ht="20">
       <c r="A181" s="5" t="n">
-        <v>1261</v>
+        <v>1302</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>742</v>
+        <v>642</v>
       </c>
       <c r="D181" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1684</v>
+        <v>1704</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>1683</v>
+        <v>1703</v>
       </c>
       <c r="G181" s="5"/>
       <c r="H181" s="5"/>
@@ -6217,7 +6215,7 @@
     </row>
     <row r="182" customHeight="1" ht="20">
       <c r="A182" s="5" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B182" s="5" t="n">
         <v>381</v>
@@ -6226,12 +6224,14 @@
         <v>962</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1964</v>
-      </c>
-      <c r="F182" s="5"/>
+        <v>1965</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>1963</v>
+      </c>
       <c r="G182" s="5"/>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
@@ -6249,23 +6249,21 @@
     </row>
     <row r="183" customHeight="1" ht="20">
       <c r="A183" s="5" t="n">
-        <v>1302</v>
+        <v>1341</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>642</v>
+        <v>802</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1704</v>
-      </c>
-      <c r="F183" s="5" t="n">
-        <v>1703</v>
-      </c>
+        <v>1783</v>
+      </c>
+      <c r="F183" s="5"/>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
@@ -6283,23 +6281,21 @@
     </row>
     <row r="184" customHeight="1" ht="20">
       <c r="A184" s="5" t="n">
-        <v>1663</v>
+        <v>1381</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>381</v>
+        <v>50</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>962</v>
+        <v>802</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1965</v>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>1963</v>
-      </c>
+        <v>1823</v>
+      </c>
+      <c r="F184" s="5"/>
       <c r="G184" s="5"/>
       <c r="H184" s="5"/>
       <c r="I184" s="5"/>
@@ -6317,21 +6313,23 @@
     </row>
     <row r="185" customHeight="1" ht="20">
       <c r="A185" s="5" t="n">
-        <v>1341</v>
+        <v>1421</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>802</v>
+        <v>642</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1783</v>
-      </c>
-      <c r="F185" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G185" s="5"/>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
@@ -6349,21 +6347,23 @@
     </row>
     <row r="186" customHeight="1" ht="20">
       <c r="A186" s="5" t="n">
-        <v>1381</v>
+        <v>1442</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>50</v>
+        <v>281</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>1823</v>
-      </c>
-      <c r="F186" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>625</v>
+      </c>
       <c r="G186" s="5"/>
       <c r="H186" s="5"/>
       <c r="I186" s="5"/>
@@ -6381,23 +6381,21 @@
     </row>
     <row r="187" customHeight="1" ht="20">
       <c r="A187" s="5" t="n">
-        <v>1421</v>
+        <v>2046</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>642</v>
+        <v>822</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>584</v>
-      </c>
+        <v>1404</v>
+      </c>
+      <c r="F187" s="5"/>
       <c r="G187" s="5"/>
       <c r="H187" s="5"/>
       <c r="I187" s="5"/>
@@ -6415,25 +6413,29 @@
     </row>
     <row r="188" customHeight="1" ht="20">
       <c r="A188" s="5" t="n">
-        <v>1442</v>
+        <v>1521</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>822</v>
+        <v>662</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>624</v>
+        <v>1883</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>625</v>
-      </c>
-      <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
+        <v>1886</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>1884</v>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>1885</v>
+      </c>
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
       <c r="K188" s="6" t="s">
@@ -6449,21 +6451,23 @@
     </row>
     <row r="189" customHeight="1" ht="20">
       <c r="A189" s="5" t="n">
-        <v>2046</v>
+        <v>1541</v>
       </c>
       <c r="B189" s="5" t="n">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>822</v>
+        <v>662</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1404</v>
-      </c>
-      <c r="F189" s="5"/>
+        <v>1763</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>1764</v>
+      </c>
       <c r="G189" s="5"/>
       <c r="H189" s="5"/>
       <c r="I189" s="5"/>
@@ -6481,29 +6485,25 @@
     </row>
     <row r="190" customHeight="1" ht="20">
       <c r="A190" s="5" t="n">
-        <v>1521</v>
+        <v>1761</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>662</v>
+        <v>822</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>1883</v>
+        <v>585</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>1886</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>1884</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>1885</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="G190" s="5"/>
+      <c r="H190" s="5"/>
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
       <c r="K190" s="6" t="s">
@@ -6519,22 +6519,22 @@
     </row>
     <row r="191" customHeight="1" ht="20">
       <c r="A191" s="5" t="n">
-        <v>1541</v>
+        <v>1801</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>662</v>
+        <v>1022</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1763</v>
+        <v>121</v>
       </c>
       <c r="F191" s="5" t="n">
-        <v>1764</v>
+        <v>2043</v>
       </c>
       <c r="G191" s="5"/>
       <c r="H191" s="5"/>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="192" customHeight="1" ht="20">
       <c r="A192" s="5" t="n">
-        <v>1761</v>
+        <v>1842</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>281</v>
+        <v>50</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>822</v>
+        <v>1042</v>
       </c>
       <c r="D192" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>585</v>
+        <v>1164</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>584</v>
+        <v>1163</v>
       </c>
       <c r="G192" s="5"/>
       <c r="H192" s="5"/>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="193" customHeight="1" ht="20">
       <c r="A193" s="5" t="n">
-        <v>1801</v>
+        <v>1881</v>
       </c>
       <c r="B193" s="5" t="n">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>1022</v>
+        <v>1042</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>121</v>
+        <v>1523</v>
       </c>
       <c r="F193" s="5" t="n">
-        <v>2043</v>
+        <v>1524</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
@@ -6621,23 +6621,21 @@
     </row>
     <row r="194" customHeight="1" ht="20">
       <c r="A194" s="5" t="n">
-        <v>1842</v>
+        <v>2001</v>
       </c>
       <c r="B194" s="5" t="n">
-        <v>50</v>
+        <v>281</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>1042</v>
+        <v>822</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1164</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>1163</v>
-      </c>
+        <v>1143</v>
+      </c>
+      <c r="F194" s="5"/>
       <c r="G194" s="5"/>
       <c r="H194" s="5"/>
       <c r="I194" s="5"/>
@@ -6655,22 +6653,22 @@
     </row>
     <row r="195" customHeight="1" ht="20">
       <c r="A195" s="5" t="n">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="B195" s="5" t="n">
-        <v>50</v>
+        <v>281</v>
       </c>
       <c r="C195" s="5" t="n">
-        <v>1042</v>
+        <v>822</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>1523</v>
+        <v>2103</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>1524</v>
+        <v>91</v>
       </c>
       <c r="G195" s="5"/>
       <c r="H195" s="5"/>
@@ -6689,7 +6687,7 @@
     </row>
     <row r="196" customHeight="1" ht="20">
       <c r="A196" s="5" t="n">
-        <v>2001</v>
+        <v>2045</v>
       </c>
       <c r="B196" s="5" t="n">
         <v>281</v>
@@ -6698,10 +6696,10 @@
         <v>822</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1143</v>
+        <v>1424</v>
       </c>
       <c r="F196" s="5"/>
       <c r="G196" s="5"/>
@@ -6721,22 +6719,22 @@
     </row>
     <row r="197" customHeight="1" ht="20">
       <c r="A197" s="5" t="n">
-        <v>1885</v>
+        <v>2061</v>
       </c>
       <c r="B197" s="5" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>822</v>
+        <v>1122</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>2103</v>
+        <v>624</v>
       </c>
       <c r="F197" s="5" t="n">
-        <v>91</v>
+        <v>625</v>
       </c>
       <c r="G197" s="5"/>
       <c r="H197" s="5"/>
@@ -6755,21 +6753,23 @@
     </row>
     <row r="198" customHeight="1" ht="20">
       <c r="A198" s="5" t="n">
-        <v>2045</v>
+        <v>1944</v>
       </c>
       <c r="B198" s="5" t="n">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>822</v>
+        <v>1102</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="F198" s="5"/>
+        <v>2186</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>2185</v>
+      </c>
       <c r="G198" s="5"/>
       <c r="H198" s="5"/>
       <c r="I198" s="5"/>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="199" customHeight="1" ht="20">
       <c r="A199" s="5" t="n">
-        <v>2061</v>
+        <v>1945</v>
       </c>
       <c r="B199" s="5" t="n">
-        <v>301</v>
+        <v>421</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>1122</v>
+        <v>1102</v>
       </c>
       <c r="D199" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>624</v>
+        <v>2188</v>
       </c>
       <c r="F199" s="5" t="n">
-        <v>625</v>
+        <v>2187</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5"/>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="200" customHeight="1" ht="20">
       <c r="A200" s="5" t="n">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B200" s="5" t="n">
         <v>421</v>
@@ -6833,10 +6833,10 @@
         <v>1</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>2185</v>
+        <v>2190</v>
       </c>
       <c r="G200" s="5"/>
       <c r="H200" s="5"/>
@@ -6855,7 +6855,7 @@
     </row>
     <row r="201" customHeight="1" ht="20">
       <c r="A201" s="5" t="n">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="B201" s="5" t="n">
         <v>421</v>
@@ -6867,10 +6867,10 @@
         <v>1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>2188</v>
+        <v>33</v>
       </c>
       <c r="F201" s="5" t="n">
-        <v>2187</v>
+        <v>2191</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5"/>
@@ -6889,22 +6889,22 @@
     </row>
     <row r="202" customHeight="1" ht="20">
       <c r="A202" s="5" t="n">
-        <v>1946</v>
+        <v>2463</v>
       </c>
       <c r="B202" s="5" t="n">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>1102</v>
+        <v>1302</v>
       </c>
       <c r="D202" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>2189</v>
+        <v>2185</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
@@ -6923,22 +6923,22 @@
     </row>
     <row r="203" customHeight="1" ht="20">
       <c r="A203" s="5" t="n">
-        <v>1947</v>
+        <v>2465</v>
       </c>
       <c r="B203" s="5" t="n">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>1102</v>
+        <v>1302</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>33</v>
+        <v>2184</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>2191</v>
+        <v>2183</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
@@ -6957,22 +6957,22 @@
     </row>
     <row r="204" customHeight="1" ht="20">
       <c r="A204" s="5" t="n">
-        <v>2463</v>
+        <v>2521</v>
       </c>
       <c r="B204" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>1302</v>
+        <v>1322</v>
       </c>
       <c r="D204" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>2185</v>
+        <v>2543</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>2186</v>
+        <v>2544</v>
       </c>
       <c r="G204" s="5"/>
       <c r="H204" s="5"/>
@@ -6991,23 +6991,21 @@
     </row>
     <row r="205" customHeight="1" ht="20">
       <c r="A205" s="5" t="n">
-        <v>2465</v>
+        <v>2324</v>
       </c>
       <c r="B205" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>1302</v>
+        <v>1222</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>2184</v>
-      </c>
-      <c r="F205" s="5" t="n">
-        <v>2183</v>
-      </c>
+        <v>2363</v>
+      </c>
+      <c r="F205" s="5"/>
       <c r="G205" s="5"/>
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
@@ -7025,22 +7023,22 @@
     </row>
     <row r="206" customHeight="1" ht="20">
       <c r="A206" s="5" t="n">
-        <v>2521</v>
+        <v>2341</v>
       </c>
       <c r="B206" s="5" t="n">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>1322</v>
+        <v>1162</v>
       </c>
       <c r="D206" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>2543</v>
+        <v>2384</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>2544</v>
+        <v>2383</v>
       </c>
       <c r="G206" s="5"/>
       <c r="H206" s="5"/>
@@ -7059,7 +7057,7 @@
     </row>
     <row r="207" customHeight="1" ht="20">
       <c r="A207" s="5" t="n">
-        <v>2324</v>
+        <v>2362</v>
       </c>
       <c r="B207" s="5" t="n">
         <v>461</v>
@@ -7071,7 +7069,7 @@
         <v>2</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>2363</v>
+        <v>2064</v>
       </c>
       <c r="F207" s="5"/>
       <c r="G207" s="5"/>
@@ -7091,23 +7089,21 @@
     </row>
     <row r="208" customHeight="1" ht="20">
       <c r="A208" s="5" t="n">
-        <v>2341</v>
+        <v>2441</v>
       </c>
       <c r="B208" s="5" t="n">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>2384</v>
-      </c>
-      <c r="F208" s="5" t="n">
-        <v>2383</v>
-      </c>
+        <v>2483</v>
+      </c>
+      <c r="F208" s="5"/>
       <c r="G208" s="5"/>
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
@@ -7125,21 +7121,23 @@
     </row>
     <row r="209" customHeight="1" ht="20">
       <c r="A209" s="5" t="n">
-        <v>2362</v>
+        <v>2541</v>
       </c>
       <c r="B209" s="5" t="n">
-        <v>461</v>
+        <v>27</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>1222</v>
+        <v>1342</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F209" s="5"/>
+        <v>2563</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>2564</v>
+      </c>
       <c r="G209" s="5"/>
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
@@ -7157,19 +7155,19 @@
     </row>
     <row r="210" customHeight="1" ht="20">
       <c r="A210" s="5" t="n">
-        <v>2441</v>
+        <v>2582</v>
       </c>
       <c r="B210" s="5" t="n">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>1222</v>
+        <v>1162</v>
       </c>
       <c r="D210" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>2483</v>
+        <v>1563</v>
       </c>
       <c r="F210" s="5"/>
       <c r="G210" s="5"/>
@@ -7189,22 +7187,22 @@
     </row>
     <row r="211" customHeight="1" ht="20">
       <c r="A211" s="5" t="n">
-        <v>2541</v>
+        <v>2661</v>
       </c>
       <c r="B211" s="5" t="n">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>1342</v>
+        <v>1202</v>
       </c>
       <c r="D211" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>2563</v>
+        <v>2664</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>2564</v>
+        <v>2663</v>
       </c>
       <c r="G211" s="5"/>
       <c r="H211" s="5"/>
@@ -7223,21 +7221,23 @@
     </row>
     <row r="212" customHeight="1" ht="20">
       <c r="A212" s="5" t="n">
-        <v>2582</v>
+        <v>2702</v>
       </c>
       <c r="B212" s="5" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>1162</v>
+        <v>1342</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F212" s="5"/>
+        <v>587</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>586</v>
+      </c>
       <c r="G212" s="5"/>
       <c r="H212" s="5"/>
       <c r="I212" s="5"/>
@@ -7255,22 +7255,22 @@
     </row>
     <row r="213" customHeight="1" ht="20">
       <c r="A213" s="5" t="n">
-        <v>2661</v>
+        <v>2741</v>
       </c>
       <c r="B213" s="5" t="n">
-        <v>261</v>
+        <v>421</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>1202</v>
+        <v>1363</v>
       </c>
       <c r="D213" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>2664</v>
+        <v>624</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>2663</v>
+        <v>625</v>
       </c>
       <c r="G213" s="5"/>
       <c r="H213" s="5"/>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="214" customHeight="1" ht="20">
       <c r="A214" s="5" t="n">
-        <v>2702</v>
+        <v>3101</v>
       </c>
       <c r="B214" s="5" t="n">
-        <v>27</v>
+        <v>481</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>1342</v>
+        <v>1282</v>
       </c>
       <c r="D214" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>587</v>
+        <v>2884</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>586</v>
+        <v>2883</v>
       </c>
       <c r="G214" s="5"/>
       <c r="H214" s="5"/>
@@ -7323,23 +7323,21 @@
     </row>
     <row r="215" customHeight="1" ht="20">
       <c r="A215" s="5" t="n">
-        <v>2741</v>
+        <v>2801</v>
       </c>
       <c r="B215" s="5" t="n">
-        <v>421</v>
+        <v>25</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>1363</v>
+        <v>1383</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="F215" s="5" t="n">
-        <v>625</v>
-      </c>
+        <v>2743</v>
+      </c>
+      <c r="F215" s="5"/>
       <c r="G215" s="5"/>
       <c r="H215" s="5"/>
       <c r="I215" s="5"/>
@@ -7357,23 +7355,21 @@
     </row>
     <row r="216" customHeight="1" ht="20">
       <c r="A216" s="5" t="n">
-        <v>3101</v>
+        <v>2822</v>
       </c>
       <c r="B216" s="5" t="n">
-        <v>481</v>
+        <v>261</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>1282</v>
+        <v>1202</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>2884</v>
-      </c>
-      <c r="F216" s="5" t="n">
-        <v>2883</v>
-      </c>
+        <v>2523</v>
+      </c>
+      <c r="F216" s="5"/>
       <c r="G216" s="5"/>
       <c r="H216" s="5"/>
       <c r="I216" s="5"/>
@@ -7391,19 +7387,19 @@
     </row>
     <row r="217" customHeight="1" ht="20">
       <c r="A217" s="5" t="n">
-        <v>2801</v>
+        <v>2823</v>
       </c>
       <c r="B217" s="5" t="n">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>1383</v>
+        <v>1202</v>
       </c>
       <c r="D217" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>2743</v>
+        <v>2323</v>
       </c>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
@@ -7423,21 +7419,23 @@
     </row>
     <row r="218" customHeight="1" ht="20">
       <c r="A218" s="5" t="n">
-        <v>2822</v>
+        <v>2842</v>
       </c>
       <c r="B218" s="5" t="n">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>1202</v>
+        <v>1342</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>2523</v>
-      </c>
-      <c r="F218" s="5"/>
+        <v>2764</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>2783</v>
+      </c>
       <c r="G218" s="5"/>
       <c r="H218" s="5"/>
       <c r="I218" s="5"/>
@@ -7455,21 +7453,23 @@
     </row>
     <row r="219" customHeight="1" ht="20">
       <c r="A219" s="5" t="n">
-        <v>2823</v>
+        <v>3021</v>
       </c>
       <c r="B219" s="5" t="n">
-        <v>261</v>
+        <v>501</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>1202</v>
+        <v>1322</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>2323</v>
-      </c>
-      <c r="F219" s="5"/>
+        <v>1023</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>1024</v>
+      </c>
       <c r="G219" s="5"/>
       <c r="H219" s="5"/>
       <c r="I219" s="5"/>
@@ -7487,22 +7487,22 @@
     </row>
     <row r="220" customHeight="1" ht="20">
       <c r="A220" s="5" t="n">
-        <v>2842</v>
+        <v>3381</v>
       </c>
       <c r="B220" s="5" t="n">
-        <v>27</v>
+        <v>521</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>1342</v>
+        <v>1423</v>
       </c>
       <c r="D220" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>2764</v>
+        <v>2963</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>2783</v>
+        <v>2964</v>
       </c>
       <c r="G220" s="5"/>
       <c r="H220" s="5"/>
@@ -7521,23 +7521,21 @@
     </row>
     <row r="221" customHeight="1" ht="20">
       <c r="A221" s="5" t="n">
-        <v>3021</v>
+        <v>3321</v>
       </c>
       <c r="B221" s="5" t="n">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>1322</v>
+        <v>1423</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>1023</v>
-      </c>
-      <c r="F221" s="5" t="n">
-        <v>1024</v>
-      </c>
+        <v>1583</v>
+      </c>
+      <c r="F221" s="5"/>
       <c r="G221" s="5"/>
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
@@ -7555,53 +7553,53 @@
     </row>
     <row r="222" customHeight="1" ht="20">
       <c r="A222" s="5" t="n">
-        <v>3381</v>
+        <v>3401</v>
       </c>
       <c r="B222" s="5" t="n">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>1423</v>
+        <v>1503</v>
       </c>
       <c r="D222" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>2963</v>
+        <v>3003</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>2964</v>
+        <v>3023</v>
       </c>
       <c r="G222" s="5"/>
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
       <c r="K222" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L222" s="7"/>
       <c r="M222" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N222" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="223" customHeight="1" ht="20">
       <c r="A223" s="5" t="n">
-        <v>3321</v>
+        <v>3843</v>
       </c>
       <c r="B223" s="5" t="n">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>1423</v>
+        <v>1664</v>
       </c>
       <c r="D223" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>1583</v>
+        <v>3465</v>
       </c>
       <c r="F223" s="5"/>
       <c r="G223" s="5"/>
@@ -7609,19 +7607,17 @@
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
       <c r="K223" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L223" s="7"/>
-      <c r="M223" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N223" s="7" t="n">
-        <v>45831.8349884259</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L223" s="7" t="n">
+        <v>45896.2966550926</v>
+      </c>
+      <c r="M223" s="6"/>
+      <c r="N223" s="7"/>
     </row>
     <row r="224" customHeight="1" ht="20">
       <c r="A224" s="5" t="n">
-        <v>3401</v>
+        <v>3406</v>
       </c>
       <c r="B224" s="5" t="n">
         <v>541</v>
@@ -7633,10 +7629,10 @@
         <v>1</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>3003</v>
+        <v>3028</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>3023</v>
+        <v>3029</v>
       </c>
       <c r="G224" s="5"/>
       <c r="H224" s="5"/>
@@ -7655,19 +7651,19 @@
     </row>
     <row r="225" customHeight="1" ht="20">
       <c r="A225" s="5" t="n">
-        <v>3843</v>
+        <v>3961</v>
       </c>
       <c r="B225" s="5" t="n">
-        <v>541</v>
+        <v>722</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>1664</v>
+        <v>1684</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>3465</v>
+        <v>3589</v>
       </c>
       <c r="F225" s="5"/>
       <c r="G225" s="5"/>
@@ -7678,29 +7674,29 @@
         <v>15</v>
       </c>
       <c r="L225" s="7" t="n">
-        <v>45896.2966550926</v>
+        <v>45935.4751157407</v>
       </c>
       <c r="M225" s="6"/>
       <c r="N225" s="7"/>
     </row>
     <row r="226" customHeight="1" ht="20">
       <c r="A226" s="5" t="n">
-        <v>3406</v>
+        <v>4061</v>
       </c>
       <c r="B226" s="5" t="n">
-        <v>541</v>
+        <v>762</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>1503</v>
+        <v>1724</v>
       </c>
       <c r="D226" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>3028</v>
+        <v>3663</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>3029</v>
+        <v>3664</v>
       </c>
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
@@ -7709,31 +7705,31 @@
       <c r="K226" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L226" s="7"/>
-      <c r="M226" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N226" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L226" s="7" t="n">
+        <v>45964.6311342593</v>
+      </c>
+      <c r="M226" s="6"/>
+      <c r="N226" s="7"/>
     </row>
     <row r="227" customHeight="1" ht="20">
       <c r="A227" s="5" t="n">
-        <v>3961</v>
+        <v>4062</v>
       </c>
       <c r="B227" s="5" t="n">
-        <v>722</v>
+        <v>762</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>1684</v>
+        <v>1724</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>3589</v>
-      </c>
-      <c r="F227" s="5"/>
+        <v>584</v>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>585</v>
+      </c>
       <c r="G227" s="5"/>
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
@@ -7742,29 +7738,29 @@
         <v>15</v>
       </c>
       <c r="L227" s="7" t="n">
-        <v>45935.4751157407</v>
+        <v>45965.4697453704</v>
       </c>
       <c r="M227" s="6"/>
       <c r="N227" s="7"/>
     </row>
     <row r="228" customHeight="1" ht="20">
       <c r="A228" s="5" t="n">
-        <v>4061</v>
+        <v>4064</v>
       </c>
       <c r="B228" s="5" t="n">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>1724</v>
+        <v>1743</v>
       </c>
       <c r="D228" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>3663</v>
+        <v>3669</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>3664</v>
+        <v>3666</v>
       </c>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
@@ -7774,30 +7770,28 @@
         <v>15</v>
       </c>
       <c r="L228" s="7" t="n">
-        <v>45964.6311342593</v>
+        <v>45966.4389236111</v>
       </c>
       <c r="M228" s="6"/>
       <c r="N228" s="7"/>
     </row>
     <row r="229" customHeight="1" ht="20">
       <c r="A229" s="5" t="n">
-        <v>4062</v>
+        <v>4065</v>
       </c>
       <c r="B229" s="5" t="n">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>1724</v>
+        <v>1743</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>584</v>
-      </c>
-      <c r="F229" s="5" t="n">
-        <v>585</v>
-      </c>
+        <v>3670</v>
+      </c>
+      <c r="F229" s="5"/>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
@@ -7806,14 +7800,14 @@
         <v>15</v>
       </c>
       <c r="L229" s="7" t="n">
-        <v>45965.4697453704</v>
+        <v>45966.5908101852</v>
       </c>
       <c r="M229" s="6"/>
       <c r="N229" s="7"/>
     </row>
     <row r="230" customHeight="1" ht="20">
       <c r="A230" s="5" t="n">
-        <v>4064</v>
+        <v>4066</v>
       </c>
       <c r="B230" s="5" t="n">
         <v>781</v>
@@ -7822,14 +7816,12 @@
         <v>1743</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>3669</v>
-      </c>
-      <c r="F230" s="5" t="n">
-        <v>3666</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F230" s="5"/>
       <c r="G230" s="5"/>
       <c r="H230" s="5"/>
       <c r="I230" s="5"/>
@@ -7838,14 +7830,14 @@
         <v>15</v>
       </c>
       <c r="L230" s="7" t="n">
-        <v>45966.4389236111</v>
+        <v>45966.7075231481</v>
       </c>
       <c r="M230" s="6"/>
       <c r="N230" s="7"/>
     </row>
     <row r="231" customHeight="1" ht="20">
       <c r="A231" s="5" t="n">
-        <v>4065</v>
+        <v>4068</v>
       </c>
       <c r="B231" s="5" t="n">
         <v>781</v>
@@ -7854,12 +7846,14 @@
         <v>1743</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>3670</v>
-      </c>
-      <c r="F231" s="5"/>
+        <v>3676</v>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>3675</v>
+      </c>
       <c r="G231" s="5"/>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
@@ -7868,14 +7862,14 @@
         <v>15</v>
       </c>
       <c r="L231" s="7" t="n">
-        <v>45966.5908101852</v>
+        <v>45967.3274768519</v>
       </c>
       <c r="M231" s="6"/>
       <c r="N231" s="7"/>
     </row>
     <row r="232" customHeight="1" ht="20">
       <c r="A232" s="5" t="n">
-        <v>4066</v>
+        <v>4069</v>
       </c>
       <c r="B232" s="5" t="n">
         <v>781</v>
@@ -7884,12 +7878,14 @@
         <v>1743</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="F232" s="5"/>
+        <v>3678</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>3677</v>
+      </c>
       <c r="G232" s="5"/>
       <c r="H232" s="5"/>
       <c r="I232" s="5"/>
@@ -7898,14 +7894,14 @@
         <v>15</v>
       </c>
       <c r="L232" s="7" t="n">
-        <v>45966.7075231481</v>
+        <v>45967.4627314815</v>
       </c>
       <c r="M232" s="6"/>
       <c r="N232" s="7"/>
     </row>
     <row r="233" customHeight="1" ht="20">
       <c r="A233" s="5" t="n">
-        <v>4068</v>
+        <v>4070</v>
       </c>
       <c r="B233" s="5" t="n">
         <v>781</v>
@@ -7917,10 +7913,10 @@
         <v>1</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>3676</v>
+        <v>2203</v>
       </c>
       <c r="F233" s="5" t="n">
-        <v>3675</v>
+        <v>3679</v>
       </c>
       <c r="G233" s="5"/>
       <c r="H233" s="5"/>
@@ -7930,29 +7926,29 @@
         <v>15</v>
       </c>
       <c r="L233" s="7" t="n">
-        <v>45967.3274768519</v>
+        <v>45967.5829398148</v>
       </c>
       <c r="M233" s="6"/>
       <c r="N233" s="7"/>
     </row>
     <row r="234" customHeight="1" ht="20">
       <c r="A234" s="5" t="n">
-        <v>4069</v>
+        <v>4303</v>
       </c>
       <c r="B234" s="5" t="n">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>1743</v>
+        <v>1724</v>
       </c>
       <c r="D234" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>3678</v>
+        <v>3868</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>3677</v>
+        <v>3869</v>
       </c>
       <c r="G234" s="5"/>
       <c r="H234" s="5"/>
@@ -7962,29 +7958,29 @@
         <v>15</v>
       </c>
       <c r="L234" s="7" t="n">
-        <v>45967.4627314815</v>
+        <v>46014.8150231481</v>
       </c>
       <c r="M234" s="6"/>
       <c r="N234" s="7"/>
     </row>
     <row r="235" customHeight="1" ht="20">
       <c r="A235" s="5" t="n">
-        <v>4070</v>
+        <v>4321</v>
       </c>
       <c r="B235" s="5" t="n">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>1743</v>
+        <v>1763</v>
       </c>
       <c r="D235" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>2203</v>
+        <v>3888</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>3679</v>
+        <v>3884</v>
       </c>
       <c r="G235" s="5"/>
       <c r="H235" s="5"/>
@@ -7994,93 +7990,97 @@
         <v>15</v>
       </c>
       <c r="L235" s="7" t="n">
-        <v>45967.5829398148</v>
+        <v>46030.6246180556</v>
       </c>
       <c r="M235" s="6"/>
       <c r="N235" s="7"/>
     </row>
     <row r="236" customHeight="1" ht="20">
       <c r="A236" s="5" t="n">
-        <v>4303</v>
+        <v>41</v>
       </c>
       <c r="B236" s="5" t="n">
-        <v>762</v>
+        <v>1</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>1724</v>
+        <v>182</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>3868</v>
+        <v>485</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>3869</v>
+        <v>486</v>
       </c>
       <c r="G236" s="5"/>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
       <c r="K236" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L236" s="7" t="n">
-        <v>46014.8150231481</v>
-      </c>
-      <c r="M236" s="6"/>
-      <c r="N236" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L236" s="7"/>
+      <c r="M236" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N236" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="237" customHeight="1" ht="20">
       <c r="A237" s="5" t="n">
-        <v>4321</v>
+        <v>57</v>
       </c>
       <c r="B237" s="5" t="n">
-        <v>801</v>
+        <v>41</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>1763</v>
+        <v>242</v>
       </c>
       <c r="D237" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>3888</v>
+        <v>587</v>
       </c>
       <c r="F237" s="5" t="n">
-        <v>3884</v>
+        <v>586</v>
       </c>
       <c r="G237" s="5"/>
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
       <c r="K237" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L237" s="7" t="n">
-        <v>46030.6246180556</v>
-      </c>
-      <c r="M237" s="6"/>
-      <c r="N237" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L237" s="7"/>
+      <c r="M237" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N237" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="238" customHeight="1" ht="20">
       <c r="A238" s="5" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B238" s="5" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>485</v>
+        <v>624</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>486</v>
+        <v>625</v>
       </c>
       <c r="G238" s="5"/>
       <c r="H238" s="5"/>
@@ -8099,22 +8099,22 @@
     </row>
     <row r="239" customHeight="1" ht="20">
       <c r="A239" s="5" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B239" s="5" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="D239" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>587</v>
+        <v>261</v>
       </c>
       <c r="F239" s="5" t="n">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="G239" s="5"/>
       <c r="H239" s="5"/>
@@ -8133,23 +8133,21 @@
     </row>
     <row r="240" customHeight="1" ht="20">
       <c r="A240" s="5" t="n">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="B240" s="5" t="n">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>262</v>
+        <v>382</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="F240" s="5" t="n">
-        <v>625</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="F240" s="5"/>
       <c r="G240" s="5"/>
       <c r="H240" s="5"/>
       <c r="I240" s="5"/>
@@ -8167,22 +8165,22 @@
     </row>
     <row r="241" customHeight="1" ht="20">
       <c r="A241" s="5" t="n">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="B241" s="5" t="n">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>262</v>
+        <v>342</v>
       </c>
       <c r="D241" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>261</v>
+        <v>706</v>
       </c>
       <c r="F241" s="5" t="n">
-        <v>623</v>
+        <v>707</v>
       </c>
       <c r="G241" s="5"/>
       <c r="H241" s="5"/>
@@ -8201,19 +8199,19 @@
     </row>
     <row r="242" customHeight="1" ht="20">
       <c r="A242" s="5" t="n">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="B242" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>664</v>
+        <v>627</v>
       </c>
       <c r="F242" s="5"/>
       <c r="G242" s="5"/>
@@ -8233,22 +8231,22 @@
     </row>
     <row r="243" customHeight="1" ht="20">
       <c r="A243" s="5" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B243" s="5" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="D243" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="F243" s="5" t="n">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="G243" s="5"/>
       <c r="H243" s="5"/>
@@ -8267,7 +8265,7 @@
     </row>
     <row r="244" customHeight="1" ht="20">
       <c r="A244" s="5" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B244" s="5" t="n">
         <v>25</v>
@@ -8279,10 +8277,10 @@
         <v>1</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>627</v>
+        <v>727</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>626</v>
+        <v>728</v>
       </c>
       <c r="G244" s="5"/>
       <c r="H244" s="5"/>
@@ -8301,22 +8299,22 @@
     </row>
     <row r="245" customHeight="1" ht="20">
       <c r="A245" s="5" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B245" s="5" t="n">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="D245" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="F245" s="5" t="n">
-        <v>724</v>
+        <v>282</v>
       </c>
       <c r="G245" s="5"/>
       <c r="H245" s="5"/>
@@ -8335,22 +8333,22 @@
     </row>
     <row r="246" customHeight="1" ht="20">
       <c r="A246" s="5" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B246" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="D246" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>727</v>
+        <v>585</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>728</v>
+        <v>584</v>
       </c>
       <c r="G246" s="5"/>
       <c r="H246" s="5"/>
@@ -8369,24 +8367,26 @@
     </row>
     <row r="247" customHeight="1" ht="20">
       <c r="A247" s="5" t="n">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="B247" s="5" t="n">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="C247" s="5" t="n">
-        <v>262</v>
+        <v>382</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>725</v>
+        <v>769</v>
       </c>
       <c r="F247" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="G247" s="5"/>
+        <v>767</v>
+      </c>
+      <c r="G247" s="5" t="n">
+        <v>768</v>
+      </c>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
@@ -8403,22 +8403,22 @@
     </row>
     <row r="248" customHeight="1" ht="20">
       <c r="A248" s="5" t="n">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="B248" s="5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="D248" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>585</v>
+        <v>624</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="G248" s="5"/>
       <c r="H248" s="5"/>
@@ -8437,26 +8437,24 @@
     </row>
     <row r="249" customHeight="1" ht="20">
       <c r="A249" s="5" t="n">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="B249" s="5" t="n">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>769</v>
+        <v>31</v>
       </c>
       <c r="F249" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="G249" s="5" t="n">
-        <v>768</v>
-      </c>
+        <v>772</v>
+      </c>
+      <c r="G249" s="5"/>
       <c r="H249" s="5"/>
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
@@ -8473,22 +8471,22 @@
     </row>
     <row r="250" customHeight="1" ht="20">
       <c r="A250" s="5" t="n">
-        <v>203</v>
+        <v>461</v>
       </c>
       <c r="B250" s="5" t="n">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="D250" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>624</v>
+        <v>1023</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>625</v>
+        <v>1024</v>
       </c>
       <c r="G250" s="5"/>
       <c r="H250" s="5"/>
@@ -8507,22 +8505,22 @@
     </row>
     <row r="251" customHeight="1" ht="20">
       <c r="A251" s="5" t="n">
-        <v>223</v>
+        <v>521</v>
       </c>
       <c r="B251" s="5" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="D251" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>31</v>
+        <v>725</v>
       </c>
       <c r="F251" s="5" t="n">
-        <v>772</v>
+        <v>282</v>
       </c>
       <c r="G251" s="5"/>
       <c r="H251" s="5"/>
@@ -8541,22 +8539,22 @@
     </row>
     <row r="252" customHeight="1" ht="20">
       <c r="A252" s="5" t="n">
-        <v>461</v>
+        <v>721</v>
       </c>
       <c r="B252" s="5" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="D252" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>1023</v>
+        <v>990</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>1024</v>
+        <v>989</v>
       </c>
       <c r="G252" s="5"/>
       <c r="H252" s="5"/>
@@ -8575,22 +8573,22 @@
     </row>
     <row r="253" customHeight="1" ht="20">
       <c r="A253" s="5" t="n">
-        <v>521</v>
+        <v>242</v>
       </c>
       <c r="B253" s="5" t="n">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>462</v>
+        <v>322</v>
       </c>
       <c r="D253" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>725</v>
+        <v>524</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>282</v>
+        <v>523</v>
       </c>
       <c r="G253" s="5"/>
       <c r="H253" s="5"/>
@@ -8609,23 +8607,21 @@
     </row>
     <row r="254" customHeight="1" ht="20">
       <c r="A254" s="5" t="n">
-        <v>721</v>
+        <v>243</v>
       </c>
       <c r="B254" s="5" t="n">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>462</v>
+        <v>322</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>990</v>
-      </c>
-      <c r="F254" s="5" t="n">
-        <v>989</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="F254" s="5"/>
       <c r="G254" s="5"/>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
@@ -8643,22 +8639,22 @@
     </row>
     <row r="255" customHeight="1" ht="20">
       <c r="A255" s="5" t="n">
-        <v>242</v>
+        <v>605</v>
       </c>
       <c r="B255" s="5" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>524</v>
+        <v>844</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>523</v>
+        <v>91</v>
       </c>
       <c r="G255" s="5"/>
       <c r="H255" s="5"/>
@@ -8677,19 +8673,19 @@
     </row>
     <row r="256" customHeight="1" ht="20">
       <c r="A256" s="5" t="n">
-        <v>243</v>
+        <v>762</v>
       </c>
       <c r="B256" s="5" t="n">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>322</v>
+        <v>502</v>
       </c>
       <c r="D256" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>764</v>
+        <v>1424</v>
       </c>
       <c r="F256" s="5"/>
       <c r="G256" s="5"/>
@@ -8709,22 +8705,22 @@
     </row>
     <row r="257" customHeight="1" ht="20">
       <c r="A257" s="5" t="n">
-        <v>605</v>
+        <v>1163</v>
       </c>
       <c r="B257" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>262</v>
+        <v>702</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>844</v>
+        <v>1023</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>91</v>
+        <v>1024</v>
       </c>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
@@ -8743,21 +8739,23 @@
     </row>
     <row r="258" customHeight="1" ht="20">
       <c r="A258" s="5" t="n">
-        <v>762</v>
+        <v>1021</v>
       </c>
       <c r="B258" s="5" t="n">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>502</v>
+        <v>562</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="F258" s="5"/>
+        <v>1383</v>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>1384</v>
+      </c>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
@@ -8775,23 +8773,21 @@
     </row>
     <row r="259" customHeight="1" ht="20">
       <c r="A259" s="5" t="n">
-        <v>1163</v>
+        <v>1324</v>
       </c>
       <c r="B259" s="5" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>702</v>
+        <v>642</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>1023</v>
-      </c>
-      <c r="F259" s="5" t="n">
-        <v>1024</v>
-      </c>
+        <v>1743</v>
+      </c>
+      <c r="F259" s="5"/>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
@@ -8809,22 +8805,22 @@
     </row>
     <row r="260" customHeight="1" ht="20">
       <c r="A260" s="5" t="n">
-        <v>1021</v>
+        <v>1246</v>
       </c>
       <c r="B260" s="5" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>562</v>
+        <v>742</v>
       </c>
       <c r="D260" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>1383</v>
+        <v>1664</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>1384</v>
+        <v>1663</v>
       </c>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
@@ -8843,7 +8839,7 @@
     </row>
     <row r="261" customHeight="1" ht="20">
       <c r="A261" s="5" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B261" s="5" t="n">
         <v>121</v>
@@ -8855,7 +8851,7 @@
         <v>2</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>1743</v>
+        <v>1723</v>
       </c>
       <c r="F261" s="5"/>
       <c r="G261" s="5"/>
@@ -8875,23 +8871,21 @@
     </row>
     <row r="262" customHeight="1" ht="20">
       <c r="A262" s="5" t="n">
-        <v>1246</v>
+        <v>1622</v>
       </c>
       <c r="B262" s="5" t="n">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>742</v>
+        <v>922</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>1664</v>
-      </c>
-      <c r="F262" s="5" t="n">
-        <v>1663</v>
-      </c>
+        <v>1923</v>
+      </c>
+      <c r="F262" s="5"/>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
@@ -8909,21 +8903,23 @@
     </row>
     <row r="263" customHeight="1" ht="20">
       <c r="A263" s="5" t="n">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="B263" s="5" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>642</v>
+        <v>802</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F263" s="5"/>
+        <v>1764</v>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>1763</v>
+      </c>
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
       <c r="I263" s="5"/>
@@ -8941,21 +8937,23 @@
     </row>
     <row r="264" customHeight="1" ht="20">
       <c r="A264" s="5" t="n">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B264" s="5" t="n">
-        <v>46</v>
+        <v>321</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>922</v>
+        <v>862</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>1923</v>
-      </c>
-      <c r="F264" s="5"/>
+        <v>963</v>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>964</v>
+      </c>
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
@@ -8973,22 +8971,22 @@
     </row>
     <row r="265" customHeight="1" ht="20">
       <c r="A265" s="5" t="n">
-        <v>1328</v>
+        <v>1461</v>
       </c>
       <c r="B265" s="5" t="n">
-        <v>50</v>
+        <v>241</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>802</v>
+        <v>662</v>
       </c>
       <c r="D265" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>1764</v>
+        <v>624</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>1763</v>
+        <v>625</v>
       </c>
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
@@ -9007,23 +9005,21 @@
     </row>
     <row r="266" customHeight="1" ht="20">
       <c r="A266" s="5" t="n">
-        <v>1624</v>
+        <v>1821</v>
       </c>
       <c r="B266" s="5" t="n">
-        <v>321</v>
+        <v>101</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>862</v>
+        <v>1022</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>963</v>
-      </c>
-      <c r="F266" s="5" t="n">
-        <v>964</v>
-      </c>
+        <v>1563</v>
+      </c>
+      <c r="F266" s="5"/>
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
@@ -9041,22 +9037,22 @@
     </row>
     <row r="267" customHeight="1" ht="20">
       <c r="A267" s="5" t="n">
-        <v>1461</v>
+        <v>1581</v>
       </c>
       <c r="B267" s="5" t="n">
-        <v>241</v>
+        <v>321</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>662</v>
+        <v>862</v>
       </c>
       <c r="D267" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>624</v>
+        <v>261</v>
       </c>
       <c r="F267" s="5" t="n">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G267" s="5"/>
       <c r="H267" s="5"/>
@@ -9075,19 +9071,19 @@
     </row>
     <row r="268" customHeight="1" ht="20">
       <c r="A268" s="5" t="n">
-        <v>1821</v>
+        <v>1643</v>
       </c>
       <c r="B268" s="5" t="n">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>1022</v>
+        <v>942</v>
       </c>
       <c r="D268" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>1563</v>
+        <v>1946</v>
       </c>
       <c r="F268" s="5"/>
       <c r="G268" s="5"/>
@@ -9107,23 +9103,21 @@
     </row>
     <row r="269" customHeight="1" ht="20">
       <c r="A269" s="5" t="n">
-        <v>1581</v>
+        <v>1645</v>
       </c>
       <c r="B269" s="5" t="n">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>862</v>
+        <v>942</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="F269" s="5" t="n">
-        <v>623</v>
-      </c>
+        <v>1943</v>
+      </c>
+      <c r="F269" s="5"/>
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
@@ -9141,19 +9135,19 @@
     </row>
     <row r="270" customHeight="1" ht="20">
       <c r="A270" s="5" t="n">
-        <v>1643</v>
+        <v>1685</v>
       </c>
       <c r="B270" s="5" t="n">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>942</v>
+        <v>982</v>
       </c>
       <c r="D270" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>1946</v>
+        <v>763</v>
       </c>
       <c r="F270" s="5"/>
       <c r="G270" s="5"/>
@@ -9173,19 +9167,19 @@
     </row>
     <row r="271" customHeight="1" ht="20">
       <c r="A271" s="5" t="n">
-        <v>1645</v>
+        <v>1844</v>
       </c>
       <c r="B271" s="5" t="n">
-        <v>26</v>
+        <v>281</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>942</v>
+        <v>822</v>
       </c>
       <c r="D271" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>1943</v>
+        <v>2085</v>
       </c>
       <c r="F271" s="5"/>
       <c r="G271" s="5"/>
@@ -9205,21 +9199,23 @@
     </row>
     <row r="272" customHeight="1" ht="20">
       <c r="A272" s="5" t="n">
-        <v>1685</v>
+        <v>1902</v>
       </c>
       <c r="B272" s="5" t="n">
-        <v>401</v>
+        <v>50</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>982</v>
+        <v>1042</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>763</v>
-      </c>
-      <c r="F272" s="5"/>
+        <v>1864</v>
+      </c>
+      <c r="F272" s="5" t="n">
+        <v>1863</v>
+      </c>
       <c r="G272" s="5"/>
       <c r="H272" s="5"/>
       <c r="I272" s="5"/>
@@ -9237,19 +9233,19 @@
     </row>
     <row r="273" customHeight="1" ht="20">
       <c r="A273" s="5" t="n">
-        <v>1844</v>
+        <v>2044</v>
       </c>
       <c r="B273" s="5" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>822</v>
+        <v>1122</v>
       </c>
       <c r="D273" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>2085</v>
+        <v>2267</v>
       </c>
       <c r="F273" s="5"/>
       <c r="G273" s="5"/>
@@ -9269,22 +9265,22 @@
     </row>
     <row r="274" customHeight="1" ht="20">
       <c r="A274" s="5" t="n">
-        <v>1902</v>
+        <v>2121</v>
       </c>
       <c r="B274" s="5" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>1042</v>
+        <v>1162</v>
       </c>
       <c r="D274" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>1864</v>
+        <v>2283</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>1863</v>
+        <v>2284</v>
       </c>
       <c r="G274" s="5"/>
       <c r="H274" s="5"/>
@@ -9303,19 +9299,19 @@
     </row>
     <row r="275" customHeight="1" ht="20">
       <c r="A275" s="5" t="n">
-        <v>2044</v>
+        <v>2142</v>
       </c>
       <c r="B275" s="5" t="n">
-        <v>301</v>
+        <v>441</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>1122</v>
+        <v>1182</v>
       </c>
       <c r="D275" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>2267</v>
+        <v>1150</v>
       </c>
       <c r="F275" s="5"/>
       <c r="G275" s="5"/>
@@ -9335,22 +9331,22 @@
     </row>
     <row r="276" customHeight="1" ht="20">
       <c r="A276" s="5" t="n">
-        <v>2121</v>
+        <v>2143</v>
       </c>
       <c r="B276" s="5" t="n">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>1162</v>
+        <v>1182</v>
       </c>
       <c r="D276" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>2283</v>
+        <v>585</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>2284</v>
+        <v>584</v>
       </c>
       <c r="G276" s="5"/>
       <c r="H276" s="5"/>
@@ -9369,21 +9365,23 @@
     </row>
     <row r="277" customHeight="1" ht="20">
       <c r="A277" s="5" t="n">
-        <v>2142</v>
+        <v>3041</v>
       </c>
       <c r="B277" s="5" t="n">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>1182</v>
+        <v>1322</v>
       </c>
       <c r="D277" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>1150</v>
-      </c>
-      <c r="F277" s="5"/>
+        <v>2863</v>
+      </c>
+      <c r="F277" s="5" t="n">
+        <v>2823</v>
+      </c>
       <c r="G277" s="5"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
@@ -9401,22 +9399,22 @@
     </row>
     <row r="278" customHeight="1" ht="20">
       <c r="A278" s="5" t="n">
-        <v>2143</v>
+        <v>3061</v>
       </c>
       <c r="B278" s="5" t="n">
-        <v>441</v>
+        <v>501</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>1182</v>
+        <v>1322</v>
       </c>
       <c r="D278" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>585</v>
+        <v>24</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>584</v>
+        <v>22</v>
       </c>
       <c r="G278" s="5"/>
       <c r="H278" s="5"/>
@@ -9435,22 +9433,22 @@
     </row>
     <row r="279" customHeight="1" ht="20">
       <c r="A279" s="5" t="n">
-        <v>3041</v>
+        <v>2301</v>
       </c>
       <c r="B279" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D279" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>2863</v>
+        <v>142</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>2823</v>
+        <v>141</v>
       </c>
       <c r="G279" s="5"/>
       <c r="H279" s="5"/>
@@ -9469,22 +9467,22 @@
     </row>
     <row r="280" customHeight="1" ht="20">
       <c r="A280" s="5" t="n">
-        <v>3061</v>
+        <v>2321</v>
       </c>
       <c r="B280" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D280" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>24</v>
+        <v>585</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="G280" s="5"/>
       <c r="H280" s="5"/>
@@ -9503,7 +9501,7 @@
     </row>
     <row r="281" customHeight="1" ht="20">
       <c r="A281" s="5" t="n">
-        <v>2301</v>
+        <v>2363</v>
       </c>
       <c r="B281" s="5" t="n">
         <v>461</v>
@@ -9512,14 +9510,12 @@
         <v>1222</v>
       </c>
       <c r="D281" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="F281" s="5" t="n">
-        <v>141</v>
-      </c>
+        <v>963</v>
+      </c>
+      <c r="F281" s="5"/>
       <c r="G281" s="5"/>
       <c r="H281" s="5"/>
       <c r="I281" s="5"/>
@@ -9537,22 +9533,22 @@
     </row>
     <row r="282" customHeight="1" ht="20">
       <c r="A282" s="5" t="n">
-        <v>2321</v>
+        <v>3141</v>
       </c>
       <c r="B282" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D282" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>585</v>
+        <v>687</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>584</v>
+        <v>688</v>
       </c>
       <c r="G282" s="5"/>
       <c r="H282" s="5"/>
@@ -9571,21 +9567,23 @@
     </row>
     <row r="283" customHeight="1" ht="20">
       <c r="A283" s="5" t="n">
-        <v>2363</v>
+        <v>2442</v>
       </c>
       <c r="B283" s="5" t="n">
-        <v>461</v>
+        <v>261</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>1222</v>
+        <v>1202</v>
       </c>
       <c r="D283" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>963</v>
-      </c>
-      <c r="F283" s="5"/>
+        <v>2484</v>
+      </c>
+      <c r="F283" s="5" t="n">
+        <v>2485</v>
+      </c>
       <c r="G283" s="5"/>
       <c r="H283" s="5"/>
       <c r="I283" s="5"/>
@@ -9603,22 +9601,22 @@
     </row>
     <row r="284" customHeight="1" ht="20">
       <c r="A284" s="5" t="n">
-        <v>3141</v>
+        <v>2503</v>
       </c>
       <c r="B284" s="5" t="n">
-        <v>501</v>
+        <v>261</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>1322</v>
+        <v>1202</v>
       </c>
       <c r="D284" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>687</v>
+        <v>2525</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>688</v>
+        <v>2524</v>
       </c>
       <c r="G284" s="5"/>
       <c r="H284" s="5"/>
@@ -9637,22 +9635,22 @@
     </row>
     <row r="285" customHeight="1" ht="20">
       <c r="A285" s="5" t="n">
-        <v>2442</v>
+        <v>2581</v>
       </c>
       <c r="B285" s="5" t="n">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>1202</v>
+        <v>1342</v>
       </c>
       <c r="D285" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E285" s="5" t="n">
-        <v>2484</v>
+        <v>2584</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>2485</v>
+        <v>2583</v>
       </c>
       <c r="G285" s="5"/>
       <c r="H285" s="5"/>
@@ -9671,22 +9669,22 @@
     </row>
     <row r="286" customHeight="1" ht="20">
       <c r="A286" s="5" t="n">
-        <v>2503</v>
+        <v>2701</v>
       </c>
       <c r="B286" s="5" t="n">
-        <v>261</v>
+        <v>181</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>1202</v>
+        <v>1262</v>
       </c>
       <c r="D286" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>2525</v>
+        <v>221</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>2524</v>
+        <v>1131</v>
       </c>
       <c r="G286" s="5"/>
       <c r="H286" s="5"/>
@@ -9705,22 +9703,22 @@
     </row>
     <row r="287" customHeight="1" ht="20">
       <c r="A287" s="5" t="n">
-        <v>2581</v>
+        <v>2761</v>
       </c>
       <c r="B287" s="5" t="n">
-        <v>27</v>
+        <v>461</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>1342</v>
+        <v>1302</v>
       </c>
       <c r="D287" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>2584</v>
+        <v>81</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>2583</v>
+        <v>2683</v>
       </c>
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
@@ -9739,22 +9737,22 @@
     </row>
     <row r="288" customHeight="1" ht="20">
       <c r="A288" s="5" t="n">
-        <v>2701</v>
+        <v>2921</v>
       </c>
       <c r="B288" s="5" t="n">
-        <v>181</v>
+        <v>501</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>1262</v>
+        <v>1322</v>
       </c>
       <c r="D288" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>221</v>
+        <v>2803</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>1131</v>
+        <v>2804</v>
       </c>
       <c r="G288" s="5"/>
       <c r="H288" s="5"/>
@@ -9773,22 +9771,22 @@
     </row>
     <row r="289" customHeight="1" ht="20">
       <c r="A289" s="5" t="n">
-        <v>2761</v>
+        <v>2922</v>
       </c>
       <c r="B289" s="5" t="n">
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>1302</v>
+        <v>1423</v>
       </c>
       <c r="D289" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E289" s="5" t="n">
-        <v>81</v>
+        <v>1303</v>
       </c>
       <c r="F289" s="5" t="n">
-        <v>2683</v>
+        <v>1147</v>
       </c>
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
@@ -9807,22 +9805,22 @@
     </row>
     <row r="290" customHeight="1" ht="20">
       <c r="A290" s="5" t="n">
-        <v>2921</v>
+        <v>2924</v>
       </c>
       <c r="B290" s="5" t="n">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>1322</v>
+        <v>1423</v>
       </c>
       <c r="D290" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>2803</v>
+        <v>24</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>2804</v>
+        <v>22</v>
       </c>
       <c r="G290" s="5"/>
       <c r="H290" s="5"/>
@@ -9841,7 +9839,7 @@
     </row>
     <row r="291" customHeight="1" ht="20">
       <c r="A291" s="5" t="n">
-        <v>2922</v>
+        <v>2983</v>
       </c>
       <c r="B291" s="5" t="n">
         <v>521</v>
@@ -9853,10 +9851,10 @@
         <v>1</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>1303</v>
+        <v>2846</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>1147</v>
+        <v>2845</v>
       </c>
       <c r="G291" s="5"/>
       <c r="H291" s="5"/>
@@ -9875,22 +9873,22 @@
     </row>
     <row r="292" customHeight="1" ht="20">
       <c r="A292" s="5" t="n">
-        <v>2924</v>
+        <v>3181</v>
       </c>
       <c r="B292" s="5" t="n">
-        <v>521</v>
+        <v>481</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>1423</v>
+        <v>1282</v>
       </c>
       <c r="D292" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>24</v>
+        <v>2164</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>22</v>
+        <v>2163</v>
       </c>
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
@@ -9909,22 +9907,22 @@
     </row>
     <row r="293" customHeight="1" ht="20">
       <c r="A293" s="5" t="n">
-        <v>2983</v>
+        <v>3221</v>
       </c>
       <c r="B293" s="5" t="n">
-        <v>521</v>
+        <v>41</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>1423</v>
+        <v>1403</v>
       </c>
       <c r="D293" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>2846</v>
+        <v>2003</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>2845</v>
+        <v>2004</v>
       </c>
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
@@ -9943,22 +9941,22 @@
     </row>
     <row r="294" customHeight="1" ht="20">
       <c r="A294" s="5" t="n">
-        <v>3181</v>
+        <v>3261</v>
       </c>
       <c r="B294" s="5" t="n">
-        <v>481</v>
+        <v>321</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>1282</v>
+        <v>1444</v>
       </c>
       <c r="D294" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>2164</v>
+        <v>2944</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>2163</v>
+        <v>2943</v>
       </c>
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
@@ -9977,23 +9975,21 @@
     </row>
     <row r="295" customHeight="1" ht="20">
       <c r="A295" s="5" t="n">
-        <v>3221</v>
+        <v>3301</v>
       </c>
       <c r="B295" s="5" t="n">
-        <v>41</v>
+        <v>461</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>1403</v>
+        <v>1483</v>
       </c>
       <c r="D295" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F295" s="5" t="n">
-        <v>2004</v>
-      </c>
+        <v>2643</v>
+      </c>
+      <c r="F295" s="5"/>
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
       <c r="I295" s="5"/>
@@ -10011,73 +10007,75 @@
     </row>
     <row r="296" customHeight="1" ht="20">
       <c r="A296" s="5" t="n">
-        <v>3261</v>
+        <v>3403</v>
       </c>
       <c r="B296" s="5" t="n">
-        <v>321</v>
+        <v>541</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>1444</v>
+        <v>1503</v>
       </c>
       <c r="D296" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>2944</v>
+        <v>3024</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>2943</v>
+        <v>3025</v>
       </c>
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
       <c r="I296" s="5"/>
       <c r="J296" s="5"/>
       <c r="K296" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L296" s="7"/>
       <c r="M296" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N296" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="297" customHeight="1" ht="20">
       <c r="A297" s="5" t="n">
-        <v>3301</v>
+        <v>3404</v>
       </c>
       <c r="B297" s="5" t="n">
-        <v>461</v>
+        <v>541</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>1483</v>
+        <v>1503</v>
       </c>
       <c r="D297" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>2643</v>
-      </c>
-      <c r="F297" s="5"/>
+        <v>3026</v>
+      </c>
+      <c r="F297" s="5" t="n">
+        <v>3027</v>
+      </c>
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5"/>
       <c r="J297" s="5"/>
       <c r="K297" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L297" s="7"/>
       <c r="M297" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N297" s="7" t="n">
-        <v>45831.8349884259</v>
+        <v>45831.8393287037</v>
       </c>
     </row>
     <row r="298" customHeight="1" ht="20">
       <c r="A298" s="5" t="n">
-        <v>3403</v>
+        <v>3422</v>
       </c>
       <c r="B298" s="5" t="n">
         <v>541</v>
@@ -10086,14 +10084,12 @@
         <v>1503</v>
       </c>
       <c r="D298" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>3024</v>
-      </c>
-      <c r="F298" s="5" t="n">
-        <v>3025</v>
-      </c>
+        <v>3065</v>
+      </c>
+      <c r="F298" s="5"/>
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
       <c r="I298" s="5"/>
@@ -10111,7 +10107,7 @@
     </row>
     <row r="299" customHeight="1" ht="20">
       <c r="A299" s="5" t="n">
-        <v>3404</v>
+        <v>3424</v>
       </c>
       <c r="B299" s="5" t="n">
         <v>541</v>
@@ -10123,10 +10119,10 @@
         <v>1</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>3026</v>
+        <v>3068</v>
       </c>
       <c r="F299" s="5" t="n">
-        <v>3027</v>
+        <v>3069</v>
       </c>
       <c r="G299" s="5"/>
       <c r="H299" s="5"/>
@@ -10145,7 +10141,7 @@
     </row>
     <row r="300" customHeight="1" ht="20">
       <c r="A300" s="5" t="n">
-        <v>3422</v>
+        <v>3427</v>
       </c>
       <c r="B300" s="5" t="n">
         <v>541</v>
@@ -10154,12 +10150,14 @@
         <v>1503</v>
       </c>
       <c r="D300" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>3065</v>
-      </c>
-      <c r="F300" s="5"/>
+        <v>2583</v>
+      </c>
+      <c r="F300" s="5" t="n">
+        <v>2584</v>
+      </c>
       <c r="G300" s="5"/>
       <c r="H300" s="5"/>
       <c r="I300" s="5"/>
@@ -10177,7 +10175,7 @@
     </row>
     <row r="301" customHeight="1" ht="20">
       <c r="A301" s="5" t="n">
-        <v>3424</v>
+        <v>3428</v>
       </c>
       <c r="B301" s="5" t="n">
         <v>541</v>
@@ -10186,14 +10184,12 @@
         <v>1503</v>
       </c>
       <c r="D301" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>3068</v>
-      </c>
-      <c r="F301" s="5" t="n">
-        <v>3069</v>
-      </c>
+        <v>3071</v>
+      </c>
+      <c r="F301" s="5"/>
       <c r="G301" s="5"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5"/>
@@ -10211,23 +10207,21 @@
     </row>
     <row r="302" customHeight="1" ht="20">
       <c r="A302" s="5" t="n">
-        <v>3427</v>
+        <v>3761</v>
       </c>
       <c r="B302" s="5" t="n">
-        <v>541</v>
+        <v>681</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>1503</v>
+        <v>1647</v>
       </c>
       <c r="D302" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>2583</v>
-      </c>
-      <c r="F302" s="5" t="n">
-        <v>2584</v>
-      </c>
+        <v>3403</v>
+      </c>
+      <c r="F302" s="5"/>
       <c r="G302" s="5"/>
       <c r="H302" s="5"/>
       <c r="I302" s="5"/>
@@ -10235,29 +10229,27 @@
       <c r="K302" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L302" s="7"/>
-      <c r="M302" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N302" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L302" s="7" t="n">
+        <v>45859.6980671296</v>
+      </c>
+      <c r="M302" s="6"/>
+      <c r="N302" s="7"/>
     </row>
     <row r="303" customHeight="1" ht="20">
       <c r="A303" s="5" t="n">
-        <v>3428</v>
+        <v>3841</v>
       </c>
       <c r="B303" s="5" t="n">
-        <v>541</v>
+        <v>681</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>1503</v>
+        <v>1647</v>
       </c>
       <c r="D303" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>3071</v>
+        <v>3463</v>
       </c>
       <c r="F303" s="5"/>
       <c r="G303" s="5"/>
@@ -10267,31 +10259,31 @@
       <c r="K303" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L303" s="7"/>
-      <c r="M303" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N303" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L303" s="7" t="n">
+        <v>45895.3855324074</v>
+      </c>
+      <c r="M303" s="6"/>
+      <c r="N303" s="7"/>
     </row>
     <row r="304" customHeight="1" ht="20">
       <c r="A304" s="5" t="n">
-        <v>3761</v>
+        <v>3901</v>
       </c>
       <c r="B304" s="5" t="n">
-        <v>681</v>
+        <v>722</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>1647</v>
+        <v>1684</v>
       </c>
       <c r="D304" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>3403</v>
-      </c>
-      <c r="F304" s="5"/>
+        <v>3523</v>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>3524</v>
+      </c>
       <c r="G304" s="5"/>
       <c r="H304" s="5"/>
       <c r="I304" s="5"/>
@@ -10300,28 +10292,30 @@
         <v>15</v>
       </c>
       <c r="L304" s="7" t="n">
-        <v>45859.6980671296</v>
+        <v>45911.2688078704</v>
       </c>
       <c r="M304" s="6"/>
       <c r="N304" s="7"/>
     </row>
     <row r="305" customHeight="1" ht="20">
       <c r="A305" s="5" t="n">
-        <v>3841</v>
+        <v>3902</v>
       </c>
       <c r="B305" s="5" t="n">
-        <v>681</v>
+        <v>621</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>1647</v>
+        <v>1683</v>
       </c>
       <c r="D305" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>3463</v>
-      </c>
-      <c r="F305" s="5"/>
+        <v>3526</v>
+      </c>
+      <c r="F305" s="5" t="n">
+        <v>3525</v>
+      </c>
       <c r="G305" s="5"/>
       <c r="H305" s="5"/>
       <c r="I305" s="5"/>
@@ -10330,29 +10324,29 @@
         <v>15</v>
       </c>
       <c r="L305" s="7" t="n">
-        <v>45895.3855324074</v>
+        <v>45911.4241203704</v>
       </c>
       <c r="M305" s="6"/>
       <c r="N305" s="7"/>
     </row>
     <row r="306" customHeight="1" ht="20">
       <c r="A306" s="5" t="n">
-        <v>3901</v>
+        <v>3903</v>
       </c>
       <c r="B306" s="5" t="n">
-        <v>722</v>
+        <v>621</v>
       </c>
       <c r="C306" s="5" t="n">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D306" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>3523</v>
+        <v>3531</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>3524</v>
+        <v>3530</v>
       </c>
       <c r="G306" s="5"/>
       <c r="H306" s="5"/>
@@ -10362,30 +10356,28 @@
         <v>15</v>
       </c>
       <c r="L306" s="7" t="n">
-        <v>45911.2688078704</v>
+        <v>45911.6326967593</v>
       </c>
       <c r="M306" s="6"/>
       <c r="N306" s="7"/>
     </row>
     <row r="307" customHeight="1" ht="20">
       <c r="A307" s="5" t="n">
-        <v>3902</v>
+        <v>4284</v>
       </c>
       <c r="B307" s="5" t="n">
-        <v>621</v>
+        <v>801</v>
       </c>
       <c r="C307" s="5" t="n">
-        <v>1683</v>
+        <v>1763</v>
       </c>
       <c r="D307" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>3526</v>
-      </c>
-      <c r="F307" s="5" t="n">
-        <v>3525</v>
-      </c>
+        <v>3810</v>
+      </c>
+      <c r="F307" s="5"/>
       <c r="G307" s="5"/>
       <c r="H307" s="5"/>
       <c r="I307" s="5"/>
@@ -10394,14 +10386,14 @@
         <v>15</v>
       </c>
       <c r="L307" s="7" t="n">
-        <v>45911.4241203704</v>
+        <v>46012.2927083333</v>
       </c>
       <c r="M307" s="6"/>
       <c r="N307" s="7"/>
     </row>
     <row r="308" customHeight="1" ht="20">
       <c r="A308" s="5" t="n">
-        <v>3903</v>
+        <v>4022</v>
       </c>
       <c r="B308" s="5" t="n">
         <v>621</v>
@@ -10410,44 +10402,46 @@
         <v>1683</v>
       </c>
       <c r="D308" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>3531</v>
+        <v>3543</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>3530</v>
+        <v>3563</v>
       </c>
       <c r="G308" s="5"/>
       <c r="H308" s="5"/>
       <c r="I308" s="5"/>
       <c r="J308" s="5"/>
       <c r="K308" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L308" s="7" t="n">
-        <v>45911.6326967593</v>
+        <v>45947.2722222222</v>
       </c>
       <c r="M308" s="6"/>
       <c r="N308" s="7"/>
     </row>
     <row r="309" customHeight="1" ht="20">
       <c r="A309" s="5" t="n">
-        <v>4284</v>
+        <v>4067</v>
       </c>
       <c r="B309" s="5" t="n">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="C309" s="5" t="n">
-        <v>1763</v>
+        <v>1743</v>
       </c>
       <c r="D309" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>3810</v>
-      </c>
-      <c r="F309" s="5"/>
+        <v>3673</v>
+      </c>
+      <c r="F309" s="5" t="n">
+        <v>3674</v>
+      </c>
       <c r="G309" s="5"/>
       <c r="H309" s="5"/>
       <c r="I309" s="5"/>
@@ -10456,61 +10450,61 @@
         <v>15</v>
       </c>
       <c r="L309" s="7" t="n">
-        <v>46012.2927083333</v>
+        <v>45966.7240046296</v>
       </c>
       <c r="M309" s="6"/>
       <c r="N309" s="7"/>
     </row>
     <row r="310" customHeight="1" ht="20">
       <c r="A310" s="5" t="n">
-        <v>4022</v>
+        <v>4071</v>
       </c>
       <c r="B310" s="5" t="n">
-        <v>621</v>
+        <v>781</v>
       </c>
       <c r="C310" s="5" t="n">
-        <v>1683</v>
+        <v>1743</v>
       </c>
       <c r="D310" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>3543</v>
+        <v>33</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>3563</v>
+        <v>3680</v>
       </c>
       <c r="G310" s="5"/>
       <c r="H310" s="5"/>
       <c r="I310" s="5"/>
       <c r="J310" s="5"/>
       <c r="K310" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L310" s="7" t="n">
-        <v>45947.2722222222</v>
+        <v>45967.679375</v>
       </c>
       <c r="M310" s="6"/>
       <c r="N310" s="7"/>
     </row>
     <row r="311" customHeight="1" ht="20">
       <c r="A311" s="5" t="n">
-        <v>4067</v>
+        <v>4141</v>
       </c>
       <c r="B311" s="5" t="n">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="C311" s="5" t="n">
-        <v>1743</v>
+        <v>1763</v>
       </c>
       <c r="D311" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>3673</v>
+        <v>3732</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>3674</v>
+        <v>3731</v>
       </c>
       <c r="G311" s="5"/>
       <c r="H311" s="5"/>
@@ -10520,29 +10514,29 @@
         <v>15</v>
       </c>
       <c r="L311" s="7" t="n">
-        <v>45966.7240046296</v>
+        <v>45985.7560185185</v>
       </c>
       <c r="M311" s="6"/>
       <c r="N311" s="7"/>
     </row>
     <row r="312" customHeight="1" ht="20">
       <c r="A312" s="5" t="n">
-        <v>4071</v>
+        <v>4142</v>
       </c>
       <c r="B312" s="5" t="n">
-        <v>781</v>
+        <v>722</v>
       </c>
       <c r="C312" s="5" t="n">
-        <v>1743</v>
+        <v>1684</v>
       </c>
       <c r="D312" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>33</v>
+        <v>3736</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>3680</v>
+        <v>3733</v>
       </c>
       <c r="G312" s="5"/>
       <c r="H312" s="5"/>
@@ -10552,30 +10546,28 @@
         <v>15</v>
       </c>
       <c r="L312" s="7" t="n">
-        <v>45967.679375</v>
+        <v>45986.6275578704</v>
       </c>
       <c r="M312" s="6"/>
       <c r="N312" s="7"/>
     </row>
     <row r="313" customHeight="1" ht="20">
       <c r="A313" s="5" t="n">
-        <v>4141</v>
+        <v>4281</v>
       </c>
       <c r="B313" s="5" t="n">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="C313" s="5" t="n">
-        <v>1763</v>
+        <v>1784</v>
       </c>
       <c r="D313" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>3732</v>
-      </c>
-      <c r="F313" s="5" t="n">
-        <v>3731</v>
-      </c>
+        <v>3843</v>
+      </c>
+      <c r="F313" s="5"/>
       <c r="G313" s="5"/>
       <c r="H313" s="5"/>
       <c r="I313" s="5"/>
@@ -10584,29 +10576,29 @@
         <v>15</v>
       </c>
       <c r="L313" s="7" t="n">
-        <v>45985.7560185185</v>
+        <v>46011.5137962963</v>
       </c>
       <c r="M313" s="6"/>
       <c r="N313" s="7"/>
     </row>
     <row r="314" customHeight="1" ht="20">
       <c r="A314" s="5" t="n">
-        <v>4142</v>
+        <v>4301</v>
       </c>
       <c r="B314" s="5" t="n">
-        <v>722</v>
+        <v>762</v>
       </c>
       <c r="C314" s="5" t="n">
-        <v>1684</v>
+        <v>1724</v>
       </c>
       <c r="D314" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>3736</v>
+        <v>3864</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>3733</v>
+        <v>3865</v>
       </c>
       <c r="G314" s="5"/>
       <c r="H314" s="5"/>
@@ -10616,28 +10608,30 @@
         <v>15</v>
       </c>
       <c r="L314" s="7" t="n">
-        <v>45986.6275578704</v>
+        <v>46014.5824189815</v>
       </c>
       <c r="M314" s="6"/>
       <c r="N314" s="7"/>
     </row>
     <row r="315" customHeight="1" ht="20">
       <c r="A315" s="5" t="n">
-        <v>4281</v>
+        <v>4302</v>
       </c>
       <c r="B315" s="5" t="n">
-        <v>822</v>
+        <v>762</v>
       </c>
       <c r="C315" s="5" t="n">
-        <v>1784</v>
+        <v>1724</v>
       </c>
       <c r="D315" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>3843</v>
-      </c>
-      <c r="F315" s="5"/>
+        <v>3866</v>
+      </c>
+      <c r="F315" s="5" t="n">
+        <v>3867</v>
+      </c>
       <c r="G315" s="5"/>
       <c r="H315" s="5"/>
       <c r="I315" s="5"/>
@@ -10646,29 +10640,29 @@
         <v>15</v>
       </c>
       <c r="L315" s="7" t="n">
-        <v>46011.5137962963</v>
+        <v>46014.7677199074</v>
       </c>
       <c r="M315" s="6"/>
       <c r="N315" s="7"/>
     </row>
     <row r="316" customHeight="1" ht="20">
       <c r="A316" s="5" t="n">
-        <v>4301</v>
+        <v>4322</v>
       </c>
       <c r="B316" s="5" t="n">
-        <v>762</v>
+        <v>861</v>
       </c>
       <c r="C316" s="5" t="n">
-        <v>1724</v>
+        <v>1823</v>
       </c>
       <c r="D316" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>3864</v>
+        <v>3026</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>3865</v>
+        <v>3889</v>
       </c>
       <c r="G316" s="5"/>
       <c r="H316" s="5"/>
@@ -10678,29 +10672,29 @@
         <v>15</v>
       </c>
       <c r="L316" s="7" t="n">
-        <v>46014.5824189815</v>
+        <v>46031.444212963</v>
       </c>
       <c r="M316" s="6"/>
       <c r="N316" s="7"/>
     </row>
     <row r="317" customHeight="1" ht="20">
       <c r="A317" s="5" t="n">
-        <v>4302</v>
+        <v>4341</v>
       </c>
       <c r="B317" s="5" t="n">
-        <v>762</v>
+        <v>801</v>
       </c>
       <c r="C317" s="5" t="n">
-        <v>1724</v>
+        <v>1763</v>
       </c>
       <c r="D317" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>3866</v>
+        <v>1163</v>
       </c>
       <c r="F317" s="5" t="n">
-        <v>3867</v>
+        <v>1164</v>
       </c>
       <c r="G317" s="5"/>
       <c r="H317" s="5"/>
@@ -10710,7 +10704,7 @@
         <v>15</v>
       </c>
       <c r="L317" s="7" t="n">
-        <v>46014.7677199074</v>
+        <v>46032.4061805556</v>
       </c>
       <c r="M317" s="6"/>
       <c r="N317" s="7"/>
@@ -10765,9 +10759,7 @@
       <c r="E319" s="5" t="n">
         <v>627</v>
       </c>
-      <c r="F319" s="5" t="n">
-        <v>626</v>
-      </c>
+      <c r="F319" s="5"/>
       <c r="G319" s="5"/>
       <c r="H319" s="5"/>
       <c r="I319" s="5"/>

--- a/inp_Excel/mov_clienti_alloggi.xlsx
+++ b/inp_Excel/mov_clienti_alloggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="16">
   <si>
     <t>MOV_CLIENTI_ALLOGGIO_PK</t>
   </si>
@@ -156,8 +156,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:N391" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:N391"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:N392" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:N392"/>
   <tableColumns count="14">
     <tableColumn id="1" name="MOV_CLIENTI_ALLOGGIO_PK"/>
     <tableColumn id="2" name="VIAGGIO_ID_FK"/>
@@ -3035,88 +3035,84 @@
     </row>
     <row r="86" customHeight="1" ht="20">
       <c r="A86" s="5" t="n">
-        <v>4205</v>
+        <v>4381</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>762</v>
+        <v>681</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1724</v>
+        <v>1647</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2143</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>3787</v>
-      </c>
+        <v>3943</v>
+      </c>
+      <c r="F86" s="5"/>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>46001.3052314815</v>
+        <v>46042.2969675926</v>
       </c>
       <c r="M86" s="6"/>
       <c r="N86" s="7"/>
     </row>
     <row r="87" customHeight="1" ht="20">
       <c r="A87" s="5" t="n">
-        <v>49</v>
+        <v>4205</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>48</v>
+        <v>762</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>202</v>
+        <v>1724</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>529</v>
+        <v>2143</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>530</v>
+        <v>3787</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L87" s="7"/>
-      <c r="M87" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N87" s="7" t="n">
-        <v>45831.8349884259</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L87" s="7" t="n">
+        <v>46001.3052314815</v>
+      </c>
+      <c r="M87" s="6"/>
+      <c r="N87" s="7"/>
     </row>
     <row r="88" customHeight="1" ht="20">
       <c r="A88" s="5" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>563</v>
+        <v>529</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>564</v>
+        <v>530</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -3135,22 +3131,22 @@
     </row>
     <row r="89" customHeight="1" ht="20">
       <c r="A89" s="5" t="n">
-        <v>822</v>
+        <v>53</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>262</v>
+        <v>162</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>488</v>
+        <v>563</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>487</v>
+        <v>564</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -3169,22 +3165,22 @@
     </row>
     <row r="90" customHeight="1" ht="20">
       <c r="A90" s="5" t="n">
-        <v>122</v>
+        <v>822</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>527</v>
+        <v>488</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -3203,7 +3199,7 @@
     </row>
     <row r="91" customHeight="1" ht="20">
       <c r="A91" s="5" t="n">
-        <v>244</v>
+        <v>122</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>44</v>
@@ -3212,12 +3208,14 @@
         <v>322</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>763</v>
-      </c>
-      <c r="F91" s="5"/>
+        <v>527</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>528</v>
+      </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -3235,7 +3233,7 @@
     </row>
     <row r="92" customHeight="1" ht="20">
       <c r="A92" s="5" t="n">
-        <v>124</v>
+        <v>244</v>
       </c>
       <c r="B92" s="5" t="n">
         <v>44</v>
@@ -3244,14 +3242,12 @@
         <v>322</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>623</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="F92" s="5"/>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -3269,7 +3265,7 @@
     </row>
     <row r="93" customHeight="1" ht="20">
       <c r="A93" s="5" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B93" s="5" t="n">
         <v>44</v>
@@ -3278,17 +3274,15 @@
         <v>322</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>704</v>
+        <v>261</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>703</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>705</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
@@ -3305,24 +3299,26 @@
     </row>
     <row r="94" customHeight="1" ht="20">
       <c r="A94" s="5" t="n">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>22</v>
+        <v>704</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="G94" s="5"/>
+        <v>703</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>705</v>
+      </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
@@ -3339,7 +3335,7 @@
     </row>
     <row r="95" customHeight="1" ht="20">
       <c r="A95" s="5" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>25</v>
@@ -3351,10 +3347,10 @@
         <v>1</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>381</v>
+        <v>22</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>726</v>
+        <v>24</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -3373,21 +3369,23 @@
     </row>
     <row r="96" customHeight="1" ht="20">
       <c r="A96" s="5" t="n">
-        <v>861</v>
+        <v>148</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>462</v>
+        <v>79</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1483</v>
-      </c>
-      <c r="F96" s="5"/>
+        <v>381</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>726</v>
+      </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -3405,19 +3403,19 @@
     </row>
     <row r="97" customHeight="1" ht="20">
       <c r="A97" s="5" t="n">
-        <v>152</v>
+        <v>861</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>81</v>
+        <v>1483</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
@@ -3437,19 +3435,19 @@
     </row>
     <row r="98" customHeight="1" ht="20">
       <c r="A98" s="5" t="n">
-        <v>1244</v>
+        <v>152</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>742</v>
+        <v>262</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>663</v>
+        <v>81</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
@@ -3469,19 +3467,19 @@
     </row>
     <row r="99" customHeight="1" ht="20">
       <c r="A99" s="5" t="n">
-        <v>158</v>
+        <v>1244</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>363</v>
+        <v>742</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>732</v>
+        <v>663</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
@@ -3501,29 +3499,23 @@
     </row>
     <row r="100" customHeight="1" ht="20">
       <c r="A100" s="5" t="n">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>527</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>766</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>528</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>765</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="6" t="s">
@@ -3539,23 +3531,29 @@
     </row>
     <row r="101" customHeight="1" ht="20">
       <c r="A101" s="5" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>382</v>
+        <v>302</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
+        <v>527</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>766</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>765</v>
+      </c>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="6" t="s">
@@ -3571,19 +3569,19 @@
     </row>
     <row r="102" customHeight="1" ht="20">
       <c r="A102" s="5" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>783</v>
+        <v>81</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
@@ -3603,19 +3601,19 @@
     </row>
     <row r="103" customHeight="1" ht="20">
       <c r="A103" s="5" t="n">
-        <v>1621</v>
+        <v>201</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>922</v>
+        <v>322</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1467</v>
+        <v>783</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
@@ -3635,23 +3633,21 @@
     </row>
     <row r="104" customHeight="1" ht="20">
       <c r="A104" s="5" t="n">
-        <v>262</v>
+        <v>1621</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>363</v>
+        <v>922</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>807</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>808</v>
-      </c>
+        <v>1467</v>
+      </c>
+      <c r="F104" s="5"/>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
@@ -3669,22 +3665,22 @@
     </row>
     <row r="105" customHeight="1" ht="20">
       <c r="A105" s="5" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>843</v>
+        <v>807</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>85</v>
+        <v>808</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -3703,7 +3699,7 @@
     </row>
     <row r="106" customHeight="1" ht="20">
       <c r="A106" s="5" t="n">
-        <v>441</v>
+        <v>281</v>
       </c>
       <c r="B106" s="5" t="n">
         <v>23</v>
@@ -3715,10 +3711,10 @@
         <v>1</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>963</v>
+        <v>843</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>964</v>
+        <v>85</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -3737,22 +3733,22 @@
     </row>
     <row r="107" customHeight="1" ht="20">
       <c r="A107" s="5" t="n">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1164</v>
+        <v>963</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>1163</v>
+        <v>964</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -3771,22 +3767,22 @@
     </row>
     <row r="108" customHeight="1" ht="20">
       <c r="A108" s="5" t="n">
-        <v>562</v>
+        <v>501</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>402</v>
+        <v>262</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1203</v>
+        <v>1164</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>90</v>
+        <v>1163</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -3805,7 +3801,7 @@
     </row>
     <row r="109" customHeight="1" ht="20">
       <c r="A109" s="5" t="n">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="B109" s="5" t="n">
         <v>81</v>
@@ -3817,10 +3813,10 @@
         <v>1</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1223</v>
+        <v>1203</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>1224</v>
+        <v>90</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
@@ -3839,21 +3835,23 @@
     </row>
     <row r="110" customHeight="1" ht="20">
       <c r="A110" s="5" t="n">
-        <v>761</v>
+        <v>581</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>522</v>
+        <v>402</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1423</v>
-      </c>
-      <c r="F110" s="5"/>
+        <v>1223</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>1224</v>
+      </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -3871,19 +3869,19 @@
     </row>
     <row r="111" customHeight="1" ht="20">
       <c r="A111" s="5" t="n">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="D111" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1404</v>
+        <v>1423</v>
       </c>
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
@@ -3903,23 +3901,21 @@
     </row>
     <row r="112" customHeight="1" ht="20">
       <c r="A112" s="5" t="n">
-        <v>981</v>
+        <v>763</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>582</v>
+        <v>502</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>463</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>83</v>
-      </c>
+        <v>1404</v>
+      </c>
+      <c r="F112" s="5"/>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
@@ -3937,22 +3933,22 @@
     </row>
     <row r="113" customHeight="1" ht="20">
       <c r="A113" s="5" t="n">
-        <v>1282</v>
+        <v>981</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>642</v>
+        <v>582</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>727</v>
+        <v>463</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>728</v>
+        <v>83</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -3971,7 +3967,7 @@
     </row>
     <row r="114" customHeight="1" ht="20">
       <c r="A114" s="5" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B114" s="5" t="n">
         <v>121</v>
@@ -3983,10 +3979,10 @@
         <v>1</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1134</v>
+        <v>727</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>1133</v>
+        <v>728</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -4005,7 +4001,7 @@
     </row>
     <row r="115" customHeight="1" ht="20">
       <c r="A115" s="5" t="n">
-        <v>1361</v>
+        <v>1283</v>
       </c>
       <c r="B115" s="5" t="n">
         <v>121</v>
@@ -4017,10 +4013,10 @@
         <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1804</v>
+        <v>1134</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>1803</v>
+        <v>1133</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -4039,21 +4035,23 @@
     </row>
     <row r="116" customHeight="1" ht="20">
       <c r="A116" s="5" t="n">
-        <v>1401</v>
+        <v>1361</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>281</v>
+        <v>121</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>822</v>
+        <v>642</v>
       </c>
       <c r="D116" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>627</v>
-      </c>
-      <c r="F116" s="5"/>
+        <v>1804</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>1803</v>
+      </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
@@ -4071,23 +4069,21 @@
     </row>
     <row r="117" customHeight="1" ht="20">
       <c r="A117" s="5" t="n">
-        <v>1682</v>
+        <v>1401</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>862</v>
+        <v>822</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>2004</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="F117" s="5"/>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
@@ -4105,7 +4101,7 @@
     </row>
     <row r="118" customHeight="1" ht="20">
       <c r="A118" s="5" t="n">
-        <v>1582</v>
+        <v>1682</v>
       </c>
       <c r="B118" s="5" t="n">
         <v>321</v>
@@ -4117,10 +4113,10 @@
         <v>1</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1904</v>
+        <v>2003</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>1903</v>
+        <v>2004</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -4139,21 +4135,23 @@
     </row>
     <row r="119" customHeight="1" ht="20">
       <c r="A119" s="5" t="n">
-        <v>1641</v>
+        <v>1582</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>26</v>
+        <v>321</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>942</v>
+        <v>862</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1948</v>
-      </c>
-      <c r="F119" s="5"/>
+        <v>1904</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>1903</v>
+      </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
@@ -4171,7 +4169,7 @@
     </row>
     <row r="120" customHeight="1" ht="20">
       <c r="A120" s="5" t="n">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="B120" s="5" t="n">
         <v>26</v>
@@ -4183,7 +4181,7 @@
         <v>2</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1944</v>
+        <v>1948</v>
       </c>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
@@ -4203,7 +4201,7 @@
     </row>
     <row r="121" customHeight="1" ht="20">
       <c r="A121" s="5" t="n">
-        <v>1646</v>
+        <v>1642</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>26</v>
@@ -4215,7 +4213,7 @@
         <v>2</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
@@ -4235,7 +4233,7 @@
     </row>
     <row r="122" customHeight="1" ht="20">
       <c r="A122" s="5" t="n">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="B122" s="5" t="n">
         <v>26</v>
@@ -4244,14 +4242,12 @@
         <v>942</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>22</v>
-      </c>
+        <v>1945</v>
+      </c>
+      <c r="F122" s="5"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
@@ -4269,21 +4265,23 @@
     </row>
     <row r="123" customHeight="1" ht="20">
       <c r="A123" s="5" t="n">
-        <v>1681</v>
+        <v>1647</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>862</v>
+        <v>942</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1147</v>
-      </c>
-      <c r="F123" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>22</v>
+      </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -4301,19 +4299,19 @@
     </row>
     <row r="124" customHeight="1" ht="20">
       <c r="A124" s="5" t="n">
-        <v>1701</v>
+        <v>1681</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>281</v>
+        <v>321</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>822</v>
+        <v>862</v>
       </c>
       <c r="D124" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>341</v>
+        <v>1147</v>
       </c>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
@@ -4333,19 +4331,19 @@
     </row>
     <row r="125" customHeight="1" ht="20">
       <c r="A125" s="5" t="n">
-        <v>1722</v>
+        <v>1701</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>48</v>
+        <v>281</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1002</v>
+        <v>822</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>26</v>
+        <v>341</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
@@ -4365,23 +4363,21 @@
     </row>
     <row r="126" customHeight="1" ht="20">
       <c r="A126" s="5" t="n">
-        <v>1921</v>
+        <v>1722</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>822</v>
+        <v>1002</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2164</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>2163</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F126" s="5"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -4399,22 +4395,22 @@
     </row>
     <row r="127" customHeight="1" ht="20">
       <c r="A127" s="5" t="n">
-        <v>2141</v>
+        <v>1921</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>1202</v>
+        <v>822</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2304</v>
+        <v>2164</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>2303</v>
+        <v>2163</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
@@ -4433,21 +4429,23 @@
     </row>
     <row r="128" customHeight="1" ht="20">
       <c r="A128" s="5" t="n">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>441</v>
+        <v>261</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>1182</v>
+        <v>1202</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F128" s="5"/>
+        <v>2304</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>2303</v>
+      </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -4465,23 +4463,21 @@
     </row>
     <row r="129" customHeight="1" ht="20">
       <c r="A129" s="5" t="n">
-        <v>1883</v>
+        <v>2144</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>281</v>
+        <v>441</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>822</v>
+        <v>1182</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>24</v>
-      </c>
+        <v>2064</v>
+      </c>
+      <c r="F129" s="5"/>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
@@ -4499,22 +4495,22 @@
     </row>
     <row r="130" customHeight="1" ht="20">
       <c r="A130" s="5" t="n">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>50</v>
+        <v>281</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>1042</v>
+        <v>822</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E130" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F130" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>22</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
@@ -4533,22 +4529,22 @@
     </row>
     <row r="131" customHeight="1" ht="20">
       <c r="A131" s="5" t="n">
-        <v>1942</v>
+        <v>1884</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>421</v>
+        <v>50</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1102</v>
+        <v>1042</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2184</v>
+        <v>24</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>2183</v>
+        <v>22</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -4567,7 +4563,7 @@
     </row>
     <row r="132" customHeight="1" ht="20">
       <c r="A132" s="5" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B132" s="5" t="n">
         <v>421</v>
@@ -4576,12 +4572,14 @@
         <v>1102</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="F132" s="5"/>
+        <v>2184</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>2183</v>
+      </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -4599,19 +4597,19 @@
     </row>
     <row r="133" customHeight="1" ht="20">
       <c r="A133" s="5" t="n">
-        <v>2322</v>
+        <v>1943</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1222</v>
+        <v>1102</v>
       </c>
       <c r="D133" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1583</v>
+        <v>81</v>
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
@@ -4631,19 +4629,19 @@
     </row>
     <row r="134" customHeight="1" ht="20">
       <c r="A134" s="5" t="n">
-        <v>2501</v>
+        <v>2322</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>26</v>
+        <v>1583</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
@@ -4663,23 +4661,21 @@
     </row>
     <row r="135" customHeight="1" ht="20">
       <c r="A135" s="5" t="n">
-        <v>2401</v>
+        <v>2501</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2443</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>1190</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F135" s="5"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
@@ -4697,22 +4693,22 @@
     </row>
     <row r="136" customHeight="1" ht="20">
       <c r="A136" s="5" t="n">
-        <v>2461</v>
+        <v>2401</v>
       </c>
       <c r="B136" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>1302</v>
+        <v>1222</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>33</v>
+        <v>2443</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>2191</v>
+        <v>1190</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -4731,22 +4727,22 @@
     </row>
     <row r="137" customHeight="1" ht="20">
       <c r="A137" s="5" t="n">
-        <v>2841</v>
+        <v>2461</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>41</v>
+        <v>461</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1403</v>
+        <v>1302</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>585</v>
+        <v>33</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>584</v>
+        <v>2191</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -4765,22 +4761,22 @@
     </row>
     <row r="138" customHeight="1" ht="20">
       <c r="A138" s="5" t="n">
-        <v>2466</v>
+        <v>2841</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>481</v>
+        <v>41</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1282</v>
+        <v>1403</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>728</v>
+        <v>585</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>727</v>
+        <v>584</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -4799,21 +4795,23 @@
     </row>
     <row r="139" customHeight="1" ht="20">
       <c r="A139" s="5" t="n">
-        <v>2481</v>
+        <v>2466</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1302</v>
+        <v>1282</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2503</v>
-      </c>
-      <c r="F139" s="5"/>
+        <v>728</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>727</v>
+      </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -4831,19 +4829,19 @@
     </row>
     <row r="140" customHeight="1" ht="20">
       <c r="A140" s="5" t="n">
-        <v>2621</v>
+        <v>2481</v>
       </c>
       <c r="B140" s="5" t="n">
         <v>461</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>1222</v>
+        <v>1302</v>
       </c>
       <c r="D140" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2623</v>
+        <v>2503</v>
       </c>
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
@@ -4863,23 +4861,21 @@
     </row>
     <row r="141" customHeight="1" ht="20">
       <c r="A141" s="5" t="n">
-        <v>2641</v>
+        <v>2621</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1282</v>
+        <v>1222</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>463</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>83</v>
-      </c>
+        <v>2623</v>
+      </c>
+      <c r="F141" s="5"/>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -4897,21 +4893,23 @@
     </row>
     <row r="142" customHeight="1" ht="20">
       <c r="A142" s="5" t="n">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>47</v>
+        <v>481</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>1362</v>
+        <v>1282</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2643</v>
-      </c>
-      <c r="F142" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>83</v>
+      </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -4929,23 +4927,21 @@
     </row>
     <row r="143" customHeight="1" ht="20">
       <c r="A143" s="5" t="n">
-        <v>2764</v>
+        <v>2642</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1342</v>
+        <v>1362</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>22</v>
-      </c>
+        <v>2643</v>
+      </c>
+      <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
@@ -4963,22 +4959,22 @@
     </row>
     <row r="144" customHeight="1" ht="20">
       <c r="A144" s="5" t="n">
-        <v>3081</v>
+        <v>2764</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>481</v>
+        <v>27</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>1282</v>
+        <v>1342</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>585</v>
+        <v>24</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>584</v>
+        <v>22</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -4997,33 +4993,37 @@
     </row>
     <row r="145" customHeight="1" ht="20">
       <c r="A145" s="5" t="n">
-        <v>3842</v>
+        <v>3081</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>681</v>
+        <v>481</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1647</v>
+        <v>1282</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>3464</v>
-      </c>
-      <c r="F145" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L145" s="7" t="n">
-        <v>45895.6354861111</v>
-      </c>
-      <c r="M145" s="6"/>
-      <c r="N145" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="L145" s="7"/>
+      <c r="M145" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N145" s="7" t="n">
+        <v>45831.8349884259</v>
+      </c>
     </row>
     <row r="146" customHeight="1" ht="20">
       <c r="A146" s="5" t="n">
@@ -5221,56 +5221,52 @@
     </row>
     <row r="152" customHeight="1" ht="20">
       <c r="A152" s="5" t="n">
-        <v>42</v>
+        <v>4382</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>1</v>
+        <v>801</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>182</v>
+        <v>1763</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>503</v>
-      </c>
-      <c r="F152" s="5" t="n">
-        <v>504</v>
-      </c>
+        <v>2085</v>
+      </c>
+      <c r="F152" s="5"/>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L152" s="7"/>
-      <c r="M152" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N152" s="7" t="n">
-        <v>45831.8349884259</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L152" s="7" t="n">
+        <v>46042.5027546296</v>
+      </c>
+      <c r="M152" s="6"/>
+      <c r="N152" s="7"/>
     </row>
     <row r="153" customHeight="1" ht="20">
       <c r="A153" s="5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>583</v>
+        <v>503</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>27</v>
+        <v>504</v>
       </c>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
@@ -5289,7 +5285,7 @@
     </row>
     <row r="154" customHeight="1" ht="20">
       <c r="A154" s="5" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B154" s="5" t="n">
         <v>48</v>
@@ -5298,13 +5294,13 @@
         <v>202</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>543</v>
+        <v>583</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>544</v>
+        <v>27</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
@@ -5323,22 +5319,22 @@
     </row>
     <row r="155" customHeight="1" ht="20">
       <c r="A155" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>585</v>
+        <v>543</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>584</v>
+        <v>544</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
@@ -5357,21 +5353,23 @@
     </row>
     <row r="156" customHeight="1" ht="20">
       <c r="A156" s="5" t="n">
-        <v>421</v>
+        <v>52</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>422</v>
+        <v>162</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>401</v>
-      </c>
-      <c r="F156" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>584</v>
+      </c>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
@@ -5389,23 +5387,21 @@
     </row>
     <row r="157" customHeight="1" ht="20">
       <c r="A157" s="5" t="n">
-        <v>146</v>
+        <v>421</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>463</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="F157" s="5"/>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
@@ -5423,22 +5419,22 @@
     </row>
     <row r="158" customHeight="1" ht="20">
       <c r="A158" s="5" t="n">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="D158" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>714</v>
+        <v>83</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>715</v>
+        <v>463</v>
       </c>
       <c r="G158" s="5"/>
       <c r="H158" s="5"/>
@@ -5457,22 +5453,22 @@
     </row>
     <row r="159" customHeight="1" ht="20">
       <c r="A159" s="5" t="n">
-        <v>347</v>
+        <v>182</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="D159" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>24</v>
+        <v>714</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>22</v>
+        <v>715</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
@@ -5491,21 +5487,23 @@
     </row>
     <row r="160" customHeight="1" ht="20">
       <c r="A160" s="5" t="n">
-        <v>194</v>
+        <v>347</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>773</v>
-      </c>
-      <c r="F160" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>22</v>
+      </c>
       <c r="G160" s="5"/>
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
@@ -5523,7 +5521,7 @@
     </row>
     <row r="161" customHeight="1" ht="20">
       <c r="A161" s="5" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B161" s="5" t="n">
         <v>44</v>
@@ -5532,14 +5530,12 @@
         <v>322</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>774</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>784</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="F161" s="5"/>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
@@ -5557,21 +5553,23 @@
     </row>
     <row r="162" customHeight="1" ht="20">
       <c r="A162" s="5" t="n">
-        <v>401</v>
+        <v>202</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>381</v>
-      </c>
-      <c r="F162" s="5"/>
+        <v>774</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>784</v>
+      </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
@@ -5589,23 +5587,21 @@
     </row>
     <row r="163" customHeight="1" ht="20">
       <c r="A163" s="5" t="n">
-        <v>482</v>
+        <v>401</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>262</v>
+        <v>363</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>996</v>
-      </c>
-      <c r="F163" s="5" t="n">
-        <v>995</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="F163" s="5"/>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
@@ -5623,22 +5619,22 @@
     </row>
     <row r="164" customHeight="1" ht="20">
       <c r="A164" s="5" t="n">
-        <v>604</v>
+        <v>482</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>502</v>
+        <v>262</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>142</v>
+        <v>996</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>141</v>
+        <v>995</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
@@ -5657,22 +5653,22 @@
     </row>
     <row r="165" customHeight="1" ht="20">
       <c r="A165" s="5" t="n">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B165" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>502</v>
+      </c>
+      <c r="D165" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="F165" s="5" t="n">
         <v>141</v>
-      </c>
-      <c r="C165" s="5" t="n">
-        <v>462</v>
-      </c>
-      <c r="D165" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E165" s="5" t="n">
-        <v>844</v>
-      </c>
-      <c r="F165" s="5" t="n">
-        <v>91</v>
       </c>
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
@@ -5691,7 +5687,7 @@
     </row>
     <row r="166" customHeight="1" ht="20">
       <c r="A166" s="5" t="n">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B166" s="5" t="n">
         <v>141</v>
@@ -5700,12 +5696,14 @@
         <v>462</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="F166" s="5"/>
+        <v>844</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>91</v>
+      </c>
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
       <c r="I166" s="5"/>
@@ -5723,19 +5721,19 @@
     </row>
     <row r="167" customHeight="1" ht="20">
       <c r="A167" s="5" t="n">
-        <v>722</v>
+        <v>608</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="D167" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>743</v>
+        <v>85</v>
       </c>
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
@@ -5755,7 +5753,7 @@
     </row>
     <row r="168" customHeight="1" ht="20">
       <c r="A168" s="5" t="n">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B168" s="5" t="n">
         <v>181</v>
@@ -5767,7 +5765,7 @@
         <v>2</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>664</v>
+        <v>743</v>
       </c>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
@@ -5787,7 +5785,7 @@
     </row>
     <row r="169" customHeight="1" ht="20">
       <c r="A169" s="5" t="n">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B169" s="5" t="n">
         <v>181</v>
@@ -5799,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>1403</v>
+        <v>664</v>
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5"/>
@@ -5819,23 +5817,21 @@
     </row>
     <row r="170" customHeight="1" ht="20">
       <c r="A170" s="5" t="n">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>625</v>
-      </c>
+        <v>1403</v>
+      </c>
+      <c r="F170" s="5"/>
       <c r="G170" s="5"/>
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
@@ -5853,21 +5849,23 @@
     </row>
     <row r="171" customHeight="1" ht="20">
       <c r="A171" s="5" t="n">
-        <v>801</v>
+        <v>741</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1463</v>
-      </c>
-      <c r="F171" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>625</v>
+      </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
@@ -5885,23 +5883,21 @@
     </row>
     <row r="172" customHeight="1" ht="20">
       <c r="A172" s="5" t="n">
-        <v>962</v>
+        <v>801</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>622</v>
+        <v>502</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>623</v>
-      </c>
+        <v>1463</v>
+      </c>
+      <c r="F172" s="5"/>
       <c r="G172" s="5"/>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
@@ -5919,22 +5915,22 @@
     </row>
     <row r="173" customHeight="1" ht="20">
       <c r="A173" s="5" t="n">
-        <v>1161</v>
+        <v>962</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>642</v>
+        <v>622</v>
       </c>
       <c r="D173" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>963</v>
+        <v>261</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>964</v>
+        <v>623</v>
       </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
@@ -5953,21 +5949,23 @@
     </row>
     <row r="174" customHeight="1" ht="20">
       <c r="A174" s="5" t="n">
-        <v>1003</v>
+        <v>1161</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>562</v>
+        <v>642</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>1463</v>
-      </c>
-      <c r="F174" s="5"/>
+        <v>963</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>964</v>
+      </c>
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
@@ -5985,23 +5983,21 @@
     </row>
     <row r="175" customHeight="1" ht="20">
       <c r="A175" s="5" t="n">
-        <v>1042</v>
+        <v>1003</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>582</v>
+        <v>562</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="F175" s="5" t="n">
-        <v>1131</v>
-      </c>
+        <v>1463</v>
+      </c>
+      <c r="F175" s="5"/>
       <c r="G175" s="5"/>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
@@ -6019,21 +6015,23 @@
     </row>
     <row r="176" customHeight="1" ht="20">
       <c r="A176" s="5" t="n">
-        <v>1721</v>
+        <v>1042</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>281</v>
+        <v>1</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>822</v>
+        <v>582</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="F176" s="5"/>
+        <v>221</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>1131</v>
+      </c>
       <c r="G176" s="5"/>
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
@@ -6051,13 +6049,13 @@
     </row>
     <row r="177" customHeight="1" ht="20">
       <c r="A177" s="5" t="n">
-        <v>1181</v>
+        <v>1721</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>201</v>
+        <v>281</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>722</v>
+        <v>822</v>
       </c>
       <c r="D177" s="5" t="n">
         <v>2</v>
@@ -6083,19 +6081,19 @@
     </row>
     <row r="178" customHeight="1" ht="20">
       <c r="A178" s="5" t="n">
-        <v>1245</v>
+        <v>1181</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>742</v>
+        <v>722</v>
       </c>
       <c r="D178" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1052</v>
+        <v>26</v>
       </c>
       <c r="F178" s="5"/>
       <c r="G178" s="5"/>
@@ -6115,7 +6113,7 @@
     </row>
     <row r="179" customHeight="1" ht="20">
       <c r="A179" s="5" t="n">
-        <v>1261</v>
+        <v>1245</v>
       </c>
       <c r="B179" s="5" t="n">
         <v>101</v>
@@ -6124,14 +6122,12 @@
         <v>742</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1684</v>
-      </c>
-      <c r="F179" s="5" t="n">
-        <v>1683</v>
-      </c>
+        <v>1052</v>
+      </c>
+      <c r="F179" s="5"/>
       <c r="G179" s="5"/>
       <c r="H179" s="5"/>
       <c r="I179" s="5"/>
@@ -6149,21 +6145,23 @@
     </row>
     <row r="180" customHeight="1" ht="20">
       <c r="A180" s="5" t="n">
-        <v>1662</v>
+        <v>1261</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>381</v>
+        <v>101</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>962</v>
+        <v>742</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1964</v>
-      </c>
-      <c r="F180" s="5"/>
+        <v>1684</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>1683</v>
+      </c>
       <c r="G180" s="5"/>
       <c r="H180" s="5"/>
       <c r="I180" s="5"/>
@@ -6181,23 +6179,21 @@
     </row>
     <row r="181" customHeight="1" ht="20">
       <c r="A181" s="5" t="n">
-        <v>1302</v>
+        <v>1662</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>121</v>
+        <v>381</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>642</v>
+        <v>962</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1704</v>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>1703</v>
-      </c>
+        <v>1964</v>
+      </c>
+      <c r="F181" s="5"/>
       <c r="G181" s="5"/>
       <c r="H181" s="5"/>
       <c r="I181" s="5"/>
@@ -6215,22 +6211,22 @@
     </row>
     <row r="182" customHeight="1" ht="20">
       <c r="A182" s="5" t="n">
-        <v>1663</v>
+        <v>1302</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>381</v>
+        <v>121</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>962</v>
+        <v>642</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1965</v>
+        <v>1704</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>1963</v>
+        <v>1703</v>
       </c>
       <c r="G182" s="5"/>
       <c r="H182" s="5"/>
@@ -6249,21 +6245,23 @@
     </row>
     <row r="183" customHeight="1" ht="20">
       <c r="A183" s="5" t="n">
-        <v>1341</v>
+        <v>1663</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>50</v>
+        <v>381</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>802</v>
+        <v>962</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1783</v>
-      </c>
-      <c r="F183" s="5"/>
+        <v>1965</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>1963</v>
+      </c>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
@@ -6281,7 +6279,7 @@
     </row>
     <row r="184" customHeight="1" ht="20">
       <c r="A184" s="5" t="n">
-        <v>1381</v>
+        <v>1341</v>
       </c>
       <c r="B184" s="5" t="n">
         <v>50</v>
@@ -6293,7 +6291,7 @@
         <v>2</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1823</v>
+        <v>1783</v>
       </c>
       <c r="F184" s="5"/>
       <c r="G184" s="5"/>
@@ -6313,23 +6311,21 @@
     </row>
     <row r="185" customHeight="1" ht="20">
       <c r="A185" s="5" t="n">
-        <v>1421</v>
+        <v>1381</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>642</v>
+        <v>802</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>584</v>
-      </c>
+        <v>1823</v>
+      </c>
+      <c r="F185" s="5"/>
       <c r="G185" s="5"/>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
@@ -6347,22 +6343,22 @@
     </row>
     <row r="186" customHeight="1" ht="20">
       <c r="A186" s="5" t="n">
-        <v>1442</v>
+        <v>1421</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>281</v>
+        <v>121</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>822</v>
+        <v>642</v>
       </c>
       <c r="D186" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>624</v>
+        <v>585</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>625</v>
+        <v>584</v>
       </c>
       <c r="G186" s="5"/>
       <c r="H186" s="5"/>
@@ -6381,7 +6377,7 @@
     </row>
     <row r="187" customHeight="1" ht="20">
       <c r="A187" s="5" t="n">
-        <v>2046</v>
+        <v>1442</v>
       </c>
       <c r="B187" s="5" t="n">
         <v>281</v>
@@ -6390,12 +6386,14 @@
         <v>822</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1404</v>
-      </c>
-      <c r="F187" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>625</v>
+      </c>
       <c r="G187" s="5"/>
       <c r="H187" s="5"/>
       <c r="I187" s="5"/>
@@ -6413,29 +6411,23 @@
     </row>
     <row r="188" customHeight="1" ht="20">
       <c r="A188" s="5" t="n">
-        <v>1521</v>
+        <v>2046</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>662</v>
+        <v>822</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1883</v>
-      </c>
-      <c r="F188" s="5" t="n">
-        <v>1886</v>
-      </c>
-      <c r="G188" s="5" t="n">
-        <v>1884</v>
-      </c>
-      <c r="H188" s="5" t="n">
-        <v>1885</v>
-      </c>
+        <v>1404</v>
+      </c>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
       <c r="K188" s="6" t="s">
@@ -6451,7 +6443,7 @@
     </row>
     <row r="189" customHeight="1" ht="20">
       <c r="A189" s="5" t="n">
-        <v>1541</v>
+        <v>1521</v>
       </c>
       <c r="B189" s="5" t="n">
         <v>241</v>
@@ -6460,16 +6452,20 @@
         <v>662</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1763</v>
+        <v>1883</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>1764</v>
-      </c>
-      <c r="G189" s="5"/>
-      <c r="H189" s="5"/>
+        <v>1886</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>1884</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>1885</v>
+      </c>
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
       <c r="K189" s="6" t="s">
@@ -6485,22 +6481,22 @@
     </row>
     <row r="190" customHeight="1" ht="20">
       <c r="A190" s="5" t="n">
-        <v>1761</v>
+        <v>1541</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>822</v>
+        <v>662</v>
       </c>
       <c r="D190" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>585</v>
+        <v>1763</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>584</v>
+        <v>1764</v>
       </c>
       <c r="G190" s="5"/>
       <c r="H190" s="5"/>
@@ -6519,22 +6515,22 @@
     </row>
     <row r="191" customHeight="1" ht="20">
       <c r="A191" s="5" t="n">
-        <v>1801</v>
+        <v>1761</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>101</v>
+        <v>281</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>1022</v>
+        <v>822</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>121</v>
+        <v>585</v>
       </c>
       <c r="F191" s="5" t="n">
-        <v>2043</v>
+        <v>584</v>
       </c>
       <c r="G191" s="5"/>
       <c r="H191" s="5"/>
@@ -6553,22 +6549,22 @@
     </row>
     <row r="192" customHeight="1" ht="20">
       <c r="A192" s="5" t="n">
-        <v>1842</v>
+        <v>1801</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>1042</v>
+        <v>1022</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1164</v>
+        <v>121</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>1163</v>
+        <v>2043</v>
       </c>
       <c r="G192" s="5"/>
       <c r="H192" s="5"/>
@@ -6587,7 +6583,7 @@
     </row>
     <row r="193" customHeight="1" ht="20">
       <c r="A193" s="5" t="n">
-        <v>1881</v>
+        <v>1842</v>
       </c>
       <c r="B193" s="5" t="n">
         <v>50</v>
@@ -6599,10 +6595,10 @@
         <v>1</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1523</v>
+        <v>1164</v>
       </c>
       <c r="F193" s="5" t="n">
-        <v>1524</v>
+        <v>1163</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
@@ -6621,21 +6617,23 @@
     </row>
     <row r="194" customHeight="1" ht="20">
       <c r="A194" s="5" t="n">
-        <v>2001</v>
+        <v>1881</v>
       </c>
       <c r="B194" s="5" t="n">
-        <v>281</v>
+        <v>50</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>822</v>
+        <v>1042</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1143</v>
-      </c>
-      <c r="F194" s="5"/>
+        <v>1523</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>1524</v>
+      </c>
       <c r="G194" s="5"/>
       <c r="H194" s="5"/>
       <c r="I194" s="5"/>
@@ -6653,7 +6651,7 @@
     </row>
     <row r="195" customHeight="1" ht="20">
       <c r="A195" s="5" t="n">
-        <v>1885</v>
+        <v>2001</v>
       </c>
       <c r="B195" s="5" t="n">
         <v>281</v>
@@ -6662,14 +6660,12 @@
         <v>822</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>2103</v>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>91</v>
-      </c>
+        <v>1143</v>
+      </c>
+      <c r="F195" s="5"/>
       <c r="G195" s="5"/>
       <c r="H195" s="5"/>
       <c r="I195" s="5"/>
@@ -6687,7 +6683,7 @@
     </row>
     <row r="196" customHeight="1" ht="20">
       <c r="A196" s="5" t="n">
-        <v>2045</v>
+        <v>1885</v>
       </c>
       <c r="B196" s="5" t="n">
         <v>281</v>
@@ -6696,12 +6692,14 @@
         <v>822</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1424</v>
-      </c>
-      <c r="F196" s="5"/>
+        <v>2103</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>91</v>
+      </c>
       <c r="G196" s="5"/>
       <c r="H196" s="5"/>
       <c r="I196" s="5"/>
@@ -6719,23 +6717,21 @@
     </row>
     <row r="197" customHeight="1" ht="20">
       <c r="A197" s="5" t="n">
-        <v>2061</v>
+        <v>2045</v>
       </c>
       <c r="B197" s="5" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>1122</v>
+        <v>822</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>624</v>
-      </c>
-      <c r="F197" s="5" t="n">
-        <v>625</v>
-      </c>
+        <v>1424</v>
+      </c>
+      <c r="F197" s="5"/>
       <c r="G197" s="5"/>
       <c r="H197" s="5"/>
       <c r="I197" s="5"/>
@@ -6753,22 +6749,22 @@
     </row>
     <row r="198" customHeight="1" ht="20">
       <c r="A198" s="5" t="n">
-        <v>1944</v>
+        <v>2061</v>
       </c>
       <c r="B198" s="5" t="n">
-        <v>421</v>
+        <v>301</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>1102</v>
+        <v>1122</v>
       </c>
       <c r="D198" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>2186</v>
+        <v>624</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>2185</v>
+        <v>625</v>
       </c>
       <c r="G198" s="5"/>
       <c r="H198" s="5"/>
@@ -6787,7 +6783,7 @@
     </row>
     <row r="199" customHeight="1" ht="20">
       <c r="A199" s="5" t="n">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B199" s="5" t="n">
         <v>421</v>
@@ -6799,10 +6795,10 @@
         <v>1</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="F199" s="5" t="n">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5"/>
@@ -6821,7 +6817,7 @@
     </row>
     <row r="200" customHeight="1" ht="20">
       <c r="A200" s="5" t="n">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B200" s="5" t="n">
         <v>421</v>
@@ -6833,10 +6829,10 @@
         <v>1</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="G200" s="5"/>
       <c r="H200" s="5"/>
@@ -6855,7 +6851,7 @@
     </row>
     <row r="201" customHeight="1" ht="20">
       <c r="A201" s="5" t="n">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B201" s="5" t="n">
         <v>421</v>
@@ -6867,10 +6863,10 @@
         <v>1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>33</v>
+        <v>2189</v>
       </c>
       <c r="F201" s="5" t="n">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5"/>
@@ -6889,22 +6885,22 @@
     </row>
     <row r="202" customHeight="1" ht="20">
       <c r="A202" s="5" t="n">
-        <v>2463</v>
+        <v>1947</v>
       </c>
       <c r="B202" s="5" t="n">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>1302</v>
+        <v>1102</v>
       </c>
       <c r="D202" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>2185</v>
+        <v>33</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>2186</v>
+        <v>2191</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
@@ -6923,7 +6919,7 @@
     </row>
     <row r="203" customHeight="1" ht="20">
       <c r="A203" s="5" t="n">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="B203" s="5" t="n">
         <v>461</v>
@@ -6932,13 +6928,13 @@
         <v>1302</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
@@ -6957,22 +6953,22 @@
     </row>
     <row r="204" customHeight="1" ht="20">
       <c r="A204" s="5" t="n">
-        <v>2521</v>
+        <v>2465</v>
       </c>
       <c r="B204" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>1322</v>
+        <v>1302</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>2543</v>
+        <v>2184</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>2544</v>
+        <v>2183</v>
       </c>
       <c r="G204" s="5"/>
       <c r="H204" s="5"/>
@@ -6991,21 +6987,23 @@
     </row>
     <row r="205" customHeight="1" ht="20">
       <c r="A205" s="5" t="n">
-        <v>2324</v>
+        <v>2521</v>
       </c>
       <c r="B205" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>2363</v>
-      </c>
-      <c r="F205" s="5"/>
+        <v>2543</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>2544</v>
+      </c>
       <c r="G205" s="5"/>
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
@@ -7023,23 +7021,21 @@
     </row>
     <row r="206" customHeight="1" ht="20">
       <c r="A206" s="5" t="n">
-        <v>2341</v>
+        <v>2324</v>
       </c>
       <c r="B206" s="5" t="n">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>2384</v>
-      </c>
-      <c r="F206" s="5" t="n">
-        <v>2383</v>
-      </c>
+        <v>2363</v>
+      </c>
+      <c r="F206" s="5"/>
       <c r="G206" s="5"/>
       <c r="H206" s="5"/>
       <c r="I206" s="5"/>
@@ -7057,21 +7053,23 @@
     </row>
     <row r="207" customHeight="1" ht="20">
       <c r="A207" s="5" t="n">
-        <v>2362</v>
+        <v>2341</v>
       </c>
       <c r="B207" s="5" t="n">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>1222</v>
+        <v>1162</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F207" s="5"/>
+        <v>2384</v>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>2383</v>
+      </c>
       <c r="G207" s="5"/>
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
@@ -7089,7 +7087,7 @@
     </row>
     <row r="208" customHeight="1" ht="20">
       <c r="A208" s="5" t="n">
-        <v>2441</v>
+        <v>2362</v>
       </c>
       <c r="B208" s="5" t="n">
         <v>461</v>
@@ -7101,7 +7099,7 @@
         <v>2</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>2483</v>
+        <v>2064</v>
       </c>
       <c r="F208" s="5"/>
       <c r="G208" s="5"/>
@@ -7121,23 +7119,21 @@
     </row>
     <row r="209" customHeight="1" ht="20">
       <c r="A209" s="5" t="n">
-        <v>2541</v>
+        <v>2441</v>
       </c>
       <c r="B209" s="5" t="n">
-        <v>27</v>
+        <v>461</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>1342</v>
+        <v>1222</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>2563</v>
-      </c>
-      <c r="F209" s="5" t="n">
-        <v>2564</v>
-      </c>
+        <v>2483</v>
+      </c>
+      <c r="F209" s="5"/>
       <c r="G209" s="5"/>
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
@@ -7155,21 +7151,23 @@
     </row>
     <row r="210" customHeight="1" ht="20">
       <c r="A210" s="5" t="n">
-        <v>2582</v>
+        <v>2541</v>
       </c>
       <c r="B210" s="5" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>1162</v>
+        <v>1342</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F210" s="5"/>
+        <v>2563</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>2564</v>
+      </c>
       <c r="G210" s="5"/>
       <c r="H210" s="5"/>
       <c r="I210" s="5"/>
@@ -7187,23 +7185,21 @@
     </row>
     <row r="211" customHeight="1" ht="20">
       <c r="A211" s="5" t="n">
-        <v>2661</v>
+        <v>2582</v>
       </c>
       <c r="B211" s="5" t="n">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>1202</v>
+        <v>1162</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>2664</v>
-      </c>
-      <c r="F211" s="5" t="n">
-        <v>2663</v>
-      </c>
+        <v>1563</v>
+      </c>
+      <c r="F211" s="5"/>
       <c r="G211" s="5"/>
       <c r="H211" s="5"/>
       <c r="I211" s="5"/>
@@ -7221,22 +7217,22 @@
     </row>
     <row r="212" customHeight="1" ht="20">
       <c r="A212" s="5" t="n">
-        <v>2702</v>
+        <v>2661</v>
       </c>
       <c r="B212" s="5" t="n">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>1342</v>
+        <v>1202</v>
       </c>
       <c r="D212" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>587</v>
+        <v>2664</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>586</v>
+        <v>2663</v>
       </c>
       <c r="G212" s="5"/>
       <c r="H212" s="5"/>
@@ -7255,22 +7251,22 @@
     </row>
     <row r="213" customHeight="1" ht="20">
       <c r="A213" s="5" t="n">
-        <v>2741</v>
+        <v>2702</v>
       </c>
       <c r="B213" s="5" t="n">
-        <v>421</v>
+        <v>27</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>1363</v>
+        <v>1342</v>
       </c>
       <c r="D213" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>624</v>
+        <v>587</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>625</v>
+        <v>586</v>
       </c>
       <c r="G213" s="5"/>
       <c r="H213" s="5"/>
@@ -7289,22 +7285,22 @@
     </row>
     <row r="214" customHeight="1" ht="20">
       <c r="A214" s="5" t="n">
-        <v>3101</v>
+        <v>2741</v>
       </c>
       <c r="B214" s="5" t="n">
-        <v>481</v>
+        <v>421</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>1282</v>
+        <v>1363</v>
       </c>
       <c r="D214" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>2884</v>
+        <v>624</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>2883</v>
+        <v>625</v>
       </c>
       <c r="G214" s="5"/>
       <c r="H214" s="5"/>
@@ -7323,21 +7319,23 @@
     </row>
     <row r="215" customHeight="1" ht="20">
       <c r="A215" s="5" t="n">
-        <v>2801</v>
+        <v>3101</v>
       </c>
       <c r="B215" s="5" t="n">
-        <v>25</v>
+        <v>481</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>1383</v>
+        <v>1282</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>2743</v>
-      </c>
-      <c r="F215" s="5"/>
+        <v>2884</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>2883</v>
+      </c>
       <c r="G215" s="5"/>
       <c r="H215" s="5"/>
       <c r="I215" s="5"/>
@@ -7355,19 +7353,19 @@
     </row>
     <row r="216" customHeight="1" ht="20">
       <c r="A216" s="5" t="n">
-        <v>2822</v>
+        <v>2801</v>
       </c>
       <c r="B216" s="5" t="n">
-        <v>261</v>
+        <v>25</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>1202</v>
+        <v>1383</v>
       </c>
       <c r="D216" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>2523</v>
+        <v>2743</v>
       </c>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
@@ -7387,7 +7385,7 @@
     </row>
     <row r="217" customHeight="1" ht="20">
       <c r="A217" s="5" t="n">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="B217" s="5" t="n">
         <v>261</v>
@@ -7399,7 +7397,7 @@
         <v>2</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>2323</v>
+        <v>2523</v>
       </c>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
@@ -7419,23 +7417,21 @@
     </row>
     <row r="218" customHeight="1" ht="20">
       <c r="A218" s="5" t="n">
-        <v>2842</v>
+        <v>2823</v>
       </c>
       <c r="B218" s="5" t="n">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>1342</v>
+        <v>1202</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>2764</v>
-      </c>
-      <c r="F218" s="5" t="n">
-        <v>2783</v>
-      </c>
+        <v>2323</v>
+      </c>
+      <c r="F218" s="5"/>
       <c r="G218" s="5"/>
       <c r="H218" s="5"/>
       <c r="I218" s="5"/>
@@ -7453,22 +7449,22 @@
     </row>
     <row r="219" customHeight="1" ht="20">
       <c r="A219" s="5" t="n">
-        <v>3021</v>
+        <v>2842</v>
       </c>
       <c r="B219" s="5" t="n">
-        <v>501</v>
+        <v>27</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>1322</v>
+        <v>1342</v>
       </c>
       <c r="D219" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>1023</v>
+        <v>2764</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>1024</v>
+        <v>2783</v>
       </c>
       <c r="G219" s="5"/>
       <c r="H219" s="5"/>
@@ -7487,22 +7483,22 @@
     </row>
     <row r="220" customHeight="1" ht="20">
       <c r="A220" s="5" t="n">
-        <v>3381</v>
+        <v>3021</v>
       </c>
       <c r="B220" s="5" t="n">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>1423</v>
+        <v>1322</v>
       </c>
       <c r="D220" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>2963</v>
+        <v>1023</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>2964</v>
+        <v>1024</v>
       </c>
       <c r="G220" s="5"/>
       <c r="H220" s="5"/>
@@ -7521,7 +7517,7 @@
     </row>
     <row r="221" customHeight="1" ht="20">
       <c r="A221" s="5" t="n">
-        <v>3321</v>
+        <v>3381</v>
       </c>
       <c r="B221" s="5" t="n">
         <v>521</v>
@@ -7530,12 +7526,14 @@
         <v>1423</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>1583</v>
-      </c>
-      <c r="F221" s="5"/>
+        <v>2963</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>2964</v>
+      </c>
       <c r="G221" s="5"/>
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
@@ -7553,55 +7551,55 @@
     </row>
     <row r="222" customHeight="1" ht="20">
       <c r="A222" s="5" t="n">
-        <v>3401</v>
+        <v>3321</v>
       </c>
       <c r="B222" s="5" t="n">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>1503</v>
+        <v>1423</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>3003</v>
-      </c>
-      <c r="F222" s="5" t="n">
-        <v>3023</v>
-      </c>
+        <v>1583</v>
+      </c>
+      <c r="F222" s="5"/>
       <c r="G222" s="5"/>
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
       <c r="K222" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L222" s="7"/>
       <c r="M222" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N222" s="7" t="n">
-        <v>45831.8393287037</v>
+        <v>45831.8349884259</v>
       </c>
     </row>
     <row r="223" customHeight="1" ht="20">
       <c r="A223" s="5" t="n">
-        <v>3843</v>
+        <v>3401</v>
       </c>
       <c r="B223" s="5" t="n">
         <v>541</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>1664</v>
+        <v>1503</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>3465</v>
-      </c>
-      <c r="F223" s="5"/>
+        <v>3003</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>3023</v>
+      </c>
       <c r="G223" s="5"/>
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
@@ -7609,31 +7607,31 @@
       <c r="K223" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L223" s="7" t="n">
-        <v>45896.2966550926</v>
-      </c>
-      <c r="M223" s="6"/>
-      <c r="N223" s="7"/>
+      <c r="L223" s="7"/>
+      <c r="M223" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N223" s="7" t="n">
+        <v>45831.8393287037</v>
+      </c>
     </row>
     <row r="224" customHeight="1" ht="20">
       <c r="A224" s="5" t="n">
-        <v>3406</v>
+        <v>3843</v>
       </c>
       <c r="B224" s="5" t="n">
         <v>541</v>
       </c>
       <c r="C224" s="5" t="n">
-        <v>1503</v>
+        <v>1664</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>3028</v>
-      </c>
-      <c r="F224" s="5" t="n">
-        <v>3029</v>
-      </c>
+        <v>3465</v>
+      </c>
+      <c r="F224" s="5"/>
       <c r="G224" s="5"/>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
@@ -7641,31 +7639,31 @@
       <c r="K224" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L224" s="7"/>
-      <c r="M224" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N224" s="7" t="n">
-        <v>45831.8393287037</v>
-      </c>
+      <c r="L224" s="7" t="n">
+        <v>45896.2966550926</v>
+      </c>
+      <c r="M224" s="6"/>
+      <c r="N224" s="7"/>
     </row>
     <row r="225" customHeight="1" ht="20">
       <c r="A225" s="5" t="n">
-        <v>3961</v>
+        <v>3406</v>
       </c>
       <c r="B225" s="5" t="n">
-        <v>722</v>
+        <v>541</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>1684</v>
+        <v>1503</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>3589</v>
-      </c>
-      <c r="F225" s="5"/>
+        <v>3028</v>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>3029</v>
+      </c>
       <c r="G225" s="5"/>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
@@ -7673,31 +7671,31 @@
       <c r="K225" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L225" s="7" t="n">
-        <v>45935.4751157407</v>
-      </c>
-      <c r="M225" s="6"/>
-      <c r="N225" s="7"/>
+      <c r="L225" s="7"/>
+      <c r="M225" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N225" s="7" t="n">
+        <v>45831.8393287037</v>
+      </c>
     </row>
     <row r="226" customHeight="1" ht="20">
       <c r="A226" s="5" t="n">
-        <v>4061</v>
+        <v>3961</v>
       </c>
       <c r="B226" s="5" t="n">
-        <v>762</v>
+        <v>722</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>1724</v>
+        <v>1684</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>3663</v>
-      </c>
-      <c r="F226" s="5" t="n">
-        <v>3664</v>
-      </c>
+        <v>3589</v>
+      </c>
+      <c r="F226" s="5"/>
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
@@ -7706,14 +7704,14 @@
         <v>15</v>
       </c>
       <c r="L226" s="7" t="n">
-        <v>45964.6311342593</v>
+        <v>45935.4751157407</v>
       </c>
       <c r="M226" s="6"/>
       <c r="N226" s="7"/>
     </row>
     <row r="227" customHeight="1" ht="20">
       <c r="A227" s="5" t="n">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="B227" s="5" t="n">
         <v>762</v>
@@ -7725,10 +7723,10 @@
         <v>1</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>584</v>
+        <v>3663</v>
       </c>
       <c r="F227" s="5" t="n">
-        <v>585</v>
+        <v>3664</v>
       </c>
       <c r="G227" s="5"/>
       <c r="H227" s="5"/>
@@ -7738,29 +7736,29 @@
         <v>15</v>
       </c>
       <c r="L227" s="7" t="n">
-        <v>45965.4697453704</v>
+        <v>45964.6311342593</v>
       </c>
       <c r="M227" s="6"/>
       <c r="N227" s="7"/>
     </row>
     <row r="228" customHeight="1" ht="20">
       <c r="A228" s="5" t="n">
-        <v>4064</v>
+        <v>4062</v>
       </c>
       <c r="B228" s="5" t="n">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>1743</v>
+        <v>1724</v>
       </c>
       <c r="D228" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>3669</v>
+        <v>584</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>3666</v>
+        <v>585</v>
       </c>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
@@ -7770,14 +7768,14 @@
         <v>15</v>
       </c>
       <c r="L228" s="7" t="n">
-        <v>45966.4389236111</v>
+        <v>45965.4697453704</v>
       </c>
       <c r="M228" s="6"/>
       <c r="N228" s="7"/>
     </row>
     <row r="229" customHeight="1" ht="20">
       <c r="A229" s="5" t="n">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="B229" s="5" t="n">
         <v>781</v>
@@ -7786,12 +7784,14 @@
         <v>1743</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>3670</v>
-      </c>
-      <c r="F229" s="5"/>
+        <v>3669</v>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>3666</v>
+      </c>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
@@ -7800,14 +7800,14 @@
         <v>15</v>
       </c>
       <c r="L229" s="7" t="n">
-        <v>45966.5908101852</v>
+        <v>45966.4389236111</v>
       </c>
       <c r="M229" s="6"/>
       <c r="N229" s="7"/>
     </row>
     <row r="230" customHeight="1" ht="20">
       <c r="A230" s="5" t="n">
-        <v>4066</v>
+        <v>4065</v>
       </c>
       <c r="B230" s="5" t="n">
         <v>781</v>
@@ -7816,10 +7816,10 @@
         <v>1743</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>81</v>
+        <v>3670</v>
       </c>
       <c r="F230" s="5"/>
       <c r="G230" s="5"/>
@@ -7830,14 +7830,14 @@
         <v>15</v>
       </c>
       <c r="L230" s="7" t="n">
-        <v>45966.7075231481</v>
+        <v>45966.5908101852</v>
       </c>
       <c r="M230" s="6"/>
       <c r="N230" s="7"/>
     </row>
     <row r="231" customHeight="1" ht="20">
       <c r="A231" s="5" t="n">
-        <v>4068</v>
+        <v>4066</v>
       </c>
       <c r="B231" s="5" t="n">
         <v>781</v>
@@ -7846,14 +7846,12 @@
         <v>1743</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>3676</v>
-      </c>
-      <c r="F231" s="5" t="n">
-        <v>3675</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F231" s="5"/>
       <c r="G231" s="5"/>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
@@ -7862,14 +7860,14 @@
         <v>15</v>
       </c>
       <c r="L231" s="7" t="n">
-        <v>45967.3274768519</v>
+        <v>45966.7075231481</v>
       </c>
       <c r="M231" s="6"/>
       <c r="N231" s="7"/>
     </row>
     <row r="232" customHeight="1" ht="20">
       <c r="A232" s="5" t="n">
-        <v>4069</v>
+        <v>4068</v>
       </c>
       <c r="B232" s="5" t="n">
         <v>781</v>
@@ -7881,10 +7879,10 @@
         <v>1</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>3677</v>
+        <v>3675</v>
       </c>
       <c r="G232" s="5"/>
       <c r="H232" s="5"/>
@@ -7894,14 +7892,14 @@
         <v>15</v>
       </c>
       <c r="L232" s="7" t="n">
-        <v>45967.4627314815</v>
+        <v>45967.3274768519</v>
       </c>
       <c r="M232" s="6"/>
       <c r="N232" s="7"/>
     </row>
     <row r="233" customHeight="1" ht="20">
       <c r="A233" s="5" t="n">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="B233" s="5" t="n">
         <v>781</v>
@@ -7913,10 +7911,10 @@
         <v>1</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>2203</v>
+        <v>3678</v>
       </c>
       <c r="F233" s="5" t="n">
-        <v>3679</v>
+        <v>3677</v>
       </c>
       <c r="G233" s="5"/>
       <c r="H233" s="5"/>
@@ -7926,29 +7924,29 @@
         <v>15</v>
       </c>
       <c r="L233" s="7" t="n">
-        <v>45967.5829398148</v>
+        <v>45967.4627314815</v>
       </c>
       <c r="M233" s="6"/>
       <c r="N233" s="7"/>
     </row>
     <row r="234" customHeight="1" ht="20">
       <c r="A234" s="5" t="n">
-        <v>4303</v>
+        <v>4070</v>
       </c>
       <c r="B234" s="5" t="n">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>1724</v>
+        <v>1743</v>
       </c>
       <c r="D234" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>3868</v>
+        <v>2203</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>3869</v>
+        <v>3679</v>
       </c>
       <c r="G234" s="5"/>
       <c r="H234" s="5"/>
@@ -7958,29 +7956,29 @@
         <v>15</v>
       </c>
       <c r="L234" s="7" t="n">
-        <v>46014.8150231481</v>
+        <v>45967.5829398148</v>
       </c>
       <c r="M234" s="6"/>
       <c r="N234" s="7"/>
     </row>
     <row r="235" customHeight="1" ht="20">
       <c r="A235" s="5" t="n">
-        <v>4321</v>
+        <v>4303</v>
       </c>
       <c r="B235" s="5" t="n">
-        <v>801</v>
+        <v>762</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>1763</v>
+        <v>1724</v>
       </c>
       <c r="D235" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>3888</v>
+        <v>3868</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>3884</v>
+        <v>3869</v>
       </c>
       <c r="G235" s="5"/>
       <c r="H235" s="5"/>
@@ -7990,63 +7988,61 @@
         <v>15</v>
       </c>
       <c r="L235" s="7" t="n">
-        <v>46030.6246180556</v>
+        <v>46014.8150231481</v>
       </c>
       <c r="M235" s="6"/>
       <c r="N235" s="7"/>
     </row>
     <row r="236" customHeight="1" ht="20">
       <c r="A236" s="5" t="n">
-        <v>41</v>
+        <v>4321</v>
       </c>
       <c r="B236" s="5" t="n">
-        <v>1</v>
+        <v>801</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>182</v>
+        <v>1763</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>485</v>
+        <v>3888</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>486</v>
+        <v>3884</v>
       </c>
       <c r="G236" s="5"/>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
       <c r="K236" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L236" s="7"/>
-      <c r="M236" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N236" s="7" t="n">
-        <v>45831.8349884259</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L236" s="7" t="n">
+        <v>46030.6246180556</v>
+      </c>
+      <c r="M236" s="6"/>
+      <c r="N236" s="7"/>
     </row>
     <row r="237" customHeight="1" ht="20">
       <c r="A237" s="5" t="n">
-        <v>57</v>
+        <v>4362</v>
       </c>
       <c r="B237" s="5" t="n">
-        <v>41</v>
+        <v>861</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>242</v>
+        <v>1823</v>
       </c>
       <c r="D237" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>587</v>
+        <v>3026</v>
       </c>
       <c r="F237" s="5" t="n">
-        <v>586</v>
+        <v>3027</v>
       </c>
       <c r="G237" s="5"/>
       <c r="H237" s="5"/>
@@ -8055,32 +8051,30 @@
       <c r="K237" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L237" s="7"/>
-      <c r="M237" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N237" s="7" t="n">
-        <v>45831.8349884259</v>
-      </c>
+      <c r="L237" s="7" t="n">
+        <v>46037.6662037037</v>
+      </c>
+      <c r="M237" s="6"/>
+      <c r="N237" s="7"/>
     </row>
     <row r="238" customHeight="1" ht="20">
       <c r="A238" s="5" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B238" s="5" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>262</v>
+        <v>182</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>624</v>
+        <v>485</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>625</v>
+        <v>486</v>
       </c>
       <c r="G238" s="5"/>
       <c r="H238" s="5"/>
@@ -8099,22 +8093,22 @@
     </row>
     <row r="239" customHeight="1" ht="20">
       <c r="A239" s="5" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B239" s="5" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="D239" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>261</v>
+        <v>587</v>
       </c>
       <c r="F239" s="5" t="n">
-        <v>623</v>
+        <v>586</v>
       </c>
       <c r="G239" s="5"/>
       <c r="H239" s="5"/>
@@ -8133,21 +8127,23 @@
     </row>
     <row r="240" customHeight="1" ht="20">
       <c r="A240" s="5" t="n">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="B240" s="5" t="n">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>664</v>
-      </c>
-      <c r="F240" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>625</v>
+      </c>
       <c r="G240" s="5"/>
       <c r="H240" s="5"/>
       <c r="I240" s="5"/>
@@ -8165,22 +8161,22 @@
     </row>
     <row r="241" customHeight="1" ht="20">
       <c r="A241" s="5" t="n">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="B241" s="5" t="n">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>342</v>
+        <v>262</v>
       </c>
       <c r="D241" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>706</v>
+        <v>261</v>
       </c>
       <c r="F241" s="5" t="n">
-        <v>707</v>
+        <v>623</v>
       </c>
       <c r="G241" s="5"/>
       <c r="H241" s="5"/>
@@ -8199,19 +8195,19 @@
     </row>
     <row r="242" customHeight="1" ht="20">
       <c r="A242" s="5" t="n">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="B242" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="F242" s="5"/>
       <c r="G242" s="5"/>
@@ -8231,22 +8227,22 @@
     </row>
     <row r="243" customHeight="1" ht="20">
       <c r="A243" s="5" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B243" s="5" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="D243" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="F243" s="5" t="n">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="G243" s="5"/>
       <c r="H243" s="5"/>
@@ -8265,7 +8261,7 @@
     </row>
     <row r="244" customHeight="1" ht="20">
       <c r="A244" s="5" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B244" s="5" t="n">
         <v>25</v>
@@ -8277,11 +8273,9 @@
         <v>1</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>727</v>
-      </c>
-      <c r="F244" s="5" t="n">
-        <v>728</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="F244" s="5"/>
       <c r="G244" s="5"/>
       <c r="H244" s="5"/>
       <c r="I244" s="5"/>
@@ -8299,22 +8293,22 @@
     </row>
     <row r="245" customHeight="1" ht="20">
       <c r="A245" s="5" t="n">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B245" s="5" t="n">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="D245" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F245" s="5" t="n">
-        <v>282</v>
+        <v>724</v>
       </c>
       <c r="G245" s="5"/>
       <c r="H245" s="5"/>
@@ -8333,22 +8327,22 @@
     </row>
     <row r="246" customHeight="1" ht="20">
       <c r="A246" s="5" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B246" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="D246" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>585</v>
+        <v>727</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>584</v>
+        <v>728</v>
       </c>
       <c r="G246" s="5"/>
       <c r="H246" s="5"/>
@@ -8367,26 +8361,24 @@
     </row>
     <row r="247" customHeight="1" ht="20">
       <c r="A247" s="5" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="B247" s="5" t="n">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="C247" s="5" t="n">
-        <v>382</v>
+        <v>262</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>769</v>
+        <v>725</v>
       </c>
       <c r="F247" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="G247" s="5" t="n">
-        <v>768</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="G247" s="5"/>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
@@ -8403,22 +8395,22 @@
     </row>
     <row r="248" customHeight="1" ht="20">
       <c r="A248" s="5" t="n">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="B248" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="D248" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>624</v>
+        <v>585</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>625</v>
+        <v>584</v>
       </c>
       <c r="G248" s="5"/>
       <c r="H248" s="5"/>
@@ -8437,24 +8429,26 @@
     </row>
     <row r="249" customHeight="1" ht="20">
       <c r="A249" s="5" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="B249" s="5" t="n">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>262</v>
+        <v>382</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>31</v>
+        <v>769</v>
       </c>
       <c r="F249" s="5" t="n">
-        <v>772</v>
-      </c>
-      <c r="G249" s="5"/>
+        <v>767</v>
+      </c>
+      <c r="G249" s="5" t="n">
+        <v>768</v>
+      </c>
       <c r="H249" s="5"/>
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
@@ -8471,22 +8465,22 @@
     </row>
     <row r="250" customHeight="1" ht="20">
       <c r="A250" s="5" t="n">
-        <v>461</v>
+        <v>203</v>
       </c>
       <c r="B250" s="5" t="n">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>262</v>
+        <v>382</v>
       </c>
       <c r="D250" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>1023</v>
+        <v>624</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>1024</v>
+        <v>625</v>
       </c>
       <c r="G250" s="5"/>
       <c r="H250" s="5"/>
@@ -8505,22 +8499,22 @@
     </row>
     <row r="251" customHeight="1" ht="20">
       <c r="A251" s="5" t="n">
-        <v>521</v>
+        <v>223</v>
       </c>
       <c r="B251" s="5" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>462</v>
+        <v>262</v>
       </c>
       <c r="D251" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>725</v>
+        <v>31</v>
       </c>
       <c r="F251" s="5" t="n">
-        <v>282</v>
+        <v>772</v>
       </c>
       <c r="G251" s="5"/>
       <c r="H251" s="5"/>
@@ -8539,22 +8533,22 @@
     </row>
     <row r="252" customHeight="1" ht="20">
       <c r="A252" s="5" t="n">
-        <v>721</v>
+        <v>461</v>
       </c>
       <c r="B252" s="5" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>462</v>
+        <v>262</v>
       </c>
       <c r="D252" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>990</v>
+        <v>1023</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>989</v>
+        <v>1024</v>
       </c>
       <c r="G252" s="5"/>
       <c r="H252" s="5"/>
@@ -8573,22 +8567,22 @@
     </row>
     <row r="253" customHeight="1" ht="20">
       <c r="A253" s="5" t="n">
-        <v>242</v>
+        <v>521</v>
       </c>
       <c r="B253" s="5" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>322</v>
+        <v>462</v>
       </c>
       <c r="D253" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>524</v>
+        <v>725</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>523</v>
+        <v>282</v>
       </c>
       <c r="G253" s="5"/>
       <c r="H253" s="5"/>
@@ -8607,21 +8601,23 @@
     </row>
     <row r="254" customHeight="1" ht="20">
       <c r="A254" s="5" t="n">
-        <v>243</v>
+        <v>721</v>
       </c>
       <c r="B254" s="5" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>322</v>
+        <v>462</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>764</v>
-      </c>
-      <c r="F254" s="5"/>
+        <v>990</v>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>989</v>
+      </c>
       <c r="G254" s="5"/>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
@@ -8639,22 +8635,22 @@
     </row>
     <row r="255" customHeight="1" ht="20">
       <c r="A255" s="5" t="n">
-        <v>605</v>
+        <v>242</v>
       </c>
       <c r="B255" s="5" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>844</v>
+        <v>524</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>91</v>
+        <v>523</v>
       </c>
       <c r="G255" s="5"/>
       <c r="H255" s="5"/>
@@ -8673,19 +8669,19 @@
     </row>
     <row r="256" customHeight="1" ht="20">
       <c r="A256" s="5" t="n">
-        <v>762</v>
+        <v>243</v>
       </c>
       <c r="B256" s="5" t="n">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>502</v>
+        <v>322</v>
       </c>
       <c r="D256" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>1424</v>
+        <v>764</v>
       </c>
       <c r="F256" s="5"/>
       <c r="G256" s="5"/>
@@ -8705,22 +8701,22 @@
     </row>
     <row r="257" customHeight="1" ht="20">
       <c r="A257" s="5" t="n">
-        <v>1163</v>
+        <v>605</v>
       </c>
       <c r="B257" s="5" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>702</v>
+        <v>262</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>1023</v>
+        <v>844</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>1024</v>
+        <v>91</v>
       </c>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
@@ -8739,23 +8735,21 @@
     </row>
     <row r="258" customHeight="1" ht="20">
       <c r="A258" s="5" t="n">
-        <v>1021</v>
+        <v>762</v>
       </c>
       <c r="B258" s="5" t="n">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>562</v>
+        <v>502</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>1383</v>
-      </c>
-      <c r="F258" s="5" t="n">
-        <v>1384</v>
-      </c>
+        <v>1424</v>
+      </c>
+      <c r="F258" s="5"/>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
@@ -8773,21 +8767,23 @@
     </row>
     <row r="259" customHeight="1" ht="20">
       <c r="A259" s="5" t="n">
-        <v>1324</v>
+        <v>1163</v>
       </c>
       <c r="B259" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>642</v>
+        <v>702</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>1743</v>
-      </c>
-      <c r="F259" s="5"/>
+        <v>1023</v>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>1024</v>
+      </c>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
@@ -8805,22 +8801,22 @@
     </row>
     <row r="260" customHeight="1" ht="20">
       <c r="A260" s="5" t="n">
-        <v>1246</v>
+        <v>1021</v>
       </c>
       <c r="B260" s="5" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>742</v>
+        <v>562</v>
       </c>
       <c r="D260" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>1664</v>
+        <v>1383</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>1663</v>
+        <v>1384</v>
       </c>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
@@ -8839,7 +8835,7 @@
     </row>
     <row r="261" customHeight="1" ht="20">
       <c r="A261" s="5" t="n">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B261" s="5" t="n">
         <v>121</v>
@@ -8851,7 +8847,7 @@
         <v>2</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>1723</v>
+        <v>1743</v>
       </c>
       <c r="F261" s="5"/>
       <c r="G261" s="5"/>
@@ -8871,21 +8867,23 @@
     </row>
     <row r="262" customHeight="1" ht="20">
       <c r="A262" s="5" t="n">
-        <v>1622</v>
+        <v>1246</v>
       </c>
       <c r="B262" s="5" t="n">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>922</v>
+        <v>742</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>1923</v>
-      </c>
-      <c r="F262" s="5"/>
+        <v>1664</v>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>1663</v>
+      </c>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
@@ -8903,23 +8901,21 @@
     </row>
     <row r="263" customHeight="1" ht="20">
       <c r="A263" s="5" t="n">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="B263" s="5" t="n">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>802</v>
+        <v>642</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>1764</v>
-      </c>
-      <c r="F263" s="5" t="n">
-        <v>1763</v>
-      </c>
+        <v>1723</v>
+      </c>
+      <c r="F263" s="5"/>
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
       <c r="I263" s="5"/>
@@ -8937,23 +8933,21 @@
     </row>
     <row r="264" customHeight="1" ht="20">
       <c r="A264" s="5" t="n">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="B264" s="5" t="n">
-        <v>321</v>
+        <v>46</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>862</v>
+        <v>922</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>963</v>
-      </c>
-      <c r="F264" s="5" t="n">
-        <v>964</v>
-      </c>
+        <v>1923</v>
+      </c>
+      <c r="F264" s="5"/>
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
@@ -8971,22 +8965,22 @@
     </row>
     <row r="265" customHeight="1" ht="20">
       <c r="A265" s="5" t="n">
-        <v>1461</v>
+        <v>1328</v>
       </c>
       <c r="B265" s="5" t="n">
-        <v>241</v>
+        <v>50</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>662</v>
+        <v>802</v>
       </c>
       <c r="D265" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>624</v>
+        <v>1764</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>625</v>
+        <v>1763</v>
       </c>
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
@@ -9005,21 +8999,23 @@
     </row>
     <row r="266" customHeight="1" ht="20">
       <c r="A266" s="5" t="n">
-        <v>1821</v>
+        <v>1624</v>
       </c>
       <c r="B266" s="5" t="n">
-        <v>101</v>
+        <v>321</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>1022</v>
+        <v>862</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F266" s="5"/>
+        <v>963</v>
+      </c>
+      <c r="F266" s="5" t="n">
+        <v>964</v>
+      </c>
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
@@ -9037,22 +9033,22 @@
     </row>
     <row r="267" customHeight="1" ht="20">
       <c r="A267" s="5" t="n">
-        <v>1581</v>
+        <v>1461</v>
       </c>
       <c r="B267" s="5" t="n">
-        <v>321</v>
+        <v>241</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>862</v>
+        <v>662</v>
       </c>
       <c r="D267" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>261</v>
+        <v>624</v>
       </c>
       <c r="F267" s="5" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G267" s="5"/>
       <c r="H267" s="5"/>
@@ -9071,19 +9067,19 @@
     </row>
     <row r="268" customHeight="1" ht="20">
       <c r="A268" s="5" t="n">
-        <v>1643</v>
+        <v>1821</v>
       </c>
       <c r="B268" s="5" t="n">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>942</v>
+        <v>1022</v>
       </c>
       <c r="D268" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>1946</v>
+        <v>1563</v>
       </c>
       <c r="F268" s="5"/>
       <c r="G268" s="5"/>
@@ -9103,21 +9099,23 @@
     </row>
     <row r="269" customHeight="1" ht="20">
       <c r="A269" s="5" t="n">
-        <v>1645</v>
+        <v>1581</v>
       </c>
       <c r="B269" s="5" t="n">
-        <v>26</v>
+        <v>321</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>942</v>
+        <v>862</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>1943</v>
-      </c>
-      <c r="F269" s="5"/>
+        <v>261</v>
+      </c>
+      <c r="F269" s="5" t="n">
+        <v>623</v>
+      </c>
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
@@ -9135,19 +9133,19 @@
     </row>
     <row r="270" customHeight="1" ht="20">
       <c r="A270" s="5" t="n">
-        <v>1685</v>
+        <v>1643</v>
       </c>
       <c r="B270" s="5" t="n">
-        <v>401</v>
+        <v>26</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>982</v>
+        <v>942</v>
       </c>
       <c r="D270" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>763</v>
+        <v>1946</v>
       </c>
       <c r="F270" s="5"/>
       <c r="G270" s="5"/>
@@ -9167,19 +9165,19 @@
     </row>
     <row r="271" customHeight="1" ht="20">
       <c r="A271" s="5" t="n">
-        <v>1844</v>
+        <v>1645</v>
       </c>
       <c r="B271" s="5" t="n">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>822</v>
+        <v>942</v>
       </c>
       <c r="D271" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>2085</v>
+        <v>1943</v>
       </c>
       <c r="F271" s="5"/>
       <c r="G271" s="5"/>
@@ -9199,23 +9197,21 @@
     </row>
     <row r="272" customHeight="1" ht="20">
       <c r="A272" s="5" t="n">
-        <v>1902</v>
+        <v>1685</v>
       </c>
       <c r="B272" s="5" t="n">
-        <v>50</v>
+        <v>401</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>1042</v>
+        <v>982</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>1864</v>
-      </c>
-      <c r="F272" s="5" t="n">
-        <v>1863</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="F272" s="5"/>
       <c r="G272" s="5"/>
       <c r="H272" s="5"/>
       <c r="I272" s="5"/>
@@ -9233,19 +9229,19 @@
     </row>
     <row r="273" customHeight="1" ht="20">
       <c r="A273" s="5" t="n">
-        <v>2044</v>
+        <v>1844</v>
       </c>
       <c r="B273" s="5" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>1122</v>
+        <v>822</v>
       </c>
       <c r="D273" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>2267</v>
+        <v>2085</v>
       </c>
       <c r="F273" s="5"/>
       <c r="G273" s="5"/>
@@ -9265,22 +9261,22 @@
     </row>
     <row r="274" customHeight="1" ht="20">
       <c r="A274" s="5" t="n">
-        <v>2121</v>
+        <v>1902</v>
       </c>
       <c r="B274" s="5" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>1162</v>
+        <v>1042</v>
       </c>
       <c r="D274" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>2283</v>
+        <v>1864</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>2284</v>
+        <v>1863</v>
       </c>
       <c r="G274" s="5"/>
       <c r="H274" s="5"/>
@@ -9299,19 +9295,19 @@
     </row>
     <row r="275" customHeight="1" ht="20">
       <c r="A275" s="5" t="n">
-        <v>2142</v>
+        <v>2044</v>
       </c>
       <c r="B275" s="5" t="n">
-        <v>441</v>
+        <v>301</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>1182</v>
+        <v>1122</v>
       </c>
       <c r="D275" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>1150</v>
+        <v>2267</v>
       </c>
       <c r="F275" s="5"/>
       <c r="G275" s="5"/>
@@ -9331,22 +9327,22 @@
     </row>
     <row r="276" customHeight="1" ht="20">
       <c r="A276" s="5" t="n">
-        <v>2143</v>
+        <v>2121</v>
       </c>
       <c r="B276" s="5" t="n">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>1182</v>
+        <v>1162</v>
       </c>
       <c r="D276" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>585</v>
+        <v>2283</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>584</v>
+        <v>2284</v>
       </c>
       <c r="G276" s="5"/>
       <c r="H276" s="5"/>
@@ -9365,23 +9361,21 @@
     </row>
     <row r="277" customHeight="1" ht="20">
       <c r="A277" s="5" t="n">
-        <v>3041</v>
+        <v>2142</v>
       </c>
       <c r="B277" s="5" t="n">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>1322</v>
+        <v>1182</v>
       </c>
       <c r="D277" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>2863</v>
-      </c>
-      <c r="F277" s="5" t="n">
-        <v>2823</v>
-      </c>
+        <v>1150</v>
+      </c>
+      <c r="F277" s="5"/>
       <c r="G277" s="5"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
@@ -9399,22 +9393,22 @@
     </row>
     <row r="278" customHeight="1" ht="20">
       <c r="A278" s="5" t="n">
-        <v>3061</v>
+        <v>2143</v>
       </c>
       <c r="B278" s="5" t="n">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>1322</v>
+        <v>1182</v>
       </c>
       <c r="D278" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>24</v>
+        <v>585</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="G278" s="5"/>
       <c r="H278" s="5"/>
@@ -9433,22 +9427,22 @@
     </row>
     <row r="279" customHeight="1" ht="20">
       <c r="A279" s="5" t="n">
-        <v>2301</v>
+        <v>3041</v>
       </c>
       <c r="B279" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D279" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>142</v>
+        <v>2863</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>141</v>
+        <v>2823</v>
       </c>
       <c r="G279" s="5"/>
       <c r="H279" s="5"/>
@@ -9467,22 +9461,22 @@
     </row>
     <row r="280" customHeight="1" ht="20">
       <c r="A280" s="5" t="n">
-        <v>2321</v>
+        <v>3061</v>
       </c>
       <c r="B280" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="D280" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>585</v>
+        <v>24</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>584</v>
+        <v>22</v>
       </c>
       <c r="G280" s="5"/>
       <c r="H280" s="5"/>
@@ -9501,7 +9495,7 @@
     </row>
     <row r="281" customHeight="1" ht="20">
       <c r="A281" s="5" t="n">
-        <v>2363</v>
+        <v>2301</v>
       </c>
       <c r="B281" s="5" t="n">
         <v>461</v>
@@ -9510,12 +9504,14 @@
         <v>1222</v>
       </c>
       <c r="D281" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>963</v>
-      </c>
-      <c r="F281" s="5"/>
+        <v>142</v>
+      </c>
+      <c r="F281" s="5" t="n">
+        <v>141</v>
+      </c>
       <c r="G281" s="5"/>
       <c r="H281" s="5"/>
       <c r="I281" s="5"/>
@@ -9533,22 +9529,22 @@
     </row>
     <row r="282" customHeight="1" ht="20">
       <c r="A282" s="5" t="n">
-        <v>3141</v>
+        <v>2321</v>
       </c>
       <c r="B282" s="5" t="n">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>1322</v>
+        <v>1222</v>
       </c>
       <c r="D282" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>687</v>
+        <v>585</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>688</v>
+        <v>584</v>
       </c>
       <c r="G282" s="5"/>
       <c r="H282" s="5"/>
@@ -9567,23 +9563,21 @@
     </row>
     <row r="283" customHeight="1" ht="20">
       <c r="A283" s="5" t="n">
-        <v>2442</v>
+        <v>2363</v>
       </c>
       <c r="B283" s="5" t="n">
-        <v>261</v>
+        <v>461</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>1202</v>
+        <v>1222</v>
       </c>
       <c r="D283" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>2484</v>
-      </c>
-      <c r="F283" s="5" t="n">
-        <v>2485</v>
-      </c>
+        <v>963</v>
+      </c>
+      <c r="F283" s="5"/>
       <c r="G283" s="5"/>
       <c r="H283" s="5"/>
       <c r="I283" s="5"/>
@@ -9601,22 +9595,22 @@
     </row>
     <row r="284" customHeight="1" ht="20">
       <c r="A284" s="5" t="n">
-        <v>2503</v>
+        <v>3141</v>
       </c>
       <c r="B284" s="5" t="n">
-        <v>261</v>
+        <v>501</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>1202</v>
+        <v>1322</v>
       </c>
       <c r="D284" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>2525</v>
+        <v>687</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>2524</v>
+        <v>688</v>
       </c>
       <c r="G284" s="5"/>
       <c r="H284" s="5"/>
@@ -9635,22 +9629,22 @@
     </row>
     <row r="285" customHeight="1" ht="20">
       <c r="A285" s="5" t="n">
-        <v>2581</v>
+        <v>2442</v>
       </c>
       <c r="B285" s="5" t="n">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>1342</v>
+        <v>1202</v>
       </c>
       <c r="D285" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E285" s="5" t="n">
-        <v>2584</v>
+        <v>2484</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>2583</v>
+        <v>2485</v>
       </c>
       <c r="G285" s="5"/>
       <c r="H285" s="5"/>
@@ -9669,22 +9663,22 @@
     </row>
     <row r="286" customHeight="1" ht="20">
       <c r="A286" s="5" t="n">
-        <v>2701</v>
+        <v>2503</v>
       </c>
       <c r="B286" s="5" t="n">
-        <v>181</v>
+        <v>261</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>1262</v>
+        <v>1202</v>
       </c>
       <c r="D286" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>221</v>
+        <v>2525</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>1131</v>
+        <v>2524</v>
       </c>
       <c r="G286" s="5"/>
       <c r="H286" s="5"/>
@@ -9703,22 +9697,22 @@
     </row>
     <row r="287" customHeight="1" ht="20">
       <c r="A287" s="5" t="n">
-        <v>2761</v>
+        <v>2581</v>
       </c>
       <c r="B287" s="5" t="n">
-        <v>461</v>
+        <v>27</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>1302</v>
+        <v>1342</v>
       </c>
       <c r="D287" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>81</v>
+        <v>2584</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>2683</v>
+        <v>2583</v>
       </c>
       <c r="G287" s="5"/>
       <c r="H287" s="5"/>
@@ -9737,22 +9731,22 @@
     </row>
     <row r="288" customHeight="1" ht="20">
       <c r="A288" s="5" t="n">
-        <v>2921</v>
+        <v>2701</v>
       </c>
       <c r="B288" s="5" t="n">
-        <v>501</v>
+        <v>181</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>1322</v>
+        <v>1262</v>
       </c>
       <c r="D288" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>2803</v>
+        <v>221</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>2804</v>
+        <v>1131</v>
       </c>
       <c r="G288" s="5"/>
       <c r="H288" s="5"/>
@@ -9771,22 +9765,22 @@
     </row>
     <row r="289" customHeight="1" ht="20">
       <c r="A289" s="5" t="n">
-        <v>2922</v>
+        <v>2761</v>
       </c>
       <c r="B289" s="5" t="n">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>1423</v>
+        <v>1302</v>
       </c>
       <c r="D289" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E289" s="5" t="n">
-        <v>1303</v>
+        <v>81</v>
       </c>
       <c r="F289" s="5" t="n">
-        <v>1147</v>
+        <v>2683</v>
       </c>
       <c r="G289" s="5"/>
       <c r="H289" s="5"/>
@@ -9805,22 +9799,22 @@
     </row>
     <row r="290" customHeight="1" ht="20">
       <c r="A290" s="5" t="n">
-        <v>2924</v>
+        <v>2921</v>
       </c>
       <c r="B290" s="5" t="n">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>1423</v>
+        <v>1322</v>
       </c>
       <c r="D290" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>24</v>
+        <v>2803</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>22</v>
+        <v>2804</v>
       </c>
       <c r="G290" s="5"/>
       <c r="H290" s="5"/>
@@ -9839,7 +9833,7 @@
     </row>
     <row r="291" customHeight="1" ht="20">
       <c r="A291" s="5" t="n">
-        <v>2983</v>
+        <v>2922</v>
       </c>
       <c r="B291" s="5" t="n">
         <v>521</v>
@@ -9851,10 +9845,10 @@
         <v>1</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>2846</v>
+        <v>1303</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>2845</v>
+        <v>1147</v>
       </c>
       <c r="G291" s="5"/>
       <c r="H291" s="5"/>
@@ -9873,22 +9867,22 @@
     </row>
     <row r="292" customHeight="1" ht="20">
       <c r="A292" s="5" t="n">
-        <v>3181</v>
+        <v>2924</v>
       </c>
       <c r="B292" s="5" t="n">
-        <v>481</v>
+        <v>521</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>1282</v>
+        <v>1423</v>
       </c>
       <c r="D292" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>2164</v>
+        <v>24</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>2163</v>
+        <v>22</v>
       </c>
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
@@ -9907,22 +9901,22 @@
     </row>
     <row r="293" customHeight="1" ht="20">
       <c r="A293" s="5" t="n">
-        <v>3221</v>
+        <v>2983</v>
       </c>
       <c r="B293" s="5" t="n">
-        <v>41</v>
+        <v>521</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>1403</v>
+        <v>1423</v>
       </c>
       <c r="D293" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>2003</v>
+        <v>2846</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>2004</v>
+        <v>2845</v>
       </c>
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
@@ -9941,22 +9935,22 @@
     </row>
     <row r="294" customHeight="1" ht="20">
       <c r="A294" s="5" t="n">
-        <v>3261</v>
+        <v>3181</v>
       </c>
       <c r="B294" s="5" t="n">
-        <v>321</v>
+        <v>481</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>1444</v>
+        <v>1282</v>
       </c>
       <c r="D294" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>2944</v>
+        <v>2164</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>2943</v>
+        <v>2163</v>
       </c>
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
@@ -9975,21 +9969,23 @@
     </row>
     <row r="295" customHeight="1" ht="20">
       <c r="A295" s="5" t="n">
-        <v>3301</v>
+        <v>3221</v>
       </c>
       <c r="B295" s="5" t="n">
-        <v>461</v>
+        <v>41</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>1483</v>
+        <v>1403</v>
       </c>
       <c r="D295" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>2643</v>
-      </c>
-      <c r="F295" s="5"/>
+        <v>2003</v>
+      </c>
+      <c r="F295" s="5" t="n">
+        <v>2004</v>
+      </c>
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
       <c r="I295" s="5"/>
@@ -10007,75 +10003,73 @@
     </row>
     <row r="296" customHeight="1" ht="20">
       <c r="A296" s="5" t="n">
-        <v>3403</v>
+        <v>3261</v>
       </c>
       <c r="B296" s="5" t="n">
-        <v>541</v>
+        <v>321</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>1503</v>
+        <v>1444</v>
       </c>
       <c r="D296" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>3024</v>
+        <v>2944</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>3025</v>
+        <v>2943</v>
       </c>
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
       <c r="I296" s="5"/>
       <c r="J296" s="5"/>
       <c r="K296" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L296" s="7"/>
       <c r="M296" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N296" s="7" t="n">
-        <v>45831.8393287037</v>
+        <v>45831.8349884259</v>
       </c>
     </row>
     <row r="297" customHeight="1" ht="20">
       <c r="A297" s="5" t="n">
-        <v>3404</v>
+        <v>3301</v>
       </c>
       <c r="B297" s="5" t="n">
-        <v>541</v>
+        <v>461</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>1503</v>
+        <v>1483</v>
       </c>
       <c r="D297" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>3026</v>
-      </c>
-      <c r="F297" s="5" t="n">
-        <v>3027</v>
-      </c>
+        <v>2643</v>
+      </c>
+      <c r="F297" s="5"/>
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5"/>
       <c r="J297" s="5"/>
       <c r="K297" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L297" s="7"/>
       <c r="M297" s="6" t="s">
         <v>14</v>
       </c>
       <c r="N297" s="7" t="n">
-        <v>45831.8393287037</v>
+        <v>45831.8349884259</v>
       </c>
     </row>
     <row r="298" customHeight="1" ht="20">
       <c r="A298" s="5" t="n">
-        <v>3422</v>
+        <v>3403</v>
       </c>
       <c r="B298" s="5" t="n">
         <v>541</v>
@@ -10084,12 +10078,14 @@
         <v>1503</v>
       </c>
       <c r="D298" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>3065</v>
-      </c>
-      <c r="F298" s="5"/>
+        <v>3024</v>
+      </c>
+      <c r="F298" s="5" t="n">
+        <v>3025</v>
+      </c>
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
       <c r="I298" s="5"/>
@@ -10107,7 +10103,7 @@
     </row>
     <row r="299" customHeight="1" ht="20">
       <c r="A299" s="5" t="n">
-        <v>3424</v>
+        <v>3404</v>
       </c>
       <c r="B299" s="5" t="n">
         <v>541</v>
@@ -10119,10 +10115,10 @@
         <v>1</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>3068</v>
+        <v>3026</v>
       </c>
       <c r="F299" s="5" t="n">
-        <v>3069</v>
+        <v>3027</v>
       </c>
       <c r="G299" s="5"/>
       <c r="H299" s="5"/>
@@ -10141,7 +10137,7 @@
     </row>
     <row r="300" customHeight="1" ht="20">
       <c r="A300" s="5" t="n">
-        <v>3427</v>
+        <v>3422</v>
       </c>
       <c r="B300" s="5" t="n">
         <v>541</v>
@@ -10150,14 +10146,12 @@
         <v>1503</v>
       </c>
       <c r="D300" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>2583</v>
-      </c>
-      <c r="F300" s="5" t="n">
-        <v>2584</v>
-      </c>
+        <v>3065</v>
+      </c>
+      <c r="F300" s="5"/>
       <c r="G300" s="5"/>
       <c r="H300" s="5"/>
       <c r="I300" s="5"/>
@@ -10175,7 +10169,7 @@
     </row>
     <row r="301" customHeight="1" ht="20">
       <c r="A301" s="5" t="n">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="B301" s="5" t="n">
         <v>541</v>
@@ -10184,12 +10178,14 @@
         <v>1503</v>
       </c>
       <c r="D301" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>3071</v>
-      </c>
-      <c r="F301" s="5"/>
+        <v>3068</v>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>3069</v>
+      </c>
       <c r="G301" s="5"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5"/>
@@ -10207,21 +10203,23 @@
     </row>
     <row r="302" customHeight="1" ht="20">
       <c r="A302" s="5" t="n">
-        <v>3761</v>
+        <v>3427</v>
       </c>
       <c r="B302" s="5" t="n">
-        <v>681</v>
+        <v>541</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>1647</v>
+        <v>1503</v>
       </c>
       <c r="D302" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>3403</v>
-      </c>
-      <c r="F302" s="5"/>
+        <v>2583</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>2584</v>
+      </c>
       <c r="G302" s="5"/>
       <c r="H302" s="5"/>
       <c r="I302" s="5"/>
@@ -10229,27 +10227,29 @@
       <c r="K302" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L302" s="7" t="n">
-        <v>45859.6980671296</v>
-      </c>
-      <c r="M302" s="6"/>
-      <c r="N302" s="7"/>
+      <c r="L302" s="7"/>
+      <c r="M302" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N302" s="7" t="n">
+        <v>45831.8393287037</v>
+      </c>
     </row>
     <row r="303" customHeight="1" ht="20">
       <c r="A303" s="5" t="n">
-        <v>3841</v>
+        <v>3428</v>
       </c>
       <c r="B303" s="5" t="n">
-        <v>681</v>
+        <v>541</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>1647</v>
+        <v>1503</v>
       </c>
       <c r="D303" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>3463</v>
+        <v>3071</v>
       </c>
       <c r="F303" s="5"/>
       <c r="G303" s="5"/>
@@ -10259,31 +10259,31 @@
       <c r="K303" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L303" s="7" t="n">
-        <v>45895.3855324074</v>
-      </c>
-      <c r="M303" s="6"/>
-      <c r="N303" s="7"/>
+      <c r="L303" s="7"/>
+      <c r="M303" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N303" s="7" t="n">
+        <v>45831.8393287037</v>
+      </c>
     </row>
     <row r="304" customHeight="1" ht="20">
       <c r="A304" s="5" t="n">
-        <v>3901</v>
+        <v>3761</v>
       </c>
       <c r="B304" s="5" t="n">
-        <v>722</v>
+        <v>681</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>1684</v>
+        <v>1647</v>
       </c>
       <c r="D304" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>3523</v>
-      </c>
-      <c r="F304" s="5" t="n">
-        <v>3524</v>
-      </c>
+        <v>3403</v>
+      </c>
+      <c r="F304" s="5"/>
       <c r="G304" s="5"/>
       <c r="H304" s="5"/>
       <c r="I304" s="5"/>
@@ -10292,29 +10292,29 @@
         <v>15</v>
       </c>
       <c r="L304" s="7" t="n">
-        <v>45911.2688078704</v>
+        <v>45859.6980671296</v>
       </c>
       <c r="M304" s="6"/>
       <c r="N304" s="7"/>
     </row>
     <row r="305" customHeight="1" ht="20">
       <c r="A305" s="5" t="n">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="B305" s="5" t="n">
-        <v>621</v>
+        <v>722</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D305" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>3526</v>
+        <v>3523</v>
       </c>
       <c r="F305" s="5" t="n">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G305" s="5"/>
       <c r="H305" s="5"/>
@@ -10324,14 +10324,14 @@
         <v>15</v>
       </c>
       <c r="L305" s="7" t="n">
-        <v>45911.4241203704</v>
+        <v>45911.2688078704</v>
       </c>
       <c r="M305" s="6"/>
       <c r="N305" s="7"/>
     </row>
     <row r="306" customHeight="1" ht="20">
       <c r="A306" s="5" t="n">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="B306" s="5" t="n">
         <v>621</v>
@@ -10343,10 +10343,10 @@
         <v>1</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>3531</v>
+        <v>3526</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>3530</v>
+        <v>3525</v>
       </c>
       <c r="G306" s="5"/>
       <c r="H306" s="5"/>
@@ -10356,28 +10356,30 @@
         <v>15</v>
       </c>
       <c r="L306" s="7" t="n">
-        <v>45911.6326967593</v>
+        <v>45911.4241203704</v>
       </c>
       <c r="M306" s="6"/>
       <c r="N306" s="7"/>
     </row>
     <row r="307" customHeight="1" ht="20">
       <c r="A307" s="5" t="n">
-        <v>4284</v>
+        <v>3903</v>
       </c>
       <c r="B307" s="5" t="n">
-        <v>801</v>
+        <v>621</v>
       </c>
       <c r="C307" s="5" t="n">
-        <v>1763</v>
+        <v>1683</v>
       </c>
       <c r="D307" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>3810</v>
-      </c>
-      <c r="F307" s="5"/>
+        <v>3531</v>
+      </c>
+      <c r="F307" s="5" t="n">
+        <v>3530</v>
+      </c>
       <c r="G307" s="5"/>
       <c r="H307" s="5"/>
       <c r="I307" s="5"/>
@@ -10386,78 +10388,76 @@
         <v>15</v>
       </c>
       <c r="L307" s="7" t="n">
-        <v>46012.2927083333</v>
+        <v>45911.6326967593</v>
       </c>
       <c r="M307" s="6"/>
       <c r="N307" s="7"/>
     </row>
     <row r="308" customHeight="1" ht="20">
       <c r="A308" s="5" t="n">
-        <v>4022</v>
+        <v>4284</v>
       </c>
       <c r="B308" s="5" t="n">
-        <v>621</v>
+        <v>801</v>
       </c>
       <c r="C308" s="5" t="n">
-        <v>1683</v>
+        <v>1763</v>
       </c>
       <c r="D308" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>3543</v>
-      </c>
-      <c r="F308" s="5" t="n">
-        <v>3563</v>
-      </c>
+        <v>3810</v>
+      </c>
+      <c r="F308" s="5"/>
       <c r="G308" s="5"/>
       <c r="H308" s="5"/>
       <c r="I308" s="5"/>
       <c r="J308" s="5"/>
       <c r="K308" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L308" s="7" t="n">
-        <v>45947.2722222222</v>
+        <v>46012.2927083333</v>
       </c>
       <c r="M308" s="6"/>
       <c r="N308" s="7"/>
     </row>
     <row r="309" customHeight="1" ht="20">
       <c r="A309" s="5" t="n">
-        <v>4067</v>
+        <v>4022</v>
       </c>
       <c r="B309" s="5" t="n">
-        <v>781</v>
+        <v>621</v>
       </c>
       <c r="C309" s="5" t="n">
-        <v>1743</v>
+        <v>1683</v>
       </c>
       <c r="D309" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>3673</v>
+        <v>3543</v>
       </c>
       <c r="F309" s="5" t="n">
-        <v>3674</v>
+        <v>3563</v>
       </c>
       <c r="G309" s="5"/>
       <c r="H309" s="5"/>
       <c r="I309" s="5"/>
       <c r="J309" s="5"/>
       <c r="K309" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L309" s="7" t="n">
-        <v>45966.7240046296</v>
+        <v>45947.2722222222</v>
       </c>
       <c r="M309" s="6"/>
       <c r="N309" s="7"/>
     </row>
     <row r="310" customHeight="1" ht="20">
       <c r="A310" s="5" t="n">
-        <v>4071</v>
+        <v>4067</v>
       </c>
       <c r="B310" s="5" t="n">
         <v>781</v>
@@ -10469,10 +10469,10 @@
         <v>1</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>33</v>
+        <v>3673</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>3680</v>
+        <v>3674</v>
       </c>
       <c r="G310" s="5"/>
       <c r="H310" s="5"/>
@@ -10482,29 +10482,29 @@
         <v>15</v>
       </c>
       <c r="L310" s="7" t="n">
-        <v>45967.679375</v>
+        <v>45966.7240046296</v>
       </c>
       <c r="M310" s="6"/>
       <c r="N310" s="7"/>
     </row>
     <row r="311" customHeight="1" ht="20">
       <c r="A311" s="5" t="n">
-        <v>4141</v>
+        <v>4071</v>
       </c>
       <c r="B311" s="5" t="n">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="C311" s="5" t="n">
-        <v>1763</v>
+        <v>1743</v>
       </c>
       <c r="D311" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>3732</v>
+        <v>33</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>3731</v>
+        <v>3680</v>
       </c>
       <c r="G311" s="5"/>
       <c r="H311" s="5"/>
@@ -10514,29 +10514,29 @@
         <v>15</v>
       </c>
       <c r="L311" s="7" t="n">
-        <v>45985.7560185185</v>
+        <v>45967.679375</v>
       </c>
       <c r="M311" s="6"/>
       <c r="N311" s="7"/>
     </row>
     <row r="312" customHeight="1" ht="20">
       <c r="A312" s="5" t="n">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="B312" s="5" t="n">
-        <v>722</v>
+        <v>801</v>
       </c>
       <c r="C312" s="5" t="n">
-        <v>1684</v>
+        <v>1763</v>
       </c>
       <c r="D312" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>3736</v>
+        <v>3732</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>3733</v>
+        <v>3731</v>
       </c>
       <c r="G312" s="5"/>
       <c r="H312" s="5"/>
@@ -10546,28 +10546,30 @@
         <v>15</v>
       </c>
       <c r="L312" s="7" t="n">
-        <v>45986.6275578704</v>
+        <v>45985.7560185185</v>
       </c>
       <c r="M312" s="6"/>
       <c r="N312" s="7"/>
     </row>
     <row r="313" customHeight="1" ht="20">
       <c r="A313" s="5" t="n">
-        <v>4281</v>
+        <v>4142</v>
       </c>
       <c r="B313" s="5" t="n">
-        <v>822</v>
+        <v>722</v>
       </c>
       <c r="C313" s="5" t="n">
-        <v>1784</v>
+        <v>1684</v>
       </c>
       <c r="D313" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>3843</v>
-      </c>
-      <c r="F313" s="5"/>
+        <v>3736</v>
+      </c>
+      <c r="F313" s="5" t="n">
+        <v>3733</v>
+      </c>
       <c r="G313" s="5"/>
       <c r="H313" s="5"/>
       <c r="I313" s="5"/>
@@ -10576,30 +10578,28 @@
         <v>15</v>
       </c>
       <c r="L313" s="7" t="n">
-        <v>46011.5137962963</v>
+        <v>45986.6275578704</v>
       </c>
       <c r="M313" s="6"/>
       <c r="N313" s="7"/>
     </row>
     <row r="314" customHeight="1" ht="20">
       <c r="A314" s="5" t="n">
-        <v>4301</v>
+        <v>4281</v>
       </c>
       <c r="B314" s="5" t="n">
-        <v>762</v>
+        <v>822</v>
       </c>
       <c r="C314" s="5" t="n">
-        <v>1724</v>
+        <v>1784</v>
       </c>
       <c r="D314" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>3864</v>
-      </c>
-      <c r="F314" s="5" t="n">
-        <v>3865</v>
-      </c>
+        <v>3843</v>
+      </c>
+      <c r="F314" s="5"/>
       <c r="G314" s="5"/>
       <c r="H314" s="5"/>
       <c r="I314" s="5"/>
@@ -10608,14 +10608,14 @@
         <v>15</v>
       </c>
       <c r="L314" s="7" t="n">
-        <v>46014.5824189815</v>
+        <v>46011.5137962963</v>
       </c>
       <c r="M314" s="6"/>
       <c r="N314" s="7"/>
     </row>
     <row r="315" customHeight="1" ht="20">
       <c r="A315" s="5" t="n">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="B315" s="5" t="n">
         <v>762</v>
@@ -10624,13 +10624,13 @@
         <v>1724</v>
       </c>
       <c r="D315" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>3866</v>
+        <v>3864</v>
       </c>
       <c r="F315" s="5" t="n">
-        <v>3867</v>
+        <v>3865</v>
       </c>
       <c r="G315" s="5"/>
       <c r="H315" s="5"/>
@@ -10640,29 +10640,29 @@
         <v>15</v>
       </c>
       <c r="L315" s="7" t="n">
-        <v>46014.7677199074</v>
+        <v>46014.5824189815</v>
       </c>
       <c r="M315" s="6"/>
       <c r="N315" s="7"/>
     </row>
     <row r="316" customHeight="1" ht="20">
       <c r="A316" s="5" t="n">
-        <v>4322</v>
+        <v>4302</v>
       </c>
       <c r="B316" s="5" t="n">
-        <v>861</v>
+        <v>762</v>
       </c>
       <c r="C316" s="5" t="n">
-        <v>1823</v>
+        <v>1724</v>
       </c>
       <c r="D316" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>3026</v>
+        <v>3866</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>3889</v>
+        <v>3867</v>
       </c>
       <c r="G316" s="5"/>
       <c r="H316" s="5"/>
@@ -10672,7 +10672,7 @@
         <v>15</v>
       </c>
       <c r="L316" s="7" t="n">
-        <v>46031.444212963</v>
+        <v>46014.7677199074</v>
       </c>
       <c r="M316" s="6"/>
       <c r="N316" s="7"/>
@@ -13159,6 +13159,38 @@
       <c r="M391" s="6"/>
       <c r="N391" s="7"/>
     </row>
+    <row r="392" customHeight="1" ht="20">
+      <c r="A392" s="5" t="n">
+        <v>4383</v>
+      </c>
+      <c r="B392" s="5" t="n">
+        <v>681</v>
+      </c>
+      <c r="C392" s="5" t="n">
+        <v>1647</v>
+      </c>
+      <c r="D392" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E392" s="5" t="n">
+        <v>3463</v>
+      </c>
+      <c r="F392" s="5" t="n">
+        <v>3464</v>
+      </c>
+      <c r="G392" s="5"/>
+      <c r="H392" s="5"/>
+      <c r="I392" s="5"/>
+      <c r="J392" s="5"/>
+      <c r="K392" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L392" s="7" t="n">
+        <v>46042.5112847222</v>
+      </c>
+      <c r="M392" s="6"/>
+      <c r="N392" s="7"/>
+    </row>
   </sheetData>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
